--- a/scripts/rf_standard/performance.xlsx
+++ b/scripts/rf_standard/performance.xlsx
@@ -9,13 +9,18 @@
   <sheets>
     <sheet name="Models" sheetId="1" r:id="rId1"/>
     <sheet name="Ensemble" sheetId="2" r:id="rId2"/>
+    <sheet name="Ensemble optspreads" sheetId="3" r:id="rId3"/>
+    <sheet name="Ensemble opt-undspreads" sheetId="4" r:id="rId4"/>
+    <sheet name="Returns Long-Short 30-min" sheetId="5" r:id="rId5"/>
+    <sheet name="Returns Long-Short Daily" sheetId="6" r:id="rId6"/>
+    <sheet name="Returns Long-Short Weekly" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="490">
   <si>
     <t>Model</t>
   </si>
@@ -237,7 +242,1288 @@
     <t>H-L 10 portfolios, 0 turnover</t>
   </si>
   <si>
-    <t>[nan, nan]</t>
+    <t>[np.float64(0.0004820588315245959), np.float64(1.001790567415518e-44)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003689100906472612), np.float64(0.8533622863223276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0523380697222433), np.float64(0.29295560993516184)]</t>
+  </si>
+  <si>
+    <t>delta_change_mean</t>
+  </si>
+  <si>
+    <t>delta_change_std</t>
+  </si>
+  <si>
+    <t>turnover_mean</t>
+  </si>
+  <si>
+    <t>turnover_std</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.05 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.04 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.03 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.02 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 10 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0.01 turnover</t>
+  </si>
+  <si>
+    <t>H-L 3 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 4 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 5 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 20 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 40 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 100 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 200 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 500 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>H-L 1000 portfolios, 0 turnover</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0029601033827550286), np.float64(0.05788511622014319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0033538928422850323), np.float64(0.10667853402464922)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0037382483212616644), np.float64(0.1501104745537107)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001141544073113132), np.float64(0.62492319534898)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003867943745490544), np.float64(3.8900646334418796e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00783217534289903), np.float64(3.253031753908829e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01937357490785451), np.float64(3.8394231984566883e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.038261710903630126), np.float64(4.798672219077994e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0948493347248128), np.float64(7.104188975481393e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.18507810970569416), np.float64(2.947778997425599e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00025031936026054594), np.float64(0.5392496339107343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00032733895146167306), np.float64(0.5373057678209867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000922073432246435), np.float64(0.1424696026083461)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002840099176633991), np.float64(0.023465010976600562)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006095549476046528), np.float64(0.015104689816531746)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.012135201503362987), np.float64(0.015123284999678898)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.030135680846438695), np.float64(0.016218488811811656)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05922129680587816), np.float64(0.01588390267176346)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1488875755662819), np.float64(0.017489511738624376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.2831196583463467), np.float64(0.01283623390358915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00033372159073928245), np.float64(2.552036154304764e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.131320292077744e-05), np.float64(0.693623938104919)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000191754128441986), np.float64(0.046295772868878676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009830654577670172), np.float64(1.194430924148776e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0021463932001326656), np.float64(5.697360910450853e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004167517425344095), np.float64(1.3592034011757217e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010261986351497526), np.float64(1.6194303430229157e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01997316938562033), np.float64(3.974662654981205e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04876229385081216), np.float64(4.426087731729898e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09649560257085157), np.float64(6.032117465795841e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.9118350349755156e-05), np.float64(0.8098914349642953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002220731604242282), np.float64(0.1605667615635594)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000358282466183393), np.float64(0.05503681704057585)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011241316104938493), np.float64(0.002141702401272293)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0022547518194906053), np.float64(0.002079727123864244)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0043026131477454784), np.float64(0.003278797751360788)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.010151108261255903), np.float64(0.005487808652694589)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01963874947030213), np.float64(0.007239723135329921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04743499504377217), np.float64(0.007806560007749907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09762495416850694), np.float64(0.012914456709939343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4327107242553603e-05), np.float64(0.7300653076683155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00013426121466425742), np.float64(0.010360926924259233)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00023069902615054363), np.float64(0.0002451412834827408)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005494462431065081), np.float64(2.0337589348472094e-06)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009484894403048756), np.float64(2.387685212165973e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015837941180791525), np.float64(0.00035577292898922574)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0032310116849285507), np.float64(0.0032565519580296256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005834020662987798), np.float64(0.007927365499501375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013576201922238735), np.float64(0.016394480081174705)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.02647098727657651), np.float64(0.01946329912836149)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00025312898315247066), np.float64(2.847560661328432e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003051932798365421), np.float64(1.477972098225258e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00034556646277885983), np.float64(9.071276000074324e-32)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004820312330593954), np.float64(9.86662695389975e-45)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000629831898881468), np.float64(1.2314646494265331e-51)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0007896241068605242), np.float64(8.505166550403518e-47)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010069889642326485), np.float64(2.1731058993533746e-31)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011294591747747233), np.float64(1.5437204392047663e-19)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013678452157991515), np.float64(1.2498851001078133e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0016230217868987774), np.float64(6.470070517614647e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23136399896641255), np.float64(0.017535156111679287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.32422161706639896), np.float64(0.0124572455886308)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.40532800700844557), np.float64(0.012410898427019111)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.423554339827032), np.float64(0.0036313905365520384)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.05835910551408477), np.float64(0.31090608322992236)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0890402771482472), np.float64(0.43943984581350487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16052733307903888), np.float64(0.5728752511479711)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.381457272473683), np.float64(0.49802970152777915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3056372820349), np.float64(0.3590037137787597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.1747875480300896), np.float64(0.39511018177884444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006629111733152867), np.float64(0.7944459579894655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008647309172589475), np.float64(0.7937775373222696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007130918539722739), np.float64(0.8558055882933663)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.013879856792573432), np.float64(0.8584054906266408)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.028734406189155036), np.float64(0.8519572326813335)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06381474241074186), np.float64(0.8343254866421037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08045489041454844), np.float64(0.915844398501155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06366018798768644), np.float64(0.9654654298554077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.16137133109711077), np.float64(0.9654535446985408)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.8988591169679712), np.float64(0.8915168626728261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004488868628421866), np.float64(0.26237898056857556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005891685045774816), np.float64(0.23506986021528567)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.008559805058712113), np.float64(0.15422627111695586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01739214472881921), np.float64(0.1282632241786315)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03346165275667612), np.float64(0.13612687188543343)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06558334724876147), np.float64(0.14015012488102818)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09566719079685142), np.float64(0.38160189165953917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.21016972102915357), np.float64(0.33065749358684576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.46229060206432365), np.float64(0.37910493791749517)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.868700260619703), np.float64(0.3953663219710557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010233746525386824), np.float64(0.8923924067062023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003276439861815191), np.float64(0.7402593112316597)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.007107489130074979), np.float64(0.5418683864133194)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015914401380332448), np.float64(0.48193723686038514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03414100722148471), np.float64(0.4466293537620934)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0728170853077138), np.float64(0.41413498989742065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.18311916161411967), np.float64(0.40717428495140573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.290559620215824), np.float64(0.5078423463961962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7554400535593669), np.float64(0.4764936355304702)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0583457259429159), np.float64(0.635895009650867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0039123347197532994), np.float64(0.13087363678898362)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004922023650677899), np.float64(0.13018937964876318)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005929648839429765), np.float64(0.12817631592174394)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009883298243290982), np.float64(0.16461716790304828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.016193845700522846), np.float64(0.23783097135652415)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03406165783111767), np.float64(0.20716894006953485)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.07796076971805978), np.float64(0.2396103939659242)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.1354934410474627), np.float64(0.30128675284561507)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3336171074337972), np.float64(0.3185829759439053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5622198035737918), np.float64(0.38056355245918005)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00019172299789632305), np.float64(0.9028505361432493)]</t>
+  </si>
+  <si>
+    <t>[np.float64(7.467192368176363e-05), np.float64(0.9644419994783623)]</t>
+  </si>
+  <si>
+    <t>[np.float64(9.87363663072214e-05), np.float64(0.954961998789468)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00036571659055302345), np.float64(0.8545747327090296)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0010105235212235102), np.float64(0.6724851396779424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003935191695286238), np.float64(0.21338905784324255)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01019668023354195), np.float64(0.04330397222696026)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015844891518840862), np.float64(0.032271800594094784)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.02366157438181059), np.float64(0.04590359900666538)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.031217653998977243), np.float64(0.04693659728346033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.3679482105231973), np.float64(0.018118987322432695)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9506369918853443), np.float64(0.05144181109700294)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.680557059867465), np.float64(0.09323123078734319)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7414070593583877), np.float64(0.45865971973045355)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.645539569580769), np.float64(0.008312821920511023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5573357111320036), np.float64(0.0003962147954264471)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.96161939803166), np.float64(8.09449564198393e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.030323738660228), np.float64(6.090442046959092e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.011932305469105), np.float64(6.575054065666741e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.231048283205811), np.float64(2.5894691396722758e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.9692902935562808), np.float64(0.049257295602327264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0008595916790624), np.float64(0.31719102810934696)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1713758960100504), np.float64(0.8639706425043078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.336869251558861), np.float64(0.1816374468103827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9756153449656368), np.float64(0.04853449199026178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.236256550877597), np.float64(0.02560418955111033)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3424411687822078), np.float64(0.019397244774233036)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3839044163619096), np.float64(0.017357475933956822)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.3733634304524727), np.float64(0.017857322194457338)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.497743552838949), np.float64(0.012694285815327569)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.5573748197409323), np.float64(0.010726077628838699)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0093253318294), np.float64(0.04483109306977481)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5561370796159453), np.float64(0.12006276312343879)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.10130147781000567), np.float64(0.9193359980312056)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6974846606029768), np.float64(0.0899859036307462)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5755338052400982), np.float64(0.00037004313212840936)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.03633602714408), np.float64(5.842101642532666e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.301838523835074), np.float64(1.476533951100759e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.476628222832023), np.float64(5.773298108868063e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.471724094768286), np.float64(5.929573504570438e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0305485798400476), np.float64(0.04262423221218488)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5202141438261505), np.float64(0.12884405636610827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2108448262573657), np.float64(0.22630503042843)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.048975774653361094), np.float64(0.960950571740417)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.233132402707605), np.float64(0.21788104797770175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.0107403806246977), np.float64(0.04468100561098272)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4254447519466327), np.float64(0.015505347980950043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.505761712636957), np.float64(0.012412229242106455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5686113171125), np.float64(0.01038724137891719)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4473592413690284), np.float64(0.014600300792844578)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8944769618119288), np.float64(0.05851462895133544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7095192986352743), np.float64(0.0877345277158766)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5222885895040965), np.float64(0.1283237224795521)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9819353284829468), np.float64(0.3264223942733551)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.216525688323978), np.float64(0.8286320562307947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7660909470594169), np.float64(0.44384346602006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.8187546237718115), np.float64(0.06931485914947134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.170143560046151), np.float64(0.030283443534154943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.2782657266779656), np.float64(0.022968148770957906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.308861810910427), np.float64(0.021199979943094097)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4704472053640454), np.float64(0.14182567924312053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3527987287953562), np.float64(0.17649418687789598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3213293001212238), np.float64(0.18676149986084914)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0494346380776776), np.float64(0.2942884505186582)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7836974836009196), np.float64(0.43344477281612487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4402280904271168), np.float64(0.6598883576619388)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.21674717043468186), np.float64(0.8284594952386561)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03628876999462585), np.float64(0.9710609686869963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3374872542711906), np.float64(0.7358363060463775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.636160902311016), np.float64(0.5248497236979791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.003497430440660006), np.float64(0.06963466820322968)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004926386399896324), np.float64(0.09724283803848863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0019527437434908633), np.float64(0.2615799346151403)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0012462113004578761), np.float64(0.5937141292967908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003581766241380213), np.float64(2.881488837206427e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.007214698810348504), np.float64(1.3751580170721763e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017564225037371047), np.float64(6.738989174565938e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.03472380876298729), np.float64(1.0641317393422203e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.08733512267833822), np.float64(6.774162366941022e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.17354230737977824), np.float64(7.53232630759278e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00029670216734128263), np.float64(0.41829770999465765)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00018791363092244949), np.float64(0.6612670987078867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00080050641440752), np.float64(0.11162233318420371)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002814026325780979), np.float64(0.019269486122704245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005099229612690506), np.float64(0.0008761497998171733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009938296444633203), np.float64(0.0006286756336516055)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.024213966188281973), np.float64(0.0006969589044417956)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0494973363716827), np.float64(0.0020722622157699484)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.12974471705443236), np.float64(0.00479174641756013)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.23602555365805758), np.float64(0.0011654394029083522)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003827447354282297), np.float64(9.730015315730629e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-8.740771377831025e-05), np.float64(0.32340171851465815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00011563589983747896), np.float64(0.2840690915833733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009687333202759952), np.float64(8.816061669431755e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.002101359226480473), np.float64(3.0770858046210177e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004091752187322864), np.float64(6.001317419356649e-09)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009772481930047303), np.float64(2.133828369486016e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01907866582136463), np.float64(6.370742529111357e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04805565854425586), np.float64(2.71226293427375e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0948068633336329), np.float64(3.4909659456704575e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-7.745757264441599e-05), np.float64(0.49611314844474463)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00015522245717216343), np.float64(0.29813390468238177)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00034271433119740656), np.float64(0.06461476698734557)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0010868596674849897), np.float64(0.0018110382082513316)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0021738944115263065), np.float64(0.001818342302067771)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004126784644137339), np.float64(0.0032462070738495078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.009256377207655197), np.float64(0.002589847963113396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01801050899567641), np.float64(0.003442580121561838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04442971591908626), np.float64(0.004561582933480808)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.09226662026201589), np.float64(0.009258428628710234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-9.871614514593039e-05), np.float64(0.39517792289107706)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-3.107658723169161e-05), np.float64(0.8536057278640882)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.8340459965754486e-05), np.float64(0.8917750053138447)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00014207182937887075), np.float64(0.7367962569269324)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.991037976584946e-05), np.float64(0.9567433434078472)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0002089162593198675), np.float64(0.9094056941163816)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.00020865097014771743), np.float64(0.9468968158394672)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.001402184802501341), np.float64(0.8517911054466409)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0046188891556539005), np.float64(0.810051703850667)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0062108994687118165), np.float64(0.858922196853961)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002494528739076012), np.float64(8.2661651591107e-22)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0002997206678042302), np.float64(3.603849338687134e-27)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0003395921538587268), np.float64(1.5923312541460015e-31)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0004760087727046762), np.float64(2.0372448041571877e-44)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0006197223429227073), np.float64(4.334766532444857e-51)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.000777647392375537), np.float64(7.852133087561152e-46)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009883768936412211), np.float64(2.1631626943061404e-30)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0011153143903611198), np.float64(4.195436293389308e-19)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0013481310714238545), np.float64(2.095792587020711e-11)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0015990557246130296), np.float64(1.0099291371605019e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.26031714120109106), np.float64(0.030452066430353895)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.45155840161801425), np.float64(0.014696787552234025)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.3097039002440982), np.float64(0.004343643534163267)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.41418035942604425), np.float64(0.004423143580744833)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.030667312142688682), np.float64(0.47225021062437483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.040795023569510674), np.float64(0.6244749869753333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.04967934749696862), np.float64(0.7999936828592189)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.14791462173088402), np.float64(0.702950210975953)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7544400222079899), np.float64(0.46942211008991686)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.4564147652071708), np.float64(0.47153378648949923)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.005849057275885389), np.float64(0.7979465050467734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.006060487778902762), np.float64(0.8204435224003583)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.003965758020169173), np.float64(0.8993183089810807)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.01033289626906134), np.float64(0.8897733177972286)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012082202648176247), np.float64(0.8977185193395745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03124630523580502), np.float64(0.8602239757298437)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0985944364575336), np.float64(0.8197950709978109)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.09809198282240651), np.float64(0.918772702121852)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1637412812822382), np.float64(0.9523194748453874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.4282095508932904), np.float64(0.9194517522273681)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0032217319369807033), np.float64(0.4681310016353135)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.004510660298051315), np.float64(0.4140137219568328)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0066457974274403975), np.float64(0.3244075066573381)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.017190860575921667), np.float64(0.12287855995596102)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0331196546940222), np.float64(0.12472329985908483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.06234020893615128), np.float64(0.1430524152882809)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.13657641594898304), np.float64(0.19330521109033744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.280073413408286), np.float64(0.1818629957862983)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.40093781811933576), np.float64(0.43299012858023256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7110089996856837), np.float64(0.4718218777721514)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00289820411032665), np.float64(0.683378550992304)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.004596664216211171), np.float64(0.6216454961239046)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.006144260394861633), np.float64(0.5954277190604836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015275812326243735), np.float64(0.47729623825467776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0329283641112801), np.float64(0.4406906594375383)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.07084388833614688), np.float64(0.4076462842564978)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.1734659621549248), np.float64(0.35123614632273825)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2883172157930288), np.float64(0.4364991215416619)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7454511228773738), np.float64(0.42505840796014166)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.079199760439135), np.float64(0.5928106004924181)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0012562264073773448), np.float64(0.8622125316953049)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0009524484917205248), np.float64(0.9275975544575105)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.0005317798296406337), np.float64(0.9672671273110972)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0003737850275696184), np.float64(0.988606861291389)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0028036096754606348), np.float64(0.9604419866665828)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.012479217104375879), np.float64(0.911478766923471)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0015351431944713749), np.float64(0.9935384648030801)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.03858179055523102), np.float64(0.9315684906286312)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.24099252831931794), np.float64(0.8325716948621446)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.5327228451830506), np.float64(0.789035738120291)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-6.774526391588225e-05), np.float64(0.9654848261359755)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0001558095507279008), np.float64(0.9251698270034219)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-5.7670798022004606e-05), np.float64(0.9733515943776108)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.00025285711207313506), np.float64(0.8982054423944877)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0007592012827033397), np.float64(0.7481521132036902)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.0035875864779977757), np.float64(0.2546721072272941)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.009828742109018369), np.float64(0.051252409753148424)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.015073724629379892), np.float64(0.04267611355451029)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.021703811262240382), np.float64(0.06835676462981725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.025903829503188248), np.float64(0.10281875612820639)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1983357477479144), np.float64(0.028204942914826905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.8647454066800568), np.float64(0.0625754545673448)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.5287905025839672), np.float64(0.12670344416402174)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.7872587543610382), np.float64(0.4313587257371188)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.8879521205251653), np.float64(0.003980011372853263)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.276496100395588), np.float64(2.1229511046500277e-05)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.11504844943395), np.float64(3.910904112872196e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.237762432121668), np.float64(2.06943571670839e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.004439045526001), np.float64(6.863186261737532e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.0049953489827255), np.float64(6.843984589896429e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.0911622022025633), np.float64(0.03682188874424213)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2748096279033143), np.float64(0.2027390585602508)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3643671114376124), np.float64(0.7156781741721003)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.3570882174329384), np.float64(0.17512797422192145)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4655096804366634), np.float64(0.013886364674836076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0145068392393513), np.float64(0.0026535766367801715)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2490792160446182), np.float64(0.001205114540279064)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.0258570881281828), np.float64(0.002557041110763261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.80916380411789), np.float64(0.005085635263496442)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2478222046768788), np.float64(0.0012103819895221465)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.6318668364802376), np.float64(0.008651902551021256)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1143474943282556), np.float64(0.03478795828047132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6920313801306341), np.float64(0.09102129935099407)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.08083689442384936), np.float64(0.9355914640684728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.6590190095871997), np.float64(0.09749576190545498)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.5799395924253115), np.float64(0.00036395505732296886)]</t>
+  </si>
+  <si>
+    <t>[np.float64(4.999174730663619), np.float64(7.047485562438567e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.2292692778731285), np.float64(2.1635542127016796e-07)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.554363062122739), np.float64(3.770103335013574e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(5.563890884055493), np.float64(3.576952585863081e-08)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.1458127960279407), np.float64(0.032181950673841726)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.6864644536049078), np.float64(0.0920881504964991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.2933469867306153), np.float64(0.19625663630572085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.01798841720611905), np.float64(0.9856524855702027)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.1643599824014557), np.float64(0.2446180450756466)]</t>
+  </si>
+  <si>
+    <t>[np.float64(1.9501248270964897), np.float64(0.051502919404666066)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.570642941230474), np.float64(0.010327006731414023)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.69270234952945), np.float64(0.007232710493117098)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7261483297198823), np.float64(0.006545041448479387)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.5596316190585466), np.float64(0.010657244210622774)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-2.096268981212016), np.float64(0.03636538743189565)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.939589023694108), np.float64(0.05277355276526772)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.7765406651919258), np.float64(0.07601590431281506)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3900394732471149), np.float64(0.16489548760750092)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.9671847577821231), np.float64(0.33373789328118797)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.6824970256236365), np.float64(0.49511818126856516)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.28735657833371636), np.float64(0.7739121729003722)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.34240012398741726), np.float64(0.7321378608782406)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.3137845079641292), np.float64(0.7537648094326744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.2196870955885219), np.float64(0.8261697315411011)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.4767388245576152), np.float64(0.14013099233506054)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.3861094125565272), np.float64(0.16609167485575785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.297575667168454), np.float64(0.19479943489516915)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-1.0778423371893542), np.float64(0.2814222554246115)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.8189319421764871), np.float64(0.41306405160167947)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.49302758276821246), np.float64(0.6221255815013867)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.23057756409487687), np.float64(0.817700723417857)]</t>
+  </si>
+  <si>
+    <t>[np.float64(-0.008096319429284174), np.float64(0.9935421187865863)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.5566283469969264), np.float64(0.5779338129348733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(0.7677244055659298), np.float64(0.44287275411342847)]</t>
+  </si>
+  <si>
+    <t>Returns</t>
   </si>
 </sst>
 </file>
@@ -1696,10 +2982,6169 @@
         <v>62</v>
       </c>
       <c r="V12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="W12" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001146553157915661</v>
+      </c>
+      <c r="D2">
+        <v>-0.002701938385143876</v>
+      </c>
+      <c r="E2">
+        <v>0.04459492117166519</v>
+      </c>
+      <c r="F2">
+        <v>0.0007123117102310061</v>
+      </c>
+      <c r="G2">
+        <v>0.0007777203572914004</v>
+      </c>
+      <c r="H2">
+        <v>1.000584936833344</v>
+      </c>
+      <c r="I2">
+        <v>0.04894854640490188</v>
+      </c>
+      <c r="J2">
+        <v>-0.06058847904205322</v>
+      </c>
+      <c r="K2">
+        <v>-0.999858558177948</v>
+      </c>
+      <c r="L2">
+        <v>2.552450656890869</v>
+      </c>
+      <c r="M2">
+        <v>-3.4678635597229</v>
+      </c>
+      <c r="N2" t="s">
+        <v>129</v>
+      </c>
+      <c r="O2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001524911231560309</v>
+      </c>
+      <c r="D3">
+        <v>-0.002993358997628093</v>
+      </c>
+      <c r="E3">
+        <v>0.05944027751684189</v>
+      </c>
+      <c r="F3">
+        <v>0.0008161556324921548</v>
+      </c>
+      <c r="G3">
+        <v>0.0008092896896414459</v>
+      </c>
+      <c r="H3">
+        <v>1.00085931553909</v>
+      </c>
+      <c r="I3">
+        <v>0.04888021841599295</v>
+      </c>
+      <c r="J3">
+        <v>-0.05035910382866859</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999457001686096</v>
+      </c>
+      <c r="L3">
+        <v>3.40214467048645</v>
+      </c>
+      <c r="M3">
+        <v>-2.882371425628662</v>
+      </c>
+      <c r="N3" t="s">
+        <v>130</v>
+      </c>
+      <c r="O3" t="s">
+        <v>190</v>
+      </c>
+      <c r="P3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001902375081829175</v>
+      </c>
+      <c r="D4">
+        <v>-0.003297819290310144</v>
+      </c>
+      <c r="E4">
+        <v>0.07429040223360062</v>
+      </c>
+      <c r="F4">
+        <v>0.0009088914375752211</v>
+      </c>
+      <c r="G4">
+        <v>0.0008943888242356479</v>
+      </c>
+      <c r="H4">
+        <v>1.000995561195908</v>
+      </c>
+      <c r="I4">
+        <v>0.04888530918571012</v>
+      </c>
+      <c r="J4">
+        <v>-0.04439092054963112</v>
+      </c>
+      <c r="K4">
+        <v>-0.9999800324440002</v>
+      </c>
+      <c r="L4">
+        <v>4.252111434936523</v>
+      </c>
+      <c r="M4">
+        <v>-2.540774345397949</v>
+      </c>
+      <c r="N4" t="s">
+        <v>131</v>
+      </c>
+      <c r="O4" t="s">
+        <v>191</v>
+      </c>
+      <c r="P4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.00377448510281827</v>
+      </c>
+      <c r="D5">
+        <v>-0.0007000447367317975</v>
+      </c>
+      <c r="E5">
+        <v>0.06692208349704742</v>
+      </c>
+      <c r="F5">
+        <v>0.00131116365082562</v>
+      </c>
+      <c r="G5">
+        <v>0.001255039940588176</v>
+      </c>
+      <c r="H5">
+        <v>1.001097069177549</v>
+      </c>
+      <c r="I5">
+        <v>0.04897025058339217</v>
+      </c>
+      <c r="J5">
+        <v>-0.01046059373766184</v>
+      </c>
+      <c r="K5">
+        <v>-0.8991568088531494</v>
+      </c>
+      <c r="L5">
+        <v>3.830375909805298</v>
+      </c>
+      <c r="M5">
+        <v>-0.598726212978363</v>
+      </c>
+      <c r="N5" t="s">
+        <v>132</v>
+      </c>
+      <c r="O5" t="s">
+        <v>192</v>
+      </c>
+      <c r="P5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.007468422047688972</v>
+      </c>
+      <c r="D6">
+        <v>0.00393149396404624</v>
+      </c>
+      <c r="E6">
+        <v>0.02668340690433979</v>
+      </c>
+      <c r="F6">
+        <v>0.001795550691895187</v>
+      </c>
+      <c r="G6">
+        <v>0.001554573886096478</v>
+      </c>
+      <c r="H6">
+        <v>1.001033683567585</v>
+      </c>
+      <c r="I6">
+        <v>0.0492144806091319</v>
+      </c>
+      <c r="J6">
+        <v>0.1473385244607925</v>
+      </c>
+      <c r="K6">
+        <v>382472.65625</v>
+      </c>
+      <c r="L6">
+        <v>1.527260899543762</v>
+      </c>
+      <c r="M6">
+        <v>8.433119773864746</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01477952904935233</v>
+      </c>
+      <c r="D7">
+        <v>0.007923153229057789</v>
+      </c>
+      <c r="E7">
+        <v>0.05349219590425491</v>
+      </c>
+      <c r="F7">
+        <v>0.002168016275390983</v>
+      </c>
+      <c r="G7">
+        <v>0.001777229597792029</v>
+      </c>
+      <c r="H7">
+        <v>1.00092553047854</v>
+      </c>
+      <c r="I7">
+        <v>0.04926054165348377</v>
+      </c>
+      <c r="J7">
+        <v>0.1481179296970367</v>
+      </c>
+      <c r="K7">
+        <v>169120022528</v>
+      </c>
+      <c r="L7">
+        <v>3.061698198318481</v>
+      </c>
+      <c r="M7">
+        <v>8.477729797363281</v>
+      </c>
+      <c r="N7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O7" t="s">
+        <v>194</v>
+      </c>
+      <c r="P7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.03644820320318456</v>
+      </c>
+      <c r="D8">
+        <v>0.01952189020812511</v>
+      </c>
+      <c r="E8">
+        <v>0.1335829794406891</v>
+      </c>
+      <c r="F8">
+        <v>0.002350918715819716</v>
+      </c>
+      <c r="G8">
+        <v>0.001871517393738031</v>
+      </c>
+      <c r="H8">
+        <v>1.000589091230315</v>
+      </c>
+      <c r="I8">
+        <v>0.05083449506969839</v>
+      </c>
+      <c r="J8">
+        <v>0.1461405456066132</v>
+      </c>
+      <c r="K8">
+        <v>3.213908631092129E+27</v>
+      </c>
+      <c r="L8">
+        <v>7.64580249786377</v>
+      </c>
+      <c r="M8">
+        <v>8.364551544189453</v>
+      </c>
+      <c r="N8" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.07237067430206512</v>
+      </c>
+      <c r="D9">
+        <v>0.03862500935792923</v>
+      </c>
+      <c r="E9">
+        <v>0.2672166228294373</v>
+      </c>
+      <c r="F9">
+        <v>0.002229031873866916</v>
+      </c>
+      <c r="G9">
+        <v>0.001823435421101749</v>
+      </c>
+      <c r="H9">
+        <v>1.000403181197968</v>
+      </c>
+      <c r="I9">
+        <v>0.05244348947302026</v>
+      </c>
+      <c r="J9">
+        <v>0.1445456892251968</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>15.29450416564941</v>
+      </c>
+      <c r="M9">
+        <v>8.27326774597168</v>
+      </c>
+      <c r="N9" t="s">
+        <v>136</v>
+      </c>
+      <c r="O9" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.1808706604195766</v>
+      </c>
+      <c r="D10">
+        <v>0.09596756845712662</v>
+      </c>
+      <c r="E10">
+        <v>0.6783690452575684</v>
+      </c>
+      <c r="F10">
+        <v>0.002071449067443609</v>
+      </c>
+      <c r="G10">
+        <v>0.001808948698453605</v>
+      </c>
+      <c r="H10">
+        <v>1.000993608934245</v>
+      </c>
+      <c r="I10">
+        <v>0.05787263100092598</v>
+      </c>
+      <c r="J10">
+        <v>0.1414680778980255</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>38.82736968994141</v>
+      </c>
+      <c r="M10">
+        <v>8.097116470336914</v>
+      </c>
+      <c r="N10" t="s">
+        <v>137</v>
+      </c>
+      <c r="O10" t="s">
+        <v>197</v>
+      </c>
+      <c r="P10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3525203574301216</v>
+      </c>
+      <c r="D11">
+        <v>0.1869264096021652</v>
+      </c>
+      <c r="E11">
+        <v>1.258220076560974</v>
+      </c>
+      <c r="F11">
+        <v>0.002014117082580924</v>
+      </c>
+      <c r="G11">
+        <v>0.001961537636816502</v>
+      </c>
+      <c r="H11">
+        <v>1.002172582619339</v>
+      </c>
+      <c r="I11">
+        <v>0.06754014983666096</v>
+      </c>
+      <c r="J11">
+        <v>0.1485641598701477</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>72.01592254638672</v>
+      </c>
+      <c r="M11">
+        <v>8.503270149230957</v>
+      </c>
+      <c r="N11" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" t="s">
+        <v>198</v>
+      </c>
+      <c r="P11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001719988811234501</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002429449959890917</v>
+      </c>
+      <c r="E12">
+        <v>0.01162141840904951</v>
+      </c>
+      <c r="F12">
+        <v>0.0007286037434823811</v>
+      </c>
+      <c r="G12">
+        <v>0.0007750873337499797</v>
+      </c>
+      <c r="H12">
+        <v>1.000552900725767</v>
+      </c>
+      <c r="I12">
+        <v>0.04897674439768888</v>
+      </c>
+      <c r="J12">
+        <v>-0.02090493403375149</v>
+      </c>
+      <c r="K12">
+        <v>-0.5488683581352234</v>
+      </c>
+      <c r="L12">
+        <v>0.6651675701141357</v>
+      </c>
+      <c r="M12">
+        <v>-1.196522116661072</v>
+      </c>
+      <c r="N12" t="s">
+        <v>139</v>
+      </c>
+      <c r="O12" t="s">
+        <v>199</v>
+      </c>
+      <c r="P12" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.002289598988456791</v>
+      </c>
+      <c r="D13">
+        <v>0.0003368866164237261</v>
+      </c>
+      <c r="E13">
+        <v>0.01512523274868727</v>
+      </c>
+      <c r="F13">
+        <v>0.0008392505696974695</v>
+      </c>
+      <c r="G13">
+        <v>0.0008320929482579231</v>
+      </c>
+      <c r="H13">
+        <v>1.000794778106396</v>
+      </c>
+      <c r="I13">
+        <v>0.04893083227036909</v>
+      </c>
+      <c r="J13">
+        <v>0.02227315306663513</v>
+      </c>
+      <c r="K13">
+        <v>2.014550924301147</v>
+      </c>
+      <c r="L13">
+        <v>0.8657131195068359</v>
+      </c>
+      <c r="M13">
+        <v>1.274834036827087</v>
+      </c>
+      <c r="N13" t="s">
+        <v>140</v>
+      </c>
+      <c r="O13" t="s">
+        <v>200</v>
+      </c>
+      <c r="P13" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002857159927645605</v>
+      </c>
+      <c r="D14">
+        <v>0.0009297257056459785</v>
+      </c>
+      <c r="E14">
+        <v>0.01791263371706009</v>
+      </c>
+      <c r="F14">
+        <v>0.0009487716015428305</v>
+      </c>
+      <c r="G14">
+        <v>0.0009283614344894886</v>
+      </c>
+      <c r="H14">
+        <v>1.000952474179532</v>
+      </c>
+      <c r="I14">
+        <v>0.04891002523583736</v>
+      </c>
+      <c r="J14">
+        <v>0.05190335214138031</v>
+      </c>
+      <c r="K14">
+        <v>19.99586868286133</v>
+      </c>
+      <c r="L14">
+        <v>1.025253772735596</v>
+      </c>
+      <c r="M14">
+        <v>2.970758438110352</v>
+      </c>
+      <c r="N14" t="s">
+        <v>141</v>
+      </c>
+      <c r="O14" t="s">
+        <v>201</v>
+      </c>
+      <c r="P14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.005682750839720679</v>
+      </c>
+      <c r="D15">
+        <v>0.002854385646060109</v>
+      </c>
+      <c r="E15">
+        <v>0.03568844869732857</v>
+      </c>
+      <c r="F15">
+        <v>0.001370460027828813</v>
+      </c>
+      <c r="G15">
+        <v>0.001291002612560987</v>
+      </c>
+      <c r="H15">
+        <v>1.001029258893546</v>
+      </c>
+      <c r="I15">
+        <v>0.04904015231606774</v>
+      </c>
+      <c r="J15">
+        <v>0.07998065650463104</v>
+      </c>
+      <c r="K15">
+        <v>11355.2275390625</v>
+      </c>
+      <c r="L15">
+        <v>2.042676687240601</v>
+      </c>
+      <c r="M15">
+        <v>4.577800750732422</v>
+      </c>
+      <c r="N15" t="s">
+        <v>142</v>
+      </c>
+      <c r="O15" t="s">
+        <v>202</v>
+      </c>
+      <c r="P15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.01127590109798376</v>
+      </c>
+      <c r="D16">
+        <v>0.0061264643445611</v>
+      </c>
+      <c r="E16">
+        <v>0.07139697670936584</v>
+      </c>
+      <c r="F16">
+        <v>0.001859754556789994</v>
+      </c>
+      <c r="G16">
+        <v>0.001591706532053649</v>
+      </c>
+      <c r="H16">
+        <v>1.001011540241924</v>
+      </c>
+      <c r="I16">
+        <v>0.04918450852285423</v>
+      </c>
+      <c r="J16">
+        <v>0.08580845594406128</v>
+      </c>
+      <c r="K16">
+        <v>489677824</v>
+      </c>
+      <c r="L16">
+        <v>4.086502552032471</v>
+      </c>
+      <c r="M16">
+        <v>4.911363124847412</v>
+      </c>
+      <c r="N16" t="s">
+        <v>143</v>
+      </c>
+      <c r="O16" t="s">
+        <v>203</v>
+      </c>
+      <c r="P16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.02232811585277765</v>
+      </c>
+      <c r="D17">
+        <v>0.01220015715807676</v>
+      </c>
+      <c r="E17">
+        <v>0.1422016769647598</v>
+      </c>
+      <c r="F17">
+        <v>0.002239057095721364</v>
+      </c>
+      <c r="G17">
+        <v>0.001813974580727518</v>
+      </c>
+      <c r="H17">
+        <v>1.000875867626674</v>
+      </c>
+      <c r="I17">
+        <v>0.04930794606555218</v>
+      </c>
+      <c r="J17">
+        <v>0.08579474687576294</v>
+      </c>
+      <c r="K17">
+        <v>1.78925159275561E+17</v>
+      </c>
+      <c r="L17">
+        <v>8.139104843139648</v>
+      </c>
+      <c r="M17">
+        <v>4.91057825088501</v>
+      </c>
+      <c r="N17" t="s">
+        <v>144</v>
+      </c>
+      <c r="O17" t="s">
+        <v>204</v>
+      </c>
+      <c r="P17" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.05542988101715576</v>
+      </c>
+      <c r="D18">
+        <v>0.03021205216646194</v>
+      </c>
+      <c r="E18">
+        <v>0.3569758236408234</v>
+      </c>
+      <c r="F18">
+        <v>0.002389397006481886</v>
+      </c>
+      <c r="G18">
+        <v>0.001892620581202209</v>
+      </c>
+      <c r="H18">
+        <v>1.000564594161063</v>
+      </c>
+      <c r="I18">
+        <v>0.0509414726745562</v>
+      </c>
+      <c r="J18">
+        <v>0.08463332802057266</v>
+      </c>
+      <c r="K18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L18">
+        <v>20.43199348449707</v>
+      </c>
+      <c r="M18">
+        <v>4.84410285949707</v>
+      </c>
+      <c r="N18" t="s">
+        <v>145</v>
+      </c>
+      <c r="O18" t="s">
+        <v>205</v>
+      </c>
+      <c r="P18" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.1091499014958178</v>
+      </c>
+      <c r="D19">
+        <v>0.05928422883152962</v>
+      </c>
+      <c r="E19">
+        <v>0.6992238163948059</v>
+      </c>
+      <c r="F19">
+        <v>0.002216283697634935</v>
+      </c>
+      <c r="G19">
+        <v>0.001831445260904729</v>
+      </c>
+      <c r="H19">
+        <v>1.000349831765927</v>
+      </c>
+      <c r="I19">
+        <v>0.0524422717036855</v>
+      </c>
+      <c r="J19">
+        <v>0.08478576689958572</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>40.02101898193359</v>
+      </c>
+      <c r="M19">
+        <v>4.852828025817871</v>
+      </c>
+      <c r="N19" t="s">
+        <v>146</v>
+      </c>
+      <c r="O19" t="s">
+        <v>206</v>
+      </c>
+      <c r="P19" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2748660446195824</v>
+      </c>
+      <c r="D20">
+        <v>0.1490462720394135</v>
+      </c>
+      <c r="E20">
+        <v>1.784208059310913</v>
+      </c>
+      <c r="F20">
+        <v>0.00204509636387229</v>
+      </c>
+      <c r="G20">
+        <v>0.00181538553442806</v>
+      </c>
+      <c r="H20">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I20">
+        <v>0.05806890046728418</v>
+      </c>
+      <c r="J20">
+        <v>0.08353637158870697</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>102.1215591430664</v>
+      </c>
+      <c r="M20">
+        <v>4.781317234039307</v>
+      </c>
+      <c r="N20" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" t="s">
+        <v>207</v>
+      </c>
+      <c r="P20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.5242911592465471</v>
+      </c>
+      <c r="D21">
+        <v>0.2839060723781586</v>
+      </c>
+      <c r="E21">
+        <v>3.240917444229126</v>
+      </c>
+      <c r="F21">
+        <v>0.002049535978585482</v>
+      </c>
+      <c r="G21">
+        <v>0.002059989841654897</v>
+      </c>
+      <c r="H21">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I21">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J21">
+        <v>0.08760052919387817</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>185.498291015625</v>
+      </c>
+      <c r="M21">
+        <v>5.01393461227417</v>
+      </c>
+      <c r="N21" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" t="s">
+        <v>208</v>
+      </c>
+      <c r="P21" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0006310631930965809</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003287565486971289</v>
+      </c>
+      <c r="E22">
+        <v>0.001832251087762415</v>
+      </c>
+      <c r="F22">
+        <v>0.000737927679438144</v>
+      </c>
+      <c r="G22">
+        <v>0.000769663427490741</v>
+      </c>
+      <c r="H22">
+        <v>1.000503051329642</v>
+      </c>
+      <c r="I22">
+        <v>0.04896867479650974</v>
+      </c>
+      <c r="J22">
+        <v>-0.1794276684522629</v>
+      </c>
+      <c r="K22">
+        <v>-0.6594719886779785</v>
+      </c>
+      <c r="L22">
+        <v>0.1048713698983192</v>
+      </c>
+      <c r="M22">
+        <v>-10.26978492736816</v>
+      </c>
+      <c r="N22" t="s">
+        <v>149</v>
+      </c>
+      <c r="O22" t="s">
+        <v>209</v>
+      </c>
+      <c r="P22" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.000837452291343372</v>
+      </c>
+      <c r="D23">
+        <v>-2.481026785972062E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.002267750445753336</v>
+      </c>
+      <c r="F23">
+        <v>0.0008544670999981463</v>
+      </c>
+      <c r="G23">
+        <v>0.0008491038461215794</v>
+      </c>
+      <c r="H23">
+        <v>1.000704730537114</v>
+      </c>
+      <c r="I23">
+        <v>0.04892410577069633</v>
+      </c>
+      <c r="J23">
+        <v>-0.01094047538936138</v>
+      </c>
+      <c r="K23">
+        <v>-0.07801944017410278</v>
+      </c>
+      <c r="L23">
+        <v>0.1297977566719055</v>
+      </c>
+      <c r="M23">
+        <v>-0.6261928677558899</v>
+      </c>
+      <c r="N23" t="s">
+        <v>150</v>
+      </c>
+      <c r="O23" t="s">
+        <v>210</v>
+      </c>
+      <c r="P23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001041666127198925</v>
+      </c>
+      <c r="D24">
+        <v>0.0002009630698012188</v>
+      </c>
+      <c r="E24">
+        <v>0.002743544522672892</v>
+      </c>
+      <c r="F24">
+        <v>0.000975981296505779</v>
+      </c>
+      <c r="G24">
+        <v>0.0009524933411739767</v>
+      </c>
+      <c r="H24">
+        <v>1.000831809451594</v>
+      </c>
+      <c r="I24">
+        <v>0.04896563379862271</v>
+      </c>
+      <c r="J24">
+        <v>0.07324942946434021</v>
+      </c>
+      <c r="K24">
+        <v>0.9316350221633911</v>
+      </c>
+      <c r="L24">
+        <v>0.1570304781198502</v>
+      </c>
+      <c r="M24">
+        <v>4.192530155181885</v>
+      </c>
+      <c r="N24" t="s">
+        <v>151</v>
+      </c>
+      <c r="O24" t="s">
+        <v>211</v>
+      </c>
+      <c r="P24" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.002042808195610897</v>
+      </c>
+      <c r="D25">
+        <v>0.001001509837806225</v>
+      </c>
+      <c r="E25">
+        <v>0.005256281699985266</v>
+      </c>
+      <c r="F25">
+        <v>0.001436703023500741</v>
+      </c>
+      <c r="G25">
+        <v>0.00132189888972789</v>
+      </c>
+      <c r="H25">
+        <v>1.000926701939862</v>
+      </c>
+      <c r="I25">
+        <v>0.04909680091019256</v>
+      </c>
+      <c r="J25">
+        <v>0.1905357986688614</v>
+      </c>
+      <c r="K25">
+        <v>25.55445861816406</v>
+      </c>
+      <c r="L25">
+        <v>0.3008503913879395</v>
+      </c>
+      <c r="M25">
+        <v>10.90557384490967</v>
+      </c>
+      <c r="N25" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" t="s">
+        <v>212</v>
+      </c>
+      <c r="P25" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.003982129479056409</v>
+      </c>
+      <c r="D26">
+        <v>0.002182038268074393</v>
+      </c>
+      <c r="E26">
+        <v>0.010410794056952</v>
+      </c>
+      <c r="F26">
+        <v>0.001929727965034544</v>
+      </c>
+      <c r="G26">
+        <v>0.001634958432987332</v>
+      </c>
+      <c r="H26">
+        <v>1.000967101392221</v>
+      </c>
+      <c r="I26">
+        <v>0.04922220966213589</v>
+      </c>
+      <c r="J26">
+        <v>0.2095938324928284</v>
+      </c>
+      <c r="K26">
+        <v>1261.017578125</v>
+      </c>
+      <c r="L26">
+        <v>0.5958758592605591</v>
+      </c>
+      <c r="M26">
+        <v>11.99638652801514</v>
+      </c>
+      <c r="N26" t="s">
+        <v>153</v>
+      </c>
+      <c r="O26" t="s">
+        <v>213</v>
+      </c>
+      <c r="P26" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.007754677829472946</v>
+      </c>
+      <c r="D27">
+        <v>0.004234179388731718</v>
+      </c>
+      <c r="E27">
+        <v>0.02075189910829067</v>
+      </c>
+      <c r="F27">
+        <v>0.002320436295121908</v>
+      </c>
+      <c r="G27">
+        <v>0.001860012300312519</v>
+      </c>
+      <c r="H27">
+        <v>1.000840675366588</v>
+      </c>
+      <c r="I27">
+        <v>0.04929697829763833</v>
+      </c>
+      <c r="J27">
+        <v>0.2040381580591202</v>
+      </c>
+      <c r="K27">
+        <v>1026778.6875</v>
+      </c>
+      <c r="L27">
+        <v>1.187762975692749</v>
+      </c>
+      <c r="M27">
+        <v>11.67840003967285</v>
+      </c>
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>214</v>
+      </c>
+      <c r="P27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.01887617704970702</v>
+      </c>
+      <c r="D28">
+        <v>0.01035221852362156</v>
+      </c>
+      <c r="E28">
+        <v>0.05134658887982368</v>
+      </c>
+      <c r="F28">
+        <v>0.002406200626865029</v>
+      </c>
+      <c r="G28">
+        <v>0.001912307576276362</v>
+      </c>
+      <c r="H28">
+        <v>1.000537237503253</v>
+      </c>
+      <c r="I28">
+        <v>0.05098689485551912</v>
+      </c>
+      <c r="J28">
+        <v>0.2016145288944244</v>
+      </c>
+      <c r="K28">
+        <v>449718475816960</v>
+      </c>
+      <c r="L28">
+        <v>2.938891410827637</v>
+      </c>
+      <c r="M28">
+        <v>11.53967952728271</v>
+      </c>
+      <c r="N28" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" t="s">
+        <v>215</v>
+      </c>
+      <c r="P28" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03724154251019005</v>
+      </c>
+      <c r="D29">
+        <v>0.02017633058130741</v>
+      </c>
+      <c r="E29">
+        <v>0.1028466671705246</v>
+      </c>
+      <c r="F29">
+        <v>0.002207845449447632</v>
+      </c>
+      <c r="G29">
+        <v>0.001867753453552723</v>
+      </c>
+      <c r="H29">
+        <v>1.000430734224298</v>
+      </c>
+      <c r="I29">
+        <v>0.05232212543308418</v>
+      </c>
+      <c r="J29">
+        <v>0.1961787492036819</v>
+      </c>
+      <c r="K29">
+        <v>2.630521760957024E+28</v>
+      </c>
+      <c r="L29">
+        <v>5.886568069458008</v>
+      </c>
+      <c r="M29">
+        <v>11.22855567932129</v>
+      </c>
+      <c r="N29" t="s">
+        <v>156</v>
+      </c>
+      <c r="O29" t="s">
+        <v>216</v>
+      </c>
+      <c r="P29" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.09144417131097614</v>
+      </c>
+      <c r="D30">
+        <v>0.04919464513659477</v>
+      </c>
+      <c r="E30">
+        <v>0.2519838511943817</v>
+      </c>
+      <c r="F30">
+        <v>0.002044863766059279</v>
+      </c>
+      <c r="G30">
+        <v>0.001833320711739361</v>
+      </c>
+      <c r="H30">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I30">
+        <v>0.05793848196911786</v>
+      </c>
+      <c r="J30">
+        <v>0.1952293515205383</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>14.42263603210449</v>
+      </c>
+      <c r="M30">
+        <v>11.17421531677246</v>
+      </c>
+      <c r="N30" t="s">
+        <v>157</v>
+      </c>
+      <c r="O30" t="s">
+        <v>217</v>
+      </c>
+      <c r="P30" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.1808505765806045</v>
+      </c>
+      <c r="D31">
+        <v>0.09717556834220886</v>
+      </c>
+      <c r="E31">
+        <v>0.5040633678436279</v>
+      </c>
+      <c r="F31">
+        <v>0.002062921179458499</v>
+      </c>
+      <c r="G31">
+        <v>0.002127579413354397</v>
+      </c>
+      <c r="H31">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I31">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J31">
+        <v>0.1927844285964966</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>28.85074806213379</v>
+      </c>
+      <c r="M31">
+        <v>11.03427696228027</v>
+      </c>
+      <c r="N31" t="s">
+        <v>158</v>
+      </c>
+      <c r="O31" t="s">
+        <v>218</v>
+      </c>
+      <c r="P31" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0006263975633119301</v>
+      </c>
+      <c r="D32">
+        <v>-3.027561251656152E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003450005548074841</v>
+      </c>
+      <c r="F32">
+        <v>0.0007565276464447379</v>
+      </c>
+      <c r="G32">
+        <v>0.0007817870937287807</v>
+      </c>
+      <c r="H32">
+        <v>1.000432260354549</v>
+      </c>
+      <c r="I32">
+        <v>0.04905688252633342</v>
+      </c>
+      <c r="J32">
+        <v>-0.008775525726377964</v>
+      </c>
+      <c r="K32">
+        <v>-0.09443479776382446</v>
+      </c>
+      <c r="L32">
+        <v>0.1974657326936722</v>
+      </c>
+      <c r="M32">
+        <v>-0.5022790431976318</v>
+      </c>
+      <c r="N32" t="s">
+        <v>159</v>
+      </c>
+      <c r="O32" t="s">
+        <v>219</v>
+      </c>
+      <c r="P32" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0008301650738034819</v>
+      </c>
+      <c r="D33">
+        <v>0.0002184577024308965</v>
+      </c>
+      <c r="E33">
+        <v>0.004509167745709419</v>
+      </c>
+      <c r="F33">
+        <v>0.0009102345793507993</v>
+      </c>
+      <c r="G33">
+        <v>0.0008892063633538783</v>
+      </c>
+      <c r="H33">
+        <v>1.000614482267749</v>
+      </c>
+      <c r="I33">
+        <v>0.0490052272395416</v>
+      </c>
+      <c r="J33">
+        <v>0.04844745621085167</v>
+      </c>
+      <c r="K33">
+        <v>1.045746326446533</v>
+      </c>
+      <c r="L33">
+        <v>0.2580883204936981</v>
+      </c>
+      <c r="M33">
+        <v>2.772955656051636</v>
+      </c>
+      <c r="N33" t="s">
+        <v>160</v>
+      </c>
+      <c r="O33" t="s">
+        <v>220</v>
+      </c>
+      <c r="P33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.001031252072598944</v>
+      </c>
+      <c r="D34">
+        <v>0.0003506883804220706</v>
+      </c>
+      <c r="E34">
+        <v>0.005319388583302498</v>
+      </c>
+      <c r="F34">
+        <v>0.001050625811330974</v>
+      </c>
+      <c r="G34">
+        <v>0.00101689575240016</v>
+      </c>
+      <c r="H34">
+        <v>1.000736058055393</v>
+      </c>
+      <c r="I34">
+        <v>0.04902551424118454</v>
+      </c>
+      <c r="J34">
+        <v>0.0659264475107193</v>
+      </c>
+      <c r="K34">
+        <v>2.154205799102783</v>
+      </c>
+      <c r="L34">
+        <v>0.3044624030590057</v>
+      </c>
+      <c r="M34">
+        <v>3.773389339447021</v>
+      </c>
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+      <c r="O34" t="s">
+        <v>221</v>
+      </c>
+      <c r="P34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.002012579049550111</v>
+      </c>
+      <c r="D35">
+        <v>0.001107042306102812</v>
+      </c>
+      <c r="E35">
+        <v>0.01041335146874189</v>
+      </c>
+      <c r="F35">
+        <v>0.001525988220237195</v>
+      </c>
+      <c r="G35">
+        <v>0.001361714210361242</v>
+      </c>
+      <c r="H35">
+        <v>1.000797248392527</v>
+      </c>
+      <c r="I35">
+        <v>0.04911573605951108</v>
+      </c>
+      <c r="J35">
+        <v>0.1063098981976509</v>
+      </c>
+      <c r="K35">
+        <v>36.51881408691406</v>
+      </c>
+      <c r="L35">
+        <v>0.5960222482681274</v>
+      </c>
+      <c r="M35">
+        <v>6.084790706634521</v>
+      </c>
+      <c r="N35" t="s">
+        <v>162</v>
+      </c>
+      <c r="O35" t="s">
+        <v>222</v>
+      </c>
+      <c r="P35" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003907331305067199</v>
+      </c>
+      <c r="D36">
+        <v>0.002218406880274415</v>
+      </c>
+      <c r="E36">
+        <v>0.02082972228527069</v>
+      </c>
+      <c r="F36">
+        <v>0.002020739717409015</v>
+      </c>
+      <c r="G36">
+        <v>0.001695220242254436</v>
+      </c>
+      <c r="H36">
+        <v>1.000971086015187</v>
+      </c>
+      <c r="I36">
+        <v>0.04919054450908145</v>
+      </c>
+      <c r="J36">
+        <v>0.1065019890666008</v>
+      </c>
+      <c r="K36">
+        <v>1420.285522460938</v>
+      </c>
+      <c r="L36">
+        <v>1.192217350006104</v>
+      </c>
+      <c r="M36">
+        <v>6.095785140991211</v>
+      </c>
+      <c r="N36" t="s">
+        <v>163</v>
+      </c>
+      <c r="O36" t="s">
+        <v>223</v>
+      </c>
+      <c r="P36" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.00758189330101247</v>
+      </c>
+      <c r="D37">
+        <v>0.004226075951009989</v>
+      </c>
+      <c r="E37">
+        <v>0.04163368791341782</v>
+      </c>
+      <c r="F37">
+        <v>0.002406937070190907</v>
+      </c>
+      <c r="G37">
+        <v>0.001903114374727011</v>
+      </c>
+      <c r="H37">
+        <v>1.000799964809572</v>
+      </c>
+      <c r="I37">
+        <v>0.04929904084399824</v>
+      </c>
+      <c r="J37">
+        <v>0.1015061661601067</v>
+      </c>
+      <c r="K37">
+        <v>999982.1875</v>
+      </c>
+      <c r="L37">
+        <v>2.382960319519043</v>
+      </c>
+      <c r="M37">
+        <v>5.809842586517334</v>
+      </c>
+      <c r="N37" t="s">
+        <v>164</v>
+      </c>
+      <c r="O37" t="s">
+        <v>224</v>
+      </c>
+      <c r="P37" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01840766128723552</v>
+      </c>
+      <c r="D38">
+        <v>0.009969081729650497</v>
+      </c>
+      <c r="E38">
+        <v>0.10406294465065</v>
+      </c>
+      <c r="F38">
+        <v>0.002416939474642277</v>
+      </c>
+      <c r="G38">
+        <v>0.001940015936270356</v>
+      </c>
+      <c r="H38">
+        <v>1.000539486669615</v>
+      </c>
+      <c r="I38">
+        <v>0.05093661080767499</v>
+      </c>
+      <c r="J38">
+        <v>0.09579857438802719</v>
+      </c>
+      <c r="K38">
+        <v>129811653591040</v>
+      </c>
+      <c r="L38">
+        <v>5.956183433532715</v>
+      </c>
+      <c r="M38">
+        <v>5.483160972595215</v>
+      </c>
+      <c r="N38" t="s">
+        <v>165</v>
+      </c>
+      <c r="O38" t="s">
+        <v>225</v>
+      </c>
+      <c r="P38" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.03630095530172588</v>
+      </c>
+      <c r="D39">
+        <v>0.01934380456805229</v>
+      </c>
+      <c r="E39">
+        <v>0.2081583142280579</v>
+      </c>
+      <c r="F39">
+        <v>0.002182628028094769</v>
+      </c>
+      <c r="G39">
+        <v>0.001819668803364038</v>
+      </c>
+      <c r="H39">
+        <v>1.000376440248711</v>
+      </c>
+      <c r="I39">
+        <v>0.05243876900691057</v>
+      </c>
+      <c r="J39">
+        <v>0.09292832762002945</v>
+      </c>
+      <c r="K39">
+        <v>1.814013114815351E+27</v>
+      </c>
+      <c r="L39">
+        <v>11.91422271728516</v>
+      </c>
+      <c r="M39">
+        <v>5.318878173828125</v>
+      </c>
+      <c r="N39" t="s">
+        <v>166</v>
+      </c>
+      <c r="O39" t="s">
+        <v>226</v>
+      </c>
+      <c r="P39" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.08832395784475108</v>
+      </c>
+      <c r="D40">
+        <v>0.04666724428534508</v>
+      </c>
+      <c r="E40">
+        <v>0.5076159238815308</v>
+      </c>
+      <c r="F40">
+        <v>0.002040733816102147</v>
+      </c>
+      <c r="G40">
+        <v>0.00190776283852756</v>
+      </c>
+      <c r="H40">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I40">
+        <v>0.05780776923815894</v>
+      </c>
+      <c r="J40">
+        <v>0.09193415939807892</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>29.0540828704834</v>
+      </c>
+      <c r="M40">
+        <v>5.261975765228271</v>
+      </c>
+      <c r="N40" t="s">
+        <v>167</v>
+      </c>
+      <c r="O40" t="s">
+        <v>227</v>
+      </c>
+      <c r="P40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.1837000004695835</v>
+      </c>
+      <c r="D41">
+        <v>0.09666277468204498</v>
+      </c>
+      <c r="E41">
+        <v>1.118583202362061</v>
+      </c>
+      <c r="F41">
+        <v>0.002060698810964823</v>
+      </c>
+      <c r="G41">
+        <v>0.002147421473637223</v>
+      </c>
+      <c r="H41">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I41">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J41">
+        <v>0.0864153653383255</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>64.02362060546875</v>
+      </c>
+      <c r="M41">
+        <v>4.946100234985352</v>
+      </c>
+      <c r="N41" t="s">
+        <v>168</v>
+      </c>
+      <c r="O41" t="s">
+        <v>228</v>
+      </c>
+      <c r="P41" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0002580187551211472</v>
+      </c>
+      <c r="D42">
+        <v>1.854568654380273E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.001185433473438025</v>
+      </c>
+      <c r="F42">
+        <v>0.0008078700047917664</v>
+      </c>
+      <c r="G42">
+        <v>0.000818609434645623</v>
+      </c>
+      <c r="H42">
+        <v>1.000299521895406</v>
+      </c>
+      <c r="I42">
+        <v>0.04906424167400596</v>
+      </c>
+      <c r="J42">
+        <v>0.01564464531838894</v>
+      </c>
+      <c r="K42">
+        <v>0.06281602382659912</v>
+      </c>
+      <c r="L42">
+        <v>0.06784988939762115</v>
+      </c>
+      <c r="M42">
+        <v>0.8954424262046814</v>
+      </c>
+      <c r="N42" t="s">
+        <v>169</v>
+      </c>
+      <c r="O42" t="s">
+        <v>229</v>
+      </c>
+      <c r="P42" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.0003363929663916806</v>
+      </c>
+      <c r="D43">
+        <v>0.0001396689331158996</v>
+      </c>
+      <c r="E43">
+        <v>0.001492126961238682</v>
+      </c>
+      <c r="F43">
+        <v>0.0009828709298744798</v>
+      </c>
+      <c r="G43">
+        <v>0.0009656272595748305</v>
+      </c>
+      <c r="H43">
+        <v>1.000475780640616</v>
+      </c>
+      <c r="I43">
+        <v>0.04904951104779152</v>
+      </c>
+      <c r="J43">
+        <v>0.09360392391681671</v>
+      </c>
+      <c r="K43">
+        <v>0.5803854465484619</v>
+      </c>
+      <c r="L43">
+        <v>0.08540390431880951</v>
+      </c>
+      <c r="M43">
+        <v>5.357547283172607</v>
+      </c>
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43" t="s">
+        <v>230</v>
+      </c>
+      <c r="P43" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0004115991133958834</v>
+      </c>
+      <c r="D44">
+        <v>0.0002371746231801808</v>
+      </c>
+      <c r="E44">
+        <v>0.001788541791029274</v>
+      </c>
+      <c r="F44">
+        <v>0.001137116574682295</v>
+      </c>
+      <c r="G44">
+        <v>0.001110181678086519</v>
+      </c>
+      <c r="H44">
+        <v>1.000534290978563</v>
+      </c>
+      <c r="I44">
+        <v>0.04910373462848851</v>
+      </c>
+      <c r="J44">
+        <v>0.1326078176498413</v>
+      </c>
+      <c r="K44">
+        <v>1.175072193145752</v>
+      </c>
+      <c r="L44">
+        <v>0.1023696064949036</v>
+      </c>
+      <c r="M44">
+        <v>7.589987754821777</v>
+      </c>
+      <c r="N44" t="s">
+        <v>171</v>
+      </c>
+      <c r="O44" t="s">
+        <v>231</v>
+      </c>
+      <c r="P44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.0007567524844732706</v>
+      </c>
+      <c r="D45">
+        <v>0.0005605188780464232</v>
+      </c>
+      <c r="E45">
+        <v>0.003278410062193871</v>
+      </c>
+      <c r="F45">
+        <v>0.001655854051932693</v>
+      </c>
+      <c r="G45">
+        <v>0.00144325930159539</v>
+      </c>
+      <c r="H45">
+        <v>1.000697759880902</v>
+      </c>
+      <c r="I45">
+        <v>0.04920199157040205</v>
+      </c>
+      <c r="J45">
+        <v>0.1709727793931961</v>
+      </c>
+      <c r="K45">
+        <v>5.269871711730957</v>
+      </c>
+      <c r="L45">
+        <v>0.1876442283391953</v>
+      </c>
+      <c r="M45">
+        <v>9.785858154296875</v>
+      </c>
+      <c r="N45" t="s">
+        <v>172</v>
+      </c>
+      <c r="O45" t="s">
+        <v>232</v>
+      </c>
+      <c r="P45" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.001363480136512485</v>
+      </c>
+      <c r="D46">
+        <v>0.0009662466472946107</v>
+      </c>
+      <c r="E46">
+        <v>0.006370443385094404</v>
+      </c>
+      <c r="F46">
+        <v>0.002139471471309662</v>
+      </c>
+      <c r="G46">
+        <v>0.001775577897205949</v>
+      </c>
+      <c r="H46">
+        <v>1.000871814930138</v>
+      </c>
+      <c r="I46">
+        <v>0.04919568368041866</v>
+      </c>
+      <c r="J46">
+        <v>0.1516765207052231</v>
+      </c>
+      <c r="K46">
+        <v>22.65831184387207</v>
+      </c>
+      <c r="L46">
+        <v>0.3646209239959717</v>
+      </c>
+      <c r="M46">
+        <v>8.681410789489746</v>
+      </c>
+      <c r="N46" t="s">
+        <v>173</v>
+      </c>
+      <c r="O46" t="s">
+        <v>233</v>
+      </c>
+      <c r="P46" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.002467262666084011</v>
+      </c>
+      <c r="D47">
+        <v>0.001620566938072443</v>
+      </c>
+      <c r="E47">
+        <v>0.0126089071854949</v>
+      </c>
+      <c r="F47">
+        <v>0.002509930869564414</v>
+      </c>
+      <c r="G47">
+        <v>0.001957843545824289</v>
+      </c>
+      <c r="H47">
+        <v>1.000685163043858</v>
+      </c>
+      <c r="I47">
+        <v>0.04946337707553106</v>
+      </c>
+      <c r="J47">
+        <v>0.1285255700349808</v>
+      </c>
+      <c r="K47">
+        <v>200.2530059814453</v>
+      </c>
+      <c r="L47">
+        <v>0.7216878533363342</v>
+      </c>
+      <c r="M47">
+        <v>7.356334686279297</v>
+      </c>
+      <c r="N47" t="s">
+        <v>174</v>
+      </c>
+      <c r="O47" t="s">
+        <v>234</v>
+      </c>
+      <c r="P47" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.005552515833045777</v>
+      </c>
+      <c r="D48">
+        <v>0.003317453665658832</v>
+      </c>
+      <c r="E48">
+        <v>0.03124971874058247</v>
+      </c>
+      <c r="F48">
+        <v>0.002360476879402995</v>
+      </c>
+      <c r="G48">
+        <v>0.001908696605823934</v>
+      </c>
+      <c r="H48">
+        <v>1.000341440397789</v>
+      </c>
+      <c r="I48">
+        <v>0.05108098211774715</v>
+      </c>
+      <c r="J48">
+        <v>0.106159470975399</v>
+      </c>
+      <c r="K48">
+        <v>51536.328125</v>
+      </c>
+      <c r="L48">
+        <v>1.788619875907898</v>
+      </c>
+      <c r="M48">
+        <v>6.076180934906006</v>
+      </c>
+      <c r="N48" t="s">
+        <v>175</v>
+      </c>
+      <c r="O48" t="s">
+        <v>235</v>
+      </c>
+      <c r="P48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.01056224579266784</v>
+      </c>
+      <c r="D49">
+        <v>0.005985424853861332</v>
+      </c>
+      <c r="E49">
+        <v>0.0625506117939949</v>
+      </c>
+      <c r="F49">
+        <v>0.002140492899343371</v>
+      </c>
+      <c r="G49">
+        <v>0.001881160074844956</v>
+      </c>
+      <c r="H49">
+        <v>1.000313170229744</v>
+      </c>
+      <c r="I49">
+        <v>0.05260296083207476</v>
+      </c>
+      <c r="J49">
+        <v>0.0956893116235733</v>
+      </c>
+      <c r="K49">
+        <v>309248096</v>
+      </c>
+      <c r="L49">
+        <v>3.580168724060059</v>
+      </c>
+      <c r="M49">
+        <v>5.476907253265381</v>
+      </c>
+      <c r="N49" t="s">
+        <v>176</v>
+      </c>
+      <c r="O49" t="s">
+        <v>236</v>
+      </c>
+      <c r="P49" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.02556376657767822</v>
+      </c>
+      <c r="D50">
+        <v>0.01393579598516226</v>
+      </c>
+      <c r="E50">
+        <v>0.1611214727163315</v>
+      </c>
+      <c r="F50">
+        <v>0.002081347163766623</v>
+      </c>
+      <c r="G50">
+        <v>0.002125326544046402</v>
+      </c>
+      <c r="H50">
+        <v>1.000940909355842</v>
+      </c>
+      <c r="I50">
+        <v>0.05784162264752678</v>
+      </c>
+      <c r="J50">
+        <v>0.08649247884750366</v>
+      </c>
+      <c r="K50">
+        <v>4.900771814625509E+19</v>
+      </c>
+      <c r="L50">
+        <v>9.222004890441895</v>
+      </c>
+      <c r="M50">
+        <v>4.95051383972168</v>
+      </c>
+      <c r="N50" t="s">
+        <v>177</v>
+      </c>
+      <c r="O50" t="s">
+        <v>237</v>
+      </c>
+      <c r="P50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.05009107444268883</v>
+      </c>
+      <c r="D51">
+        <v>0.02699847519397736</v>
+      </c>
+      <c r="E51">
+        <v>0.3228775858879089</v>
+      </c>
+      <c r="F51">
+        <v>0.002132575493305922</v>
+      </c>
+      <c r="G51">
+        <v>0.002485503675416112</v>
+      </c>
+      <c r="H51">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I51">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J51">
+        <v>0.08361829817295074</v>
+      </c>
+      <c r="K51">
+        <v>7.993238298751033E+37</v>
+      </c>
+      <c r="L51">
+        <v>18.4803352355957</v>
+      </c>
+      <c r="M51">
+        <v>4.786006450653076</v>
+      </c>
+      <c r="N51" t="s">
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>238</v>
+      </c>
+      <c r="P51" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0001662472259284278</v>
+      </c>
+      <c r="D52">
+        <v>0.0002533363876864314</v>
+      </c>
+      <c r="E52">
+        <v>0.0007221880368888378</v>
+      </c>
+      <c r="F52">
+        <v>0.001064282492734492</v>
+      </c>
+      <c r="G52">
+        <v>0.001025633420795202</v>
+      </c>
+      <c r="H52">
+        <v>0.9996184236302168</v>
+      </c>
+      <c r="I52">
+        <v>0.04950012499406261</v>
+      </c>
+      <c r="J52">
+        <v>0.3507900536060333</v>
+      </c>
+      <c r="K52">
+        <v>1.292792081832886</v>
+      </c>
+      <c r="L52">
+        <v>0.04133540764451027</v>
+      </c>
+      <c r="M52">
+        <v>20.07794189453125</v>
+      </c>
+      <c r="N52" t="s">
+        <v>179</v>
+      </c>
+      <c r="O52" t="s">
+        <v>239</v>
+      </c>
+      <c r="P52" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002052396690130036</v>
+      </c>
+      <c r="D53">
+        <v>0.0003052731044590473</v>
+      </c>
+      <c r="E53">
+        <v>0.0007711445214226842</v>
+      </c>
+      <c r="F53">
+        <v>0.001254401751793921</v>
+      </c>
+      <c r="G53">
+        <v>0.001205331762321293</v>
+      </c>
+      <c r="H53">
+        <v>0.9999103956344916</v>
+      </c>
+      <c r="I53">
+        <v>0.04945975539251334</v>
+      </c>
+      <c r="J53">
+        <v>0.3958701491355896</v>
+      </c>
+      <c r="K53">
+        <v>1.718264818191528</v>
+      </c>
+      <c r="L53">
+        <v>0.04413750022649765</v>
+      </c>
+      <c r="M53">
+        <v>22.65816307067871</v>
+      </c>
+      <c r="N53" t="s">
+        <v>180</v>
+      </c>
+      <c r="O53" t="s">
+        <v>240</v>
+      </c>
+      <c r="P53" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0002393125683109491</v>
+      </c>
+      <c r="D54">
+        <v>0.0003456742269918323</v>
+      </c>
+      <c r="E54">
+        <v>0.0008048059535212815</v>
+      </c>
+      <c r="F54">
+        <v>0.001373047241941094</v>
+      </c>
+      <c r="G54">
+        <v>0.001286366954445839</v>
+      </c>
+      <c r="H54">
+        <v>1.000136945653601</v>
+      </c>
+      <c r="I54">
+        <v>0.04939518034853253</v>
+      </c>
+      <c r="J54">
+        <v>0.4295125007629395</v>
+      </c>
+      <c r="K54">
+        <v>2.102909564971924</v>
+      </c>
+      <c r="L54">
+        <v>0.04606415703892708</v>
+      </c>
+      <c r="M54">
+        <v>24.5837287902832</v>
+      </c>
+      <c r="N54" t="s">
+        <v>181</v>
+      </c>
+      <c r="O54" t="s">
+        <v>241</v>
+      </c>
+      <c r="P54" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.0003578668236321751</v>
+      </c>
+      <c r="D55">
+        <v>0.0004816377768293023</v>
+      </c>
+      <c r="E55">
+        <v>0.0009209293639287353</v>
+      </c>
+      <c r="F55">
+        <v>0.001750802039168775</v>
+      </c>
+      <c r="G55">
+        <v>0.001554734073579311</v>
+      </c>
+      <c r="H55">
+        <v>1.000633820684129</v>
+      </c>
+      <c r="I55">
+        <v>0.04910148309512233</v>
+      </c>
+      <c r="J55">
+        <v>0.5229910016059875</v>
+      </c>
+      <c r="K55">
+        <v>3.842154979705811</v>
+      </c>
+      <c r="L55">
+        <v>0.0527106374502182</v>
+      </c>
+      <c r="M55">
+        <v>29.93409729003906</v>
+      </c>
+      <c r="N55" t="s">
+        <v>182</v>
+      </c>
+      <c r="O55" t="s">
+        <v>242</v>
+      </c>
+      <c r="P55" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0004871414127433322</v>
+      </c>
+      <c r="D56">
+        <v>0.0006287465221248567</v>
+      </c>
+      <c r="E56">
+        <v>0.001105769188143313</v>
+      </c>
+      <c r="F56">
+        <v>0.002323186723515391</v>
+      </c>
+      <c r="G56">
+        <v>0.00190910988021642</v>
+      </c>
+      <c r="H56">
+        <v>1.000558950478084</v>
+      </c>
+      <c r="I56">
+        <v>0.04961640493684114</v>
+      </c>
+      <c r="J56">
+        <v>0.5686056017875671</v>
+      </c>
+      <c r="K56">
+        <v>6.838175296783447</v>
+      </c>
+      <c r="L56">
+        <v>0.06329019367694855</v>
+      </c>
+      <c r="M56">
+        <v>32.5449104309082</v>
+      </c>
+      <c r="N56" t="s">
+        <v>183</v>
+      </c>
+      <c r="O56" t="s">
+        <v>243</v>
+      </c>
+      <c r="P56" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0006275245932933209</v>
+      </c>
+      <c r="D57">
+        <v>0.0007855389849282801</v>
+      </c>
+      <c r="E57">
+        <v>0.001470794901251793</v>
+      </c>
+      <c r="F57">
+        <v>0.002486313227564096</v>
+      </c>
+      <c r="G57">
+        <v>0.002021294087171555</v>
+      </c>
+      <c r="H57">
+        <v>1.000194683101097</v>
+      </c>
+      <c r="I57">
+        <v>0.04993685538484502</v>
+      </c>
+      <c r="J57">
+        <v>0.5340914726257324</v>
+      </c>
+      <c r="K57">
+        <v>12.09957695007324</v>
+      </c>
+      <c r="L57">
+        <v>0.08418293297290802</v>
+      </c>
+      <c r="M57">
+        <v>30.5694465637207</v>
+      </c>
+      <c r="N57" t="s">
+        <v>184</v>
+      </c>
+      <c r="O57" t="s">
+        <v>244</v>
+      </c>
+      <c r="P57" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.0008477787583734509</v>
+      </c>
+      <c r="D58">
+        <v>0.0009955440182238817</v>
+      </c>
+      <c r="E58">
+        <v>0.00236724317073822</v>
+      </c>
+      <c r="F58">
+        <v>0.00227425224147737</v>
+      </c>
+      <c r="G58">
+        <v>0.00206473539583385</v>
+      </c>
+      <c r="H58">
+        <v>0.9999895811482418</v>
+      </c>
+      <c r="I58">
+        <v>0.05213928436574763</v>
+      </c>
+      <c r="J58">
+        <v>0.4205499589443207</v>
+      </c>
+      <c r="K58">
+        <v>25.04148101806641</v>
+      </c>
+      <c r="L58">
+        <v>0.135492354631424</v>
+      </c>
+      <c r="M58">
+        <v>24.07074546813965</v>
+      </c>
+      <c r="N58" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" t="s">
+        <v>245</v>
+      </c>
+      <c r="P58" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.001036323134654023</v>
+      </c>
+      <c r="D59">
+        <v>0.001111504388973117</v>
+      </c>
+      <c r="E59">
+        <v>0.003481929423287511</v>
+      </c>
+      <c r="F59">
+        <v>0.002126416657119989</v>
+      </c>
+      <c r="G59">
+        <v>0.002339457627385855</v>
+      </c>
+      <c r="H59">
+        <v>0.9996028205076266</v>
+      </c>
+      <c r="I59">
+        <v>0.05468516144245333</v>
+      </c>
+      <c r="J59">
+        <v>0.3192208409309387</v>
+      </c>
+      <c r="K59">
+        <v>37.06427383422852</v>
+      </c>
+      <c r="L59">
+        <v>0.199292927980423</v>
+      </c>
+      <c r="M59">
+        <v>18.27103614807129</v>
+      </c>
+      <c r="N59" t="s">
+        <v>186</v>
+      </c>
+      <c r="O59" t="s">
+        <v>246</v>
+      </c>
+      <c r="P59" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001292448051987435</v>
+      </c>
+      <c r="D60">
+        <v>0.001341164577752352</v>
+      </c>
+      <c r="E60">
+        <v>0.005689751822501421</v>
+      </c>
+      <c r="F60">
+        <v>0.002134056529030204</v>
+      </c>
+      <c r="G60">
+        <v>0.002193818800151348</v>
+      </c>
+      <c r="H60">
+        <v>1.0002779146598</v>
+      </c>
+      <c r="I60">
+        <v>0.05974928639118577</v>
+      </c>
+      <c r="J60">
+        <v>0.2357158362865448</v>
+      </c>
+      <c r="K60">
+        <v>79.71342468261719</v>
+      </c>
+      <c r="L60">
+        <v>0.3256606459617615</v>
+      </c>
+      <c r="M60">
+        <v>13.49151420593262</v>
+      </c>
+      <c r="N60" t="s">
+        <v>187</v>
+      </c>
+      <c r="O60" t="s">
+        <v>247</v>
+      </c>
+      <c r="P60" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001470189732499061</v>
+      </c>
+      <c r="D61">
+        <v>0.001587220234796405</v>
+      </c>
+      <c r="E61">
+        <v>0.007910348474979401</v>
+      </c>
+      <c r="F61">
+        <v>0.002211001003161073</v>
+      </c>
+      <c r="G61">
+        <v>0.002577970968559384</v>
+      </c>
+      <c r="H61">
+        <v>1.00186658506732</v>
+      </c>
+      <c r="I61">
+        <v>0.06811389335013521</v>
+      </c>
+      <c r="J61">
+        <v>0.2006511092185974</v>
+      </c>
+      <c r="K61">
+        <v>179.5088043212891</v>
+      </c>
+      <c r="L61">
+        <v>0.4527594745159149</v>
+      </c>
+      <c r="M61">
+        <v>11.48453712463379</v>
+      </c>
+      <c r="N61" t="s">
+        <v>188</v>
+      </c>
+      <c r="O61" t="s">
+        <v>248</v>
+      </c>
+      <c r="P61" t="s">
+        <v>308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:16">
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2">
+        <v>0.001081786487482666</v>
+      </c>
+      <c r="D2">
+        <v>-0.003209168324247003</v>
+      </c>
+      <c r="E2">
+        <v>0.05505451560020447</v>
+      </c>
+      <c r="F2">
+        <v>0.0007220860570669174</v>
+      </c>
+      <c r="G2">
+        <v>0.0007811211398802698</v>
+      </c>
+      <c r="H2">
+        <v>1.000557113172389</v>
+      </c>
+      <c r="I2">
+        <v>0.04896146290954414</v>
+      </c>
+      <c r="J2">
+        <v>-0.05829073861241341</v>
+      </c>
+      <c r="K2">
+        <v>-0.9999732971191406</v>
+      </c>
+      <c r="L2">
+        <v>3.151119470596313</v>
+      </c>
+      <c r="M2">
+        <v>-3.336349248886108</v>
+      </c>
+      <c r="N2" t="s">
+        <v>309</v>
+      </c>
+      <c r="O2" t="s">
+        <v>369</v>
+      </c>
+      <c r="P2" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3">
+        <v>0.001438610467043554</v>
+      </c>
+      <c r="D3">
+        <v>-0.00441643875092268</v>
+      </c>
+      <c r="E3">
+        <v>0.0849117785692215</v>
+      </c>
+      <c r="F3">
+        <v>0.0008227601647377014</v>
+      </c>
+      <c r="G3">
+        <v>0.0008149937493726611</v>
+      </c>
+      <c r="H3">
+        <v>1.000816042165218</v>
+      </c>
+      <c r="I3">
+        <v>0.04890325490626187</v>
+      </c>
+      <c r="J3">
+        <v>-0.05201208591461182</v>
+      </c>
+      <c r="K3">
+        <v>-0.9999995231628418</v>
+      </c>
+      <c r="L3">
+        <v>4.860040187835693</v>
+      </c>
+      <c r="M3">
+        <v>-2.976982116699219</v>
+      </c>
+      <c r="N3" t="s">
+        <v>310</v>
+      </c>
+      <c r="O3" t="s">
+        <v>370</v>
+      </c>
+      <c r="P3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4">
+        <v>0.001794543670766371</v>
+      </c>
+      <c r="D4">
+        <v>-0.001610947889275849</v>
+      </c>
+      <c r="E4">
+        <v>0.0498129278421402</v>
+      </c>
+      <c r="F4">
+        <v>0.0009145466610789299</v>
+      </c>
+      <c r="G4">
+        <v>0.000909551337826997</v>
+      </c>
+      <c r="H4">
+        <v>1.000956177952619</v>
+      </c>
+      <c r="I4">
+        <v>0.04893594156717705</v>
+      </c>
+      <c r="J4">
+        <v>-0.03233995661139488</v>
+      </c>
+      <c r="K4">
+        <v>-0.9949160814285278</v>
+      </c>
+      <c r="L4">
+        <v>2.851110219955444</v>
+      </c>
+      <c r="M4">
+        <v>-1.85102105140686</v>
+      </c>
+      <c r="N4" t="s">
+        <v>311</v>
+      </c>
+      <c r="O4" t="s">
+        <v>371</v>
+      </c>
+      <c r="P4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5">
+        <v>0.003560013682120057</v>
+      </c>
+      <c r="D5">
+        <v>-0.0008181389421224594</v>
+      </c>
+      <c r="E5">
+        <v>0.06694034487009048</v>
+      </c>
+      <c r="F5">
+        <v>0.00131190987303853</v>
+      </c>
+      <c r="G5">
+        <v>0.001256113057024777</v>
+      </c>
+      <c r="H5">
+        <v>1.00111229330266</v>
+      </c>
+      <c r="I5">
+        <v>0.04897488288848205</v>
+      </c>
+      <c r="J5">
+        <v>-0.01222191099077463</v>
+      </c>
+      <c r="K5">
+        <v>-0.9315260648727417</v>
+      </c>
+      <c r="L5">
+        <v>3.831421136856079</v>
+      </c>
+      <c r="M5">
+        <v>-0.6995375752449036</v>
+      </c>
+      <c r="N5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O5" t="s">
+        <v>372</v>
+      </c>
+      <c r="P5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6">
+        <v>0</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6">
+        <v>0.007041805938121605</v>
+      </c>
+      <c r="D6">
+        <v>0.003614481305703521</v>
+      </c>
+      <c r="E6">
+        <v>0.01974936760962009</v>
+      </c>
+      <c r="F6">
+        <v>0.001801613485440612</v>
+      </c>
+      <c r="G6">
+        <v>0.001550439861603081</v>
+      </c>
+      <c r="H6">
+        <v>1.001020761835894</v>
+      </c>
+      <c r="I6">
+        <v>0.04921832363902825</v>
+      </c>
+      <c r="J6">
+        <v>0.1830175668001175</v>
+      </c>
+      <c r="K6">
+        <v>135876.765625</v>
+      </c>
+      <c r="L6">
+        <v>1.13038170337677</v>
+      </c>
+      <c r="M6">
+        <v>10.47525787353516</v>
+      </c>
+      <c r="N6" t="s">
+        <v>313</v>
+      </c>
+      <c r="O6" t="s">
+        <v>373</v>
+      </c>
+      <c r="P6" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>0.01392654329019912</v>
+      </c>
+      <c r="D7">
+        <v>0.007256045006215572</v>
+      </c>
+      <c r="E7">
+        <v>0.03872774541378021</v>
+      </c>
+      <c r="F7">
+        <v>0.002161666285246611</v>
+      </c>
+      <c r="G7">
+        <v>0.001768713817000389</v>
+      </c>
+      <c r="H7">
+        <v>1.000919761005615</v>
+      </c>
+      <c r="I7">
+        <v>0.04926414413749837</v>
+      </c>
+      <c r="J7">
+        <v>0.1873603761196136</v>
+      </c>
+      <c r="K7">
+        <v>19330150400</v>
+      </c>
+      <c r="L7">
+        <v>2.216634750366211</v>
+      </c>
+      <c r="M7">
+        <v>10.7238245010376</v>
+      </c>
+      <c r="N7" t="s">
+        <v>314</v>
+      </c>
+      <c r="O7" t="s">
+        <v>374</v>
+      </c>
+      <c r="P7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8">
+        <v>0.0343227994678451</v>
+      </c>
+      <c r="D8">
+        <v>0.01760995574295521</v>
+      </c>
+      <c r="E8">
+        <v>0.09200668334960938</v>
+      </c>
+      <c r="F8">
+        <v>0.002355757635086775</v>
+      </c>
+      <c r="G8">
+        <v>0.001872617402113974</v>
+      </c>
+      <c r="H8">
+        <v>1.000589091230315</v>
+      </c>
+      <c r="I8">
+        <v>0.05083449506969839</v>
+      </c>
+      <c r="J8">
+        <v>0.1913986653089523</v>
+      </c>
+      <c r="K8">
+        <v>6.862634976042236E+24</v>
+      </c>
+      <c r="L8">
+        <v>5.26612663269043</v>
+      </c>
+      <c r="M8">
+        <v>10.95496082305908</v>
+      </c>
+      <c r="N8" t="s">
+        <v>315</v>
+      </c>
+      <c r="O8" t="s">
+        <v>375</v>
+      </c>
+      <c r="P8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9">
+        <v>0.06812078169428451</v>
+      </c>
+      <c r="D9">
+        <v>0.0348602756857872</v>
+      </c>
+      <c r="E9">
+        <v>0.1847865134477615</v>
+      </c>
+      <c r="F9">
+        <v>0.002237043343484402</v>
+      </c>
+      <c r="G9">
+        <v>0.001820900826714933</v>
+      </c>
+      <c r="H9">
+        <v>1.000403181197968</v>
+      </c>
+      <c r="I9">
+        <v>0.05244348947302026</v>
+      </c>
+      <c r="J9">
+        <v>0.1886516213417053</v>
+      </c>
+      <c r="K9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L9">
+        <v>10.57650566101074</v>
+      </c>
+      <c r="M9">
+        <v>10.79773044586182</v>
+      </c>
+      <c r="N9" t="s">
+        <v>316</v>
+      </c>
+      <c r="O9" t="s">
+        <v>376</v>
+      </c>
+      <c r="P9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10">
+        <v>0.170100051901817</v>
+      </c>
+      <c r="D10">
+        <v>0.08795516937971115</v>
+      </c>
+      <c r="E10">
+        <v>0.4981154799461365</v>
+      </c>
+      <c r="F10">
+        <v>0.00207999162375927</v>
+      </c>
+      <c r="G10">
+        <v>0.001863814075477421</v>
+      </c>
+      <c r="H10">
+        <v>1.000993608934245</v>
+      </c>
+      <c r="I10">
+        <v>0.05787263100092598</v>
+      </c>
+      <c r="J10">
+        <v>0.1765758544206619</v>
+      </c>
+      <c r="K10" t="s">
+        <v>128</v>
+      </c>
+      <c r="L10">
+        <v>28.51031303405762</v>
+      </c>
+      <c r="M10">
+        <v>10.10655784606934</v>
+      </c>
+      <c r="N10" t="s">
+        <v>317</v>
+      </c>
+      <c r="O10" t="s">
+        <v>377</v>
+      </c>
+      <c r="P10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11">
+        <v>0.3325572081232822</v>
+      </c>
+      <c r="D11">
+        <v>0.1747188419103622</v>
+      </c>
+      <c r="E11">
+        <v>0.994087278842926</v>
+      </c>
+      <c r="F11">
+        <v>0.00202989368699491</v>
+      </c>
+      <c r="G11">
+        <v>0.002066181739792228</v>
+      </c>
+      <c r="H11">
+        <v>1.002172582619339</v>
+      </c>
+      <c r="I11">
+        <v>0.06754014983666096</v>
+      </c>
+      <c r="J11">
+        <v>0.1757580488920212</v>
+      </c>
+      <c r="K11" t="s">
+        <v>128</v>
+      </c>
+      <c r="L11">
+        <v>56.89793014526367</v>
+      </c>
+      <c r="M11">
+        <v>10.05974960327148</v>
+      </c>
+      <c r="N11" t="s">
+        <v>318</v>
+      </c>
+      <c r="O11" t="s">
+        <v>378</v>
+      </c>
+      <c r="P11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12">
+        <v>0.001336917171209844</v>
+      </c>
+      <c r="D12">
+        <v>-0.0002902563137467951</v>
+      </c>
+      <c r="E12">
+        <v>0.0104484036564827</v>
+      </c>
+      <c r="F12">
+        <v>0.0007255234522745013</v>
+      </c>
+      <c r="G12">
+        <v>0.0007792959804646671</v>
+      </c>
+      <c r="H12">
+        <v>1.00055293727758</v>
+      </c>
+      <c r="I12">
+        <v>0.04894785297129705</v>
+      </c>
+      <c r="J12">
+        <v>-0.0277799665927887</v>
+      </c>
+      <c r="K12">
+        <v>-0.6136755347251892</v>
+      </c>
+      <c r="L12">
+        <v>0.5980284810066223</v>
+      </c>
+      <c r="M12">
+        <v>-1.590023875236511</v>
+      </c>
+      <c r="N12" t="s">
+        <v>319</v>
+      </c>
+      <c r="O12" t="s">
+        <v>379</v>
+      </c>
+      <c r="P12" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13">
+        <v>0.001778950545691277</v>
+      </c>
+      <c r="D13">
+        <v>0.0001945183321367949</v>
+      </c>
+      <c r="E13">
+        <v>0.01222601439803839</v>
+      </c>
+      <c r="F13">
+        <v>0.0008439474040642381</v>
+      </c>
+      <c r="G13">
+        <v>0.0008422087412327528</v>
+      </c>
+      <c r="H13">
+        <v>1.000801366583584</v>
+      </c>
+      <c r="I13">
+        <v>0.04889407328984739</v>
+      </c>
+      <c r="J13">
+        <v>0.0159101989120245</v>
+      </c>
+      <c r="K13">
+        <v>0.8913339376449585</v>
+      </c>
+      <c r="L13">
+        <v>0.6997724771499634</v>
+      </c>
+      <c r="M13">
+        <v>0.9106417298316956</v>
+      </c>
+      <c r="N13" t="s">
+        <v>320</v>
+      </c>
+      <c r="O13" t="s">
+        <v>380</v>
+      </c>
+      <c r="P13" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14">
+        <v>0.002219096740657559</v>
+      </c>
+      <c r="D14">
+        <v>0.0008047814480960369</v>
+      </c>
+      <c r="E14">
+        <v>0.01433415338397026</v>
+      </c>
+      <c r="F14">
+        <v>0.0009485309710726142</v>
+      </c>
+      <c r="G14">
+        <v>0.000931467569898814</v>
+      </c>
+      <c r="H14">
+        <v>1.000922766898597</v>
+      </c>
+      <c r="I14">
+        <v>0.04891361193308997</v>
+      </c>
+      <c r="J14">
+        <v>0.05614433065056801</v>
+      </c>
+      <c r="K14">
+        <v>12.94896411895752</v>
+      </c>
+      <c r="L14">
+        <v>0.8204346299171448</v>
+      </c>
+      <c r="M14">
+        <v>3.213496685028076</v>
+      </c>
+      <c r="N14" t="s">
+        <v>321</v>
+      </c>
+      <c r="O14" t="s">
+        <v>381</v>
+      </c>
+      <c r="P14" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15">
+        <v>0.004406622943597144</v>
+      </c>
+      <c r="D15">
+        <v>0.002824706491082907</v>
+      </c>
+      <c r="E15">
+        <v>0.03423083946108818</v>
+      </c>
+      <c r="F15">
+        <v>0.00137016037479043</v>
+      </c>
+      <c r="G15">
+        <v>0.001291464432142675</v>
+      </c>
+      <c r="H15">
+        <v>1.001023292779322</v>
+      </c>
+      <c r="I15">
+        <v>0.04901421118178486</v>
+      </c>
+      <c r="J15">
+        <v>0.08251934498548508</v>
+      </c>
+      <c r="K15">
+        <v>10305.7578125</v>
+      </c>
+      <c r="L15">
+        <v>1.959248304367065</v>
+      </c>
+      <c r="M15">
+        <v>4.723106384277344</v>
+      </c>
+      <c r="N15" t="s">
+        <v>322</v>
+      </c>
+      <c r="O15" t="s">
+        <v>382</v>
+      </c>
+      <c r="P15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16">
+        <v>0.008726216862801877</v>
+      </c>
+      <c r="D16">
+        <v>0.005086246412247419</v>
+      </c>
+      <c r="E16">
+        <v>0.04354469478130341</v>
+      </c>
+      <c r="F16">
+        <v>0.001853605965152383</v>
+      </c>
+      <c r="G16">
+        <v>0.001587207312695682</v>
+      </c>
+      <c r="H16">
+        <v>1.001008401872038</v>
+      </c>
+      <c r="I16">
+        <v>0.04918327422992472</v>
+      </c>
+      <c r="J16">
+        <v>0.11680518835783</v>
+      </c>
+      <c r="K16">
+        <v>16526820</v>
+      </c>
+      <c r="L16">
+        <v>2.492339372634888</v>
+      </c>
+      <c r="M16">
+        <v>6.685502529144287</v>
+      </c>
+      <c r="N16" t="s">
+        <v>323</v>
+      </c>
+      <c r="O16" t="s">
+        <v>383</v>
+      </c>
+      <c r="P16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17">
+        <v>0.01725164847415456</v>
+      </c>
+      <c r="D17">
+        <v>0.009906371124088764</v>
+      </c>
+      <c r="E17">
+        <v>0.08260323852300644</v>
+      </c>
+      <c r="F17">
+        <v>0.002234248444437981</v>
+      </c>
+      <c r="G17">
+        <v>0.001817291369661689</v>
+      </c>
+      <c r="H17">
+        <v>1.000875867626674</v>
+      </c>
+      <c r="I17">
+        <v>0.04930794606555218</v>
+      </c>
+      <c r="J17">
+        <v>0.1199271529912949</v>
+      </c>
+      <c r="K17">
+        <v>105920344358912</v>
+      </c>
+      <c r="L17">
+        <v>4.727908134460449</v>
+      </c>
+      <c r="M17">
+        <v>6.864192485809326</v>
+      </c>
+      <c r="N17" t="s">
+        <v>324</v>
+      </c>
+      <c r="O17" t="s">
+        <v>384</v>
+      </c>
+      <c r="P17" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
+      <c r="A18">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18">
+        <v>0.04269327043502681</v>
+      </c>
+      <c r="D18">
+        <v>0.02411847747862339</v>
+      </c>
+      <c r="E18">
+        <v>0.2029885947704315</v>
+      </c>
+      <c r="F18">
+        <v>0.002387812593951821</v>
+      </c>
+      <c r="G18">
+        <v>0.001889336039312184</v>
+      </c>
+      <c r="H18">
+        <v>1.000564594161063</v>
+      </c>
+      <c r="I18">
+        <v>0.0509414726745562</v>
+      </c>
+      <c r="J18">
+        <v>0.1188169121742249</v>
+      </c>
+      <c r="K18">
+        <v>8.075815117791773E+33</v>
+      </c>
+      <c r="L18">
+        <v>11.61832618713379</v>
+      </c>
+      <c r="M18">
+        <v>6.800646305084229</v>
+      </c>
+      <c r="N18" t="s">
+        <v>325</v>
+      </c>
+      <c r="O18" t="s">
+        <v>385</v>
+      </c>
+      <c r="P18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
+      <c r="A19">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C19">
+        <v>0.08418466847197584</v>
+      </c>
+      <c r="D19">
+        <v>0.04939908906817436</v>
+      </c>
+      <c r="E19">
+        <v>0.4570958614349365</v>
+      </c>
+      <c r="F19">
+        <v>0.002217968460172415</v>
+      </c>
+      <c r="G19">
+        <v>0.001825356972403824</v>
+      </c>
+      <c r="H19">
+        <v>1.000349831765927</v>
+      </c>
+      <c r="I19">
+        <v>0.0524422717036855</v>
+      </c>
+      <c r="J19">
+        <v>0.1080716177821159</v>
+      </c>
+      <c r="K19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19">
+        <v>26.16249847412109</v>
+      </c>
+      <c r="M19">
+        <v>6.185625076293945</v>
+      </c>
+      <c r="N19" t="s">
+        <v>326</v>
+      </c>
+      <c r="O19" t="s">
+        <v>386</v>
+      </c>
+      <c r="P19" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
+      <c r="A20">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>0.2112472697835106</v>
+      </c>
+      <c r="D20">
+        <v>0.1295772045850754</v>
+      </c>
+      <c r="E20">
+        <v>1.308696389198303</v>
+      </c>
+      <c r="F20">
+        <v>0.002055155346170068</v>
+      </c>
+      <c r="G20">
+        <v>0.001789074274711311</v>
+      </c>
+      <c r="H20">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I20">
+        <v>0.05806890046728418</v>
+      </c>
+      <c r="J20">
+        <v>0.09901242703199387</v>
+      </c>
+      <c r="K20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L20">
+        <v>74.90500640869141</v>
+      </c>
+      <c r="M20">
+        <v>5.667109966278076</v>
+      </c>
+      <c r="N20" t="s">
+        <v>327</v>
+      </c>
+      <c r="O20" t="s">
+        <v>387</v>
+      </c>
+      <c r="P20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
+      <c r="A21">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21">
+        <v>0.4081338326073733</v>
+      </c>
+      <c r="D21">
+        <v>0.2356650978326797</v>
+      </c>
+      <c r="E21">
+        <v>2.067750215530396</v>
+      </c>
+      <c r="F21">
+        <v>0.002051230985671282</v>
+      </c>
+      <c r="G21">
+        <v>0.00201975111849606</v>
+      </c>
+      <c r="H21">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I21">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J21">
+        <v>0.1139717474579811</v>
+      </c>
+      <c r="K21" t="s">
+        <v>128</v>
+      </c>
+      <c r="L21">
+        <v>118.3504791259766</v>
+      </c>
+      <c r="M21">
+        <v>6.523326873779297</v>
+      </c>
+      <c r="N21" t="s">
+        <v>328</v>
+      </c>
+      <c r="O21" t="s">
+        <v>388</v>
+      </c>
+      <c r="P21" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
+      <c r="A22">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22">
+        <v>0.0006156350990521457</v>
+      </c>
+      <c r="D22">
+        <v>-0.0003792000934481621</v>
+      </c>
+      <c r="E22">
+        <v>0.002029274590313435</v>
+      </c>
+      <c r="F22">
+        <v>0.0007443950744345784</v>
+      </c>
+      <c r="G22">
+        <v>0.0007792320102453232</v>
+      </c>
+      <c r="H22">
+        <v>1.000490136852817</v>
+      </c>
+      <c r="I22">
+        <v>0.04900054839207681</v>
+      </c>
+      <c r="J22">
+        <v>-0.1868648529052734</v>
+      </c>
+      <c r="K22">
+        <v>-0.7113413214683533</v>
+      </c>
+      <c r="L22">
+        <v>0.1161482706665993</v>
+      </c>
+      <c r="M22">
+        <v>-10.69546222686768</v>
+      </c>
+      <c r="N22" t="s">
+        <v>329</v>
+      </c>
+      <c r="O22" t="s">
+        <v>389</v>
+      </c>
+      <c r="P22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
+      <c r="A23">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23">
+        <v>0.0008169521222688851</v>
+      </c>
+      <c r="D23">
+        <v>-8.240219176514074E-05</v>
+      </c>
+      <c r="E23">
+        <v>0.002523471601307392</v>
+      </c>
+      <c r="F23">
+        <v>0.0008644938352517784</v>
+      </c>
+      <c r="G23">
+        <v>0.0008580878493376076</v>
+      </c>
+      <c r="H23">
+        <v>1.000721907677112</v>
+      </c>
+      <c r="I23">
+        <v>0.04891877802676723</v>
+      </c>
+      <c r="J23">
+        <v>-0.0326542966067791</v>
+      </c>
+      <c r="K23">
+        <v>-0.2365190386772156</v>
+      </c>
+      <c r="L23">
+        <v>0.1444343030452728</v>
+      </c>
+      <c r="M23">
+        <v>-1.869012832641602</v>
+      </c>
+      <c r="N23" t="s">
+        <v>330</v>
+      </c>
+      <c r="O23" t="s">
+        <v>390</v>
+      </c>
+      <c r="P23" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
+      <c r="A24">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24">
+        <v>0.001016223203816223</v>
+      </c>
+      <c r="D24">
+        <v>0.0001228088513016701</v>
+      </c>
+      <c r="E24">
+        <v>0.003078268375247717</v>
+      </c>
+      <c r="F24">
+        <v>0.0009851476643234491</v>
+      </c>
+      <c r="G24">
+        <v>0.0009614878217689693</v>
+      </c>
+      <c r="H24">
+        <v>1.000859443131074</v>
+      </c>
+      <c r="I24">
+        <v>0.04894446259685714</v>
+      </c>
+      <c r="J24">
+        <v>0.0398954339325428</v>
+      </c>
+      <c r="K24">
+        <v>0.4951415061950684</v>
+      </c>
+      <c r="L24">
+        <v>0.1761888563632965</v>
+      </c>
+      <c r="M24">
+        <v>2.283468961715698</v>
+      </c>
+      <c r="N24" t="s">
+        <v>331</v>
+      </c>
+      <c r="O24" t="s">
+        <v>391</v>
+      </c>
+      <c r="P24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>0.001993455775382883</v>
+      </c>
+      <c r="D25">
+        <v>0.0009865000611171126</v>
+      </c>
+      <c r="E25">
+        <v>0.005126030184328556</v>
+      </c>
+      <c r="F25">
+        <v>0.001432523131370544</v>
+      </c>
+      <c r="G25">
+        <v>0.001329980092123151</v>
+      </c>
+      <c r="H25">
+        <v>1.000953843890703</v>
+      </c>
+      <c r="I25">
+        <v>0.0490920872196858</v>
+      </c>
+      <c r="J25">
+        <v>0.1924491375684738</v>
+      </c>
+      <c r="K25">
+        <v>24.28066444396973</v>
+      </c>
+      <c r="L25">
+        <v>0.2933952510356903</v>
+      </c>
+      <c r="M25">
+        <v>11.01508617401123</v>
+      </c>
+      <c r="N25" t="s">
+        <v>332</v>
+      </c>
+      <c r="O25" t="s">
+        <v>392</v>
+      </c>
+      <c r="P25" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>93</v>
+      </c>
+      <c r="C26">
+        <v>0.0038863565795664</v>
+      </c>
+      <c r="D26">
+        <v>0.002136343624442816</v>
+      </c>
+      <c r="E26">
+        <v>0.01001446042209864</v>
+      </c>
+      <c r="F26">
+        <v>0.001928059267811477</v>
+      </c>
+      <c r="G26">
+        <v>0.001640524715185165</v>
+      </c>
+      <c r="H26">
+        <v>1.00096962163241</v>
+      </c>
+      <c r="I26">
+        <v>0.04921263132038384</v>
+      </c>
+      <c r="J26">
+        <v>0.2133258879184723</v>
+      </c>
+      <c r="K26">
+        <v>1086.04296875</v>
+      </c>
+      <c r="L26">
+        <v>0.5731911659240723</v>
+      </c>
+      <c r="M26">
+        <v>12.20999526977539</v>
+      </c>
+      <c r="N26" t="s">
+        <v>333</v>
+      </c>
+      <c r="O26" t="s">
+        <v>393</v>
+      </c>
+      <c r="P26" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27">
+        <v>0.007566825932234753</v>
+      </c>
+      <c r="D27">
+        <v>0.004155073780566454</v>
+      </c>
+      <c r="E27">
+        <v>0.0198802575469017</v>
+      </c>
+      <c r="F27">
+        <v>0.002322975778952241</v>
+      </c>
+      <c r="G27">
+        <v>0.001870693173259497</v>
+      </c>
+      <c r="H27">
+        <v>1.000841551836483</v>
+      </c>
+      <c r="I27">
+        <v>0.04930098523582576</v>
+      </c>
+      <c r="J27">
+        <v>0.2090050280094147</v>
+      </c>
+      <c r="K27">
+        <v>793102.8125</v>
+      </c>
+      <c r="L27">
+        <v>1.137873411178589</v>
+      </c>
+      <c r="M27">
+        <v>11.96268558502197</v>
+      </c>
+      <c r="N27" t="s">
+        <v>334</v>
+      </c>
+      <c r="O27" t="s">
+        <v>394</v>
+      </c>
+      <c r="P27" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28">
+        <v>0.01841260663994244</v>
+      </c>
+      <c r="D28">
+        <v>0.009899760596454144</v>
+      </c>
+      <c r="E28">
+        <v>0.0493512749671936</v>
+      </c>
+      <c r="F28">
+        <v>0.002413787879049778</v>
+      </c>
+      <c r="G28">
+        <v>0.001925164135172963</v>
+      </c>
+      <c r="H28">
+        <v>1.000537237503253</v>
+      </c>
+      <c r="I28">
+        <v>0.05098689485551912</v>
+      </c>
+      <c r="J28">
+        <v>0.2005978673696518</v>
+      </c>
+      <c r="K28">
+        <v>103651267837952</v>
+      </c>
+      <c r="L28">
+        <v>2.824687004089355</v>
+      </c>
+      <c r="M28">
+        <v>11.48149013519287</v>
+      </c>
+      <c r="N28" t="s">
+        <v>335</v>
+      </c>
+      <c r="O28" t="s">
+        <v>395</v>
+      </c>
+      <c r="P28" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29">
+        <v>0.03631594290304519</v>
+      </c>
+      <c r="D29">
+        <v>0.01935631223022938</v>
+      </c>
+      <c r="E29">
+        <v>0.09983525425195694</v>
+      </c>
+      <c r="F29">
+        <v>0.002207325771450996</v>
+      </c>
+      <c r="G29">
+        <v>0.001862652949057519</v>
+      </c>
+      <c r="H29">
+        <v>1.000430734224298</v>
+      </c>
+      <c r="I29">
+        <v>0.05232212543308418</v>
+      </c>
+      <c r="J29">
+        <v>0.1938825398683548</v>
+      </c>
+      <c r="K29">
+        <v>1.888473471055856E+27</v>
+      </c>
+      <c r="L29">
+        <v>5.714205741882324</v>
+      </c>
+      <c r="M29">
+        <v>11.09712886810303</v>
+      </c>
+      <c r="N29" t="s">
+        <v>336</v>
+      </c>
+      <c r="O29" t="s">
+        <v>396</v>
+      </c>
+      <c r="P29" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30">
+        <v>0.08917372158857674</v>
+      </c>
+      <c r="D30">
+        <v>0.04844195395708084</v>
+      </c>
+      <c r="E30">
+        <v>0.2443641871213913</v>
+      </c>
+      <c r="F30">
+        <v>0.002051797695457935</v>
+      </c>
+      <c r="G30">
+        <v>0.00184230413287878</v>
+      </c>
+      <c r="H30">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I30">
+        <v>0.05793848196911786</v>
+      </c>
+      <c r="J30">
+        <v>0.1982367187738419</v>
+      </c>
+      <c r="K30" t="s">
+        <v>128</v>
+      </c>
+      <c r="L30">
+        <v>13.9865140914917</v>
+      </c>
+      <c r="M30">
+        <v>11.34634685516357</v>
+      </c>
+      <c r="N30" t="s">
+        <v>337</v>
+      </c>
+      <c r="O30" t="s">
+        <v>397</v>
+      </c>
+      <c r="P30" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31">
+        <v>0.176322503951735</v>
+      </c>
+      <c r="D31">
+        <v>0.09537460654973984</v>
+      </c>
+      <c r="E31">
+        <v>0.4862891137599945</v>
+      </c>
+      <c r="F31">
+        <v>0.002082765800878406</v>
+      </c>
+      <c r="G31">
+        <v>0.002150909742340446</v>
+      </c>
+      <c r="H31">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I31">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J31">
+        <v>0.1961273699998856</v>
+      </c>
+      <c r="K31" t="s">
+        <v>128</v>
+      </c>
+      <c r="L31">
+        <v>27.83341407775879</v>
+      </c>
+      <c r="M31">
+        <v>11.22561454772949</v>
+      </c>
+      <c r="N31" t="s">
+        <v>338</v>
+      </c>
+      <c r="O31" t="s">
+        <v>398</v>
+      </c>
+      <c r="P31" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>0.0005329825155403512</v>
+      </c>
+      <c r="D32">
+        <v>-8.07794785941951E-05</v>
+      </c>
+      <c r="E32">
+        <v>0.003243436105549335</v>
+      </c>
+      <c r="F32">
+        <v>0.0007572735194116831</v>
+      </c>
+      <c r="G32">
+        <v>0.0007844878709875047</v>
+      </c>
+      <c r="H32">
+        <v>1.000427078750425</v>
+      </c>
+      <c r="I32">
+        <v>0.04906541003546702</v>
+      </c>
+      <c r="J32">
+        <v>-0.02490552514791489</v>
+      </c>
+      <c r="K32">
+        <v>-0.23248291015625</v>
+      </c>
+      <c r="L32">
+        <v>0.1856424510478973</v>
+      </c>
+      <c r="M32">
+        <v>-1.425501346588135</v>
+      </c>
+      <c r="N32" t="s">
+        <v>339</v>
+      </c>
+      <c r="O32" t="s">
+        <v>399</v>
+      </c>
+      <c r="P32" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33">
+        <v>0</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33">
+        <v>0.0007058285058348833</v>
+      </c>
+      <c r="D33">
+        <v>0.0001500307262176648</v>
+      </c>
+      <c r="E33">
+        <v>0.004251590929925442</v>
+      </c>
+      <c r="F33">
+        <v>0.0009124184143729508</v>
+      </c>
+      <c r="G33">
+        <v>0.0009070710511878133</v>
+      </c>
+      <c r="H33">
+        <v>1.000638464324489</v>
+      </c>
+      <c r="I33">
+        <v>0.04900385875075021</v>
+      </c>
+      <c r="J33">
+        <v>0.03528813645243645</v>
+      </c>
+      <c r="K33">
+        <v>0.6349952220916748</v>
+      </c>
+      <c r="L33">
+        <v>0.2433455437421799</v>
+      </c>
+      <c r="M33">
+        <v>2.019764184951782</v>
+      </c>
+      <c r="N33" t="s">
+        <v>340</v>
+      </c>
+      <c r="O33" t="s">
+        <v>400</v>
+      </c>
+      <c r="P33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34">
+        <v>0</v>
+      </c>
+      <c r="B34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34">
+        <v>0.0008761720421081607</v>
+      </c>
+      <c r="D34">
+        <v>0.0003359469992574304</v>
+      </c>
+      <c r="E34">
+        <v>0.005282245576381683</v>
+      </c>
+      <c r="F34">
+        <v>0.001053311862051487</v>
+      </c>
+      <c r="G34">
+        <v>0.001033245935104787</v>
+      </c>
+      <c r="H34">
+        <v>1.000738412118996</v>
+      </c>
+      <c r="I34">
+        <v>0.04901971405410643</v>
+      </c>
+      <c r="J34">
+        <v>0.06359927356243134</v>
+      </c>
+      <c r="K34">
+        <v>2.005150556564331</v>
+      </c>
+      <c r="L34">
+        <v>0.3023364543914795</v>
+      </c>
+      <c r="M34">
+        <v>3.640190362930298</v>
+      </c>
+      <c r="N34" t="s">
+        <v>341</v>
+      </c>
+      <c r="O34" t="s">
+        <v>401</v>
+      </c>
+      <c r="P34" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35">
+        <v>0</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35">
+        <v>0.00170435363677883</v>
+      </c>
+      <c r="D35">
+        <v>0.00107032572850585</v>
+      </c>
+      <c r="E35">
+        <v>0.009906389750540257</v>
+      </c>
+      <c r="F35">
+        <v>0.001518251141533256</v>
+      </c>
+      <c r="G35">
+        <v>0.001365067786537111</v>
+      </c>
+      <c r="H35">
+        <v>1.000798447912862</v>
+      </c>
+      <c r="I35">
+        <v>0.04913091878765977</v>
+      </c>
+      <c r="J35">
+        <v>0.1080439761281013</v>
+      </c>
+      <c r="K35">
+        <v>32.27113723754883</v>
+      </c>
+      <c r="L35">
+        <v>0.5670055747032166</v>
+      </c>
+      <c r="M35">
+        <v>6.184042930603027</v>
+      </c>
+      <c r="N35" t="s">
+        <v>342</v>
+      </c>
+      <c r="O35" t="s">
+        <v>402</v>
+      </c>
+      <c r="P35" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36">
+        <v>0</v>
+      </c>
+      <c r="B36" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36">
+        <v>0.003292965261051304</v>
+      </c>
+      <c r="D36">
+        <v>0.002138299169018865</v>
+      </c>
+      <c r="E36">
+        <v>0.01982378400862217</v>
+      </c>
+      <c r="F36">
+        <v>0.002012478653341532</v>
+      </c>
+      <c r="G36">
+        <v>0.001692259451374412</v>
+      </c>
+      <c r="H36">
+        <v>1.000941406418178</v>
+      </c>
+      <c r="I36">
+        <v>0.04920137923646728</v>
+      </c>
+      <c r="J36">
+        <v>0.1078653410077095</v>
+      </c>
+      <c r="K36">
+        <v>1092.841918945312</v>
+      </c>
+      <c r="L36">
+        <v>1.134641051292419</v>
+      </c>
+      <c r="M36">
+        <v>6.173818588256836</v>
+      </c>
+      <c r="N36" t="s">
+        <v>343</v>
+      </c>
+      <c r="O36" t="s">
+        <v>403</v>
+      </c>
+      <c r="P36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37">
+        <v>0</v>
+      </c>
+      <c r="B37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37">
+        <v>0.006357265696876434</v>
+      </c>
+      <c r="D37">
+        <v>0.004050134215503931</v>
+      </c>
+      <c r="E37">
+        <v>0.03988539800047874</v>
+      </c>
+      <c r="F37">
+        <v>0.002402722137048841</v>
+      </c>
+      <c r="G37">
+        <v>0.001901271403767169</v>
+      </c>
+      <c r="H37">
+        <v>1.000767981380587</v>
+      </c>
+      <c r="I37">
+        <v>0.04931496227280869</v>
+      </c>
+      <c r="J37">
+        <v>0.1015442833304405</v>
+      </c>
+      <c r="K37">
+        <v>563231.3125</v>
+      </c>
+      <c r="L37">
+        <v>2.282894611358643</v>
+      </c>
+      <c r="M37">
+        <v>5.812024116516113</v>
+      </c>
+      <c r="N37" t="s">
+        <v>344</v>
+      </c>
+      <c r="O37" t="s">
+        <v>404</v>
+      </c>
+      <c r="P37" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38">
+        <v>0</v>
+      </c>
+      <c r="B38" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38">
+        <v>0.01535229053865883</v>
+      </c>
+      <c r="D38">
+        <v>0.009076998569071293</v>
+      </c>
+      <c r="E38">
+        <v>0.08742498606443405</v>
+      </c>
+      <c r="F38">
+        <v>0.002414375077933073</v>
+      </c>
+      <c r="G38">
+        <v>0.001932341721840203</v>
+      </c>
+      <c r="H38">
+        <v>1.000526736771615</v>
+      </c>
+      <c r="I38">
+        <v>0.05094588060725464</v>
+      </c>
+      <c r="J38">
+        <v>0.1038261353969574</v>
+      </c>
+      <c r="K38">
+        <v>7177357492224</v>
+      </c>
+      <c r="L38">
+        <v>5.003887176513672</v>
+      </c>
+      <c r="M38">
+        <v>5.942629337310791</v>
+      </c>
+      <c r="N38" t="s">
+        <v>345</v>
+      </c>
+      <c r="O38" t="s">
+        <v>405</v>
+      </c>
+      <c r="P38" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39">
+        <v>0.03019131737773812</v>
+      </c>
+      <c r="D39">
+        <v>0.01769630610942841</v>
+      </c>
+      <c r="E39">
+        <v>0.1751586943864822</v>
+      </c>
+      <c r="F39">
+        <v>0.002195966895669699</v>
+      </c>
+      <c r="G39">
+        <v>0.001853389549069107</v>
+      </c>
+      <c r="H39">
+        <v>1.000376440248711</v>
+      </c>
+      <c r="I39">
+        <v>0.05243876900691057</v>
+      </c>
+      <c r="J39">
+        <v>0.101030133664608</v>
+      </c>
+      <c r="K39">
+        <v>9.060553579670435E+24</v>
+      </c>
+      <c r="L39">
+        <v>10.02544498443604</v>
+      </c>
+      <c r="M39">
+        <v>5.782596111297607</v>
+      </c>
+      <c r="N39" t="s">
+        <v>346</v>
+      </c>
+      <c r="O39" t="s">
+        <v>406</v>
+      </c>
+      <c r="P39" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40">
+        <v>0</v>
+      </c>
+      <c r="B40" t="s">
+        <v>107</v>
+      </c>
+      <c r="C40">
+        <v>0.07342531243948802</v>
+      </c>
+      <c r="D40">
+        <v>0.04363153129816055</v>
+      </c>
+      <c r="E40">
+        <v>0.4457373917102814</v>
+      </c>
+      <c r="F40">
+        <v>0.002058869460597634</v>
+      </c>
+      <c r="G40">
+        <v>0.001940650166943669</v>
+      </c>
+      <c r="H40">
+        <v>1.001008908811846</v>
+      </c>
+      <c r="I40">
+        <v>0.05780776923815894</v>
+      </c>
+      <c r="J40">
+        <v>0.09788618236780167</v>
+      </c>
+      <c r="K40" t="s">
+        <v>128</v>
+      </c>
+      <c r="L40">
+        <v>25.51238250732422</v>
+      </c>
+      <c r="M40">
+        <v>5.60264778137207</v>
+      </c>
+      <c r="N40" t="s">
+        <v>347</v>
+      </c>
+      <c r="O40" t="s">
+        <v>407</v>
+      </c>
+      <c r="P40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41">
+        <v>0</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>0.150903543831252</v>
+      </c>
+      <c r="D41">
+        <v>0.0913098081946373</v>
+      </c>
+      <c r="E41">
+        <v>1.009886980056763</v>
+      </c>
+      <c r="F41">
+        <v>0.002085836371406913</v>
+      </c>
+      <c r="G41">
+        <v>0.002218080451712012</v>
+      </c>
+      <c r="H41">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I41">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J41">
+        <v>0.09041586518287659</v>
+      </c>
+      <c r="K41" t="s">
+        <v>128</v>
+      </c>
+      <c r="L41">
+        <v>57.80224609375</v>
+      </c>
+      <c r="M41">
+        <v>5.175074100494385</v>
+      </c>
+      <c r="N41" t="s">
+        <v>348</v>
+      </c>
+      <c r="O41" t="s">
+        <v>408</v>
+      </c>
+      <c r="P41" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42">
+        <v>0</v>
+      </c>
+      <c r="B42" t="s">
+        <v>109</v>
+      </c>
+      <c r="C42">
+        <v>0.0005918953574764287</v>
+      </c>
+      <c r="D42">
+        <v>-9.733506885822862E-05</v>
+      </c>
+      <c r="E42">
+        <v>0.003309028688818216</v>
+      </c>
+      <c r="F42">
+        <v>0.0008138600387610495</v>
+      </c>
+      <c r="G42">
+        <v>0.0008272940758615732</v>
+      </c>
+      <c r="H42">
+        <v>1.000298620331045</v>
+      </c>
+      <c r="I42">
+        <v>0.04905665566667329</v>
+      </c>
+      <c r="J42">
+        <v>-0.02941499650478363</v>
+      </c>
+      <c r="K42">
+        <v>-0.2730394005775452</v>
+      </c>
+      <c r="L42">
+        <v>0.1893967241048813</v>
+      </c>
+      <c r="M42">
+        <v>-1.68360710144043</v>
+      </c>
+      <c r="N42" t="s">
+        <v>349</v>
+      </c>
+      <c r="O42" t="s">
+        <v>409</v>
+      </c>
+      <c r="P42" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43">
+        <v>0</v>
+      </c>
+      <c r="B43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C43">
+        <v>0.000782202167414614</v>
+      </c>
+      <c r="D43">
+        <v>-3.002471021318343E-05</v>
+      </c>
+      <c r="E43">
+        <v>0.00480106333270669</v>
+      </c>
+      <c r="F43">
+        <v>0.0009884532773867249</v>
+      </c>
+      <c r="G43">
+        <v>0.0009791339980438352</v>
+      </c>
+      <c r="H43">
+        <v>1.000473720410847</v>
+      </c>
+      <c r="I43">
+        <v>0.04904552843823369</v>
+      </c>
+      <c r="J43">
+        <v>-0.006253762636333704</v>
+      </c>
+      <c r="K43">
+        <v>-0.0937272310256958</v>
+      </c>
+      <c r="L43">
+        <v>0.2747953534126282</v>
+      </c>
+      <c r="M43">
+        <v>-0.3579425513744354</v>
+      </c>
+      <c r="N43" t="s">
+        <v>350</v>
+      </c>
+      <c r="O43" t="s">
+        <v>410</v>
+      </c>
+      <c r="P43" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44">
+        <v>0</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44">
+        <v>0.0009694281094859701</v>
+      </c>
+      <c r="D44">
+        <v>2.89207400783198E-05</v>
+      </c>
+      <c r="E44">
+        <v>0.005938183981925249</v>
+      </c>
+      <c r="F44">
+        <v>0.00114169844891876</v>
+      </c>
+      <c r="G44">
+        <v>0.001119807711802423</v>
+      </c>
+      <c r="H44">
+        <v>1.000537327948644</v>
+      </c>
+      <c r="I44">
+        <v>0.0491027166735744</v>
+      </c>
+      <c r="J44">
+        <v>0.004870300646871328</v>
+      </c>
+      <c r="K44">
+        <v>0.09954595565795898</v>
+      </c>
+      <c r="L44">
+        <v>0.3398799896240234</v>
+      </c>
+      <c r="M44">
+        <v>0.2787582278251648</v>
+      </c>
+      <c r="N44" t="s">
+        <v>351</v>
+      </c>
+      <c r="O44" t="s">
+        <v>411</v>
+      </c>
+      <c r="P44" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45">
+        <v>0</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45">
+        <v>0.001873767437616163</v>
+      </c>
+      <c r="D45">
+        <v>0.0001416531740687788</v>
+      </c>
+      <c r="E45">
+        <v>0.01204914972186089</v>
+      </c>
+      <c r="F45">
+        <v>0.001651587896049023</v>
+      </c>
+      <c r="G45">
+        <v>0.001450430601835251</v>
+      </c>
+      <c r="H45">
+        <v>1.000682907285449</v>
+      </c>
+      <c r="I45">
+        <v>0.04919862678366487</v>
+      </c>
+      <c r="J45">
+        <v>0.01175627950578928</v>
+      </c>
+      <c r="K45">
+        <v>0.5902899503707886</v>
+      </c>
+      <c r="L45">
+        <v>0.6896493434906006</v>
+      </c>
+      <c r="M45">
+        <v>0.6728865504264832</v>
+      </c>
+      <c r="N45" t="s">
+        <v>352</v>
+      </c>
+      <c r="O45" t="s">
+        <v>412</v>
+      </c>
+      <c r="P45" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46">
+        <v>0</v>
+      </c>
+      <c r="B46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C46">
+        <v>0.003601289812828226</v>
+      </c>
+      <c r="D46">
+        <v>4.685103704105131E-05</v>
+      </c>
+      <c r="E46">
+        <v>0.02623402699828148</v>
+      </c>
+      <c r="F46">
+        <v>0.002141973003745079</v>
+      </c>
+      <c r="G46">
+        <v>0.001771170762367547</v>
+      </c>
+      <c r="H46">
+        <v>1.000860598515493</v>
+      </c>
+      <c r="I46">
+        <v>0.04920445102458396</v>
+      </c>
+      <c r="J46">
+        <v>0.001785888103768229</v>
+      </c>
+      <c r="K46">
+        <v>0.1658780574798584</v>
+      </c>
+      <c r="L46">
+        <v>1.501539945602417</v>
+      </c>
+      <c r="M46">
+        <v>0.1022177189588547</v>
+      </c>
+      <c r="N46" t="s">
+        <v>353</v>
+      </c>
+      <c r="O46" t="s">
+        <v>413</v>
+      </c>
+      <c r="P46" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47">
+        <v>0</v>
+      </c>
+      <c r="B47" t="s">
+        <v>114</v>
+      </c>
+      <c r="C47">
+        <v>0.006967242315226832</v>
+      </c>
+      <c r="D47">
+        <v>-0.0002224871568614617</v>
+      </c>
+      <c r="E47">
+        <v>0.05234704911708832</v>
+      </c>
+      <c r="F47">
+        <v>0.002519572619348764</v>
+      </c>
+      <c r="G47">
+        <v>0.0019601343665272</v>
+      </c>
+      <c r="H47">
+        <v>1.000663401886648</v>
+      </c>
+      <c r="I47">
+        <v>0.04946138320991884</v>
+      </c>
+      <c r="J47">
+        <v>-0.004250233061611652</v>
+      </c>
+      <c r="K47">
+        <v>-0.5176111459732056</v>
+      </c>
+      <c r="L47">
+        <v>2.996154069900513</v>
+      </c>
+      <c r="M47">
+        <v>-0.243267834186554</v>
+      </c>
+      <c r="N47" t="s">
+        <v>354</v>
+      </c>
+      <c r="O47" t="s">
+        <v>414</v>
+      </c>
+      <c r="P47" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48">
+        <v>0</v>
+      </c>
+      <c r="B48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C48">
+        <v>0.01676024983079183</v>
+      </c>
+      <c r="D48">
+        <v>0.0002069326146738604</v>
+      </c>
+      <c r="E48">
+        <v>0.08930941671133041</v>
+      </c>
+      <c r="F48">
+        <v>0.002380403690040112</v>
+      </c>
+      <c r="G48">
+        <v>0.001958596985787153</v>
+      </c>
+      <c r="H48">
+        <v>1.000341440397789</v>
+      </c>
+      <c r="I48">
+        <v>0.05108098211774715</v>
+      </c>
+      <c r="J48">
+        <v>0.002317030215635896</v>
+      </c>
+      <c r="K48">
+        <v>0.9697158336639404</v>
+      </c>
+      <c r="L48">
+        <v>5.111745357513428</v>
+      </c>
+      <c r="M48">
+        <v>0.1326183527708054</v>
+      </c>
+      <c r="N48" t="s">
+        <v>355</v>
+      </c>
+      <c r="O48" t="s">
+        <v>415</v>
+      </c>
+      <c r="P48" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49">
+        <v>0</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49">
+        <v>0.03349014726234306</v>
+      </c>
+      <c r="D49">
+        <v>-0.001445561530999839</v>
+      </c>
+      <c r="E49">
+        <v>0.2139632701873779</v>
+      </c>
+      <c r="F49">
+        <v>0.002168604638427496</v>
+      </c>
+      <c r="G49">
+        <v>0.002037117723375559</v>
+      </c>
+      <c r="H49">
+        <v>1.000313170229744</v>
+      </c>
+      <c r="I49">
+        <v>0.05260296083207476</v>
+      </c>
+      <c r="J49">
+        <v>-0.006756119895726442</v>
+      </c>
+      <c r="K49">
+        <v>-0.9912524819374084</v>
+      </c>
+      <c r="L49">
+        <v>12.2464771270752</v>
+      </c>
+      <c r="M49">
+        <v>-0.3866956532001495</v>
+      </c>
+      <c r="N49" t="s">
+        <v>356</v>
+      </c>
+      <c r="O49" t="s">
+        <v>416</v>
+      </c>
+      <c r="P49" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50">
+        <v>0</v>
+      </c>
+      <c r="B50" t="s">
+        <v>117</v>
+      </c>
+      <c r="C50">
+        <v>0.08412571914879582</v>
+      </c>
+      <c r="D50">
+        <v>-0.004890034440904856</v>
+      </c>
+      <c r="E50">
+        <v>0.5478843450546265</v>
+      </c>
+      <c r="F50">
+        <v>0.002101392718032002</v>
+      </c>
+      <c r="G50">
+        <v>0.002387484069913626</v>
+      </c>
+      <c r="H50">
+        <v>1.000940909355842</v>
+      </c>
+      <c r="I50">
+        <v>0.05784162264752678</v>
+      </c>
+      <c r="J50">
+        <v>-0.008925303816795349</v>
+      </c>
+      <c r="K50">
+        <v>-0.9999998807907104</v>
+      </c>
+      <c r="L50">
+        <v>31.35890007019043</v>
+      </c>
+      <c r="M50">
+        <v>-0.5108518004417419</v>
+      </c>
+      <c r="N50" t="s">
+        <v>357</v>
+      </c>
+      <c r="O50" t="s">
+        <v>417</v>
+      </c>
+      <c r="P50" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51">
+        <v>0</v>
+      </c>
+      <c r="B51" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51">
+        <v>0.1549631303880432</v>
+      </c>
+      <c r="D51">
+        <v>-0.006714881397783756</v>
+      </c>
+      <c r="E51">
+        <v>0.9970443248748779</v>
+      </c>
+      <c r="F51">
+        <v>0.002130667213350534</v>
+      </c>
+      <c r="G51">
+        <v>0.002541814697906375</v>
+      </c>
+      <c r="H51">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I51">
+        <v>0.06768650018013105</v>
+      </c>
+      <c r="J51">
+        <v>-0.0067347870208323</v>
+      </c>
+      <c r="K51">
+        <v>-1</v>
+      </c>
+      <c r="L51">
+        <v>57.06718063354492</v>
+      </c>
+      <c r="M51">
+        <v>-0.3854746222496033</v>
+      </c>
+      <c r="N51" t="s">
+        <v>358</v>
+      </c>
+      <c r="O51" t="s">
+        <v>418</v>
+      </c>
+      <c r="P51" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52">
+        <v>0</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52">
+        <v>0.0001620632274617623</v>
+      </c>
+      <c r="D52">
+        <v>0.0002493795764166862</v>
+      </c>
+      <c r="E52">
+        <v>0.0007202735869213939</v>
+      </c>
+      <c r="F52">
+        <v>0.00108547299169004</v>
+      </c>
+      <c r="G52">
+        <v>0.00104921346064657</v>
+      </c>
+      <c r="H52">
+        <v>0.9996482251291215</v>
+      </c>
+      <c r="I52">
+        <v>0.0494486703989773</v>
+      </c>
+      <c r="J52">
+        <v>0.3462289571762085</v>
+      </c>
+      <c r="K52">
+        <v>1.263440847396851</v>
+      </c>
+      <c r="L52">
+        <v>0.04122583195567131</v>
+      </c>
+      <c r="M52">
+        <v>19.81688117980957</v>
+      </c>
+      <c r="N52" t="s">
+        <v>359</v>
+      </c>
+      <c r="O52" t="s">
+        <v>419</v>
+      </c>
+      <c r="P52" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53">
+        <v>0</v>
+      </c>
+      <c r="B53" t="s">
+        <v>120</v>
+      </c>
+      <c r="C53">
+        <v>0.0002004284874786391</v>
+      </c>
+      <c r="D53">
+        <v>0.0002995521645061672</v>
+      </c>
+      <c r="E53">
+        <v>0.0007634233334101737</v>
+      </c>
+      <c r="F53">
+        <v>0.001261208322830498</v>
+      </c>
+      <c r="G53">
+        <v>0.001225930056534708</v>
+      </c>
+      <c r="H53">
+        <v>0.9998926504783099</v>
+      </c>
+      <c r="I53">
+        <v>0.049456425060798</v>
+      </c>
+      <c r="J53">
+        <v>0.3923801481723785</v>
+      </c>
+      <c r="K53">
+        <v>1.667799472808838</v>
+      </c>
+      <c r="L53">
+        <v>0.04369556531310081</v>
+      </c>
+      <c r="M53">
+        <v>22.45840835571289</v>
+      </c>
+      <c r="N53" t="s">
+        <v>360</v>
+      </c>
+      <c r="O53" t="s">
+        <v>420</v>
+      </c>
+      <c r="P53" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54">
+        <v>0</v>
+      </c>
+      <c r="B54" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54">
+        <v>0.0002338736291877912</v>
+      </c>
+      <c r="D54">
+        <v>0.0003395303501747549</v>
+      </c>
+      <c r="E54">
+        <v>0.000794466002844274</v>
+      </c>
+      <c r="F54">
+        <v>0.001376677886582911</v>
+      </c>
+      <c r="G54">
+        <v>0.001303217839449644</v>
+      </c>
+      <c r="H54">
+        <v>1.000091145906271</v>
+      </c>
+      <c r="I54">
+        <v>0.04945056046438354</v>
+      </c>
+      <c r="J54">
+        <v>0.4273692667484283</v>
+      </c>
+      <c r="K54">
+        <v>2.040553569793701</v>
+      </c>
+      <c r="L54">
+        <v>0.04547233507037163</v>
+      </c>
+      <c r="M54">
+        <v>24.46105766296387</v>
+      </c>
+      <c r="N54" t="s">
+        <v>361</v>
+      </c>
+      <c r="O54" t="s">
+        <v>421</v>
+      </c>
+      <c r="P54" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55">
+        <v>0</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55">
+        <v>0.000351008549467084</v>
+      </c>
+      <c r="D55">
+        <v>0.0004757340357173234</v>
+      </c>
+      <c r="E55">
+        <v>0.0009131475235335529</v>
+      </c>
+      <c r="F55">
+        <v>0.001746159628964961</v>
+      </c>
+      <c r="G55">
+        <v>0.001536614261567593</v>
+      </c>
+      <c r="H55">
+        <v>1.000638193026288</v>
+      </c>
+      <c r="I55">
+        <v>0.04911851651043118</v>
+      </c>
+      <c r="J55">
+        <v>0.5209826827049255</v>
+      </c>
+      <c r="K55">
+        <v>3.750420570373535</v>
+      </c>
+      <c r="L55">
+        <v>0.0522652305662632</v>
+      </c>
+      <c r="M55">
+        <v>29.81914710998535</v>
+      </c>
+      <c r="N55" t="s">
+        <v>362</v>
+      </c>
+      <c r="O55" t="s">
+        <v>422</v>
+      </c>
+      <c r="P55" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56">
+        <v>0</v>
+      </c>
+      <c r="B56" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56">
+        <v>0.0004802021850016374</v>
+      </c>
+      <c r="D56">
+        <v>0.0006188990082591772</v>
+      </c>
+      <c r="E56">
+        <v>0.001094821142032743</v>
+      </c>
+      <c r="F56">
+        <v>0.002354843076318502</v>
+      </c>
+      <c r="G56">
+        <v>0.001914759865030646</v>
+      </c>
+      <c r="H56">
+        <v>1.000540117442564</v>
+      </c>
+      <c r="I56">
+        <v>0.04962360312461609</v>
+      </c>
+      <c r="J56">
+        <v>0.5652968883514404</v>
+      </c>
+      <c r="K56">
+        <v>6.59129810333252</v>
+      </c>
+      <c r="L56">
+        <v>0.06266357004642487</v>
+      </c>
+      <c r="M56">
+        <v>32.35552978515625</v>
+      </c>
+      <c r="N56" t="s">
+        <v>363</v>
+      </c>
+      <c r="O56" t="s">
+        <v>423</v>
+      </c>
+      <c r="P56" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57">
+        <v>0</v>
+      </c>
+      <c r="B57" t="s">
+        <v>123</v>
+      </c>
+      <c r="C57">
+        <v>0.0006211683903385823</v>
+      </c>
+      <c r="D57">
+        <v>0.0007738558342680335</v>
+      </c>
+      <c r="E57">
+        <v>0.001466007786802948</v>
+      </c>
+      <c r="F57">
+        <v>0.002530817408114672</v>
+      </c>
+      <c r="G57">
+        <v>0.002023634035140276</v>
+      </c>
+      <c r="H57">
+        <v>1.000218117252766</v>
+      </c>
+      <c r="I57">
+        <v>0.04990845858670896</v>
+      </c>
+      <c r="J57">
+        <v>0.5278661251068115</v>
+      </c>
+      <c r="K57">
+        <v>11.608078956604</v>
+      </c>
+      <c r="L57">
+        <v>0.08390893787145615</v>
+      </c>
+      <c r="M57">
+        <v>30.21313095092773</v>
+      </c>
+      <c r="N57" t="s">
+        <v>364</v>
+      </c>
+      <c r="O57" t="s">
+        <v>424</v>
+      </c>
+      <c r="P57" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58">
+        <v>0</v>
+      </c>
+      <c r="B58" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58">
+        <v>0.0008424621339504759</v>
+      </c>
+      <c r="D58">
+        <v>0.0009774428326636553</v>
+      </c>
+      <c r="E58">
+        <v>0.002366612898185849</v>
+      </c>
+      <c r="F58">
+        <v>0.002303982619196177</v>
+      </c>
+      <c r="G58">
+        <v>0.002055846387520432</v>
+      </c>
+      <c r="H58">
+        <v>1.000036848016128</v>
+      </c>
+      <c r="I58">
+        <v>0.05196122746515161</v>
+      </c>
+      <c r="J58">
+        <v>0.4130133986473083</v>
+      </c>
+      <c r="K58">
+        <v>23.54206657409668</v>
+      </c>
+      <c r="L58">
+        <v>0.1354562938213348</v>
+      </c>
+      <c r="M58">
+        <v>23.63937950134277</v>
+      </c>
+      <c r="N58" t="s">
+        <v>365</v>
+      </c>
+      <c r="O58" t="s">
+        <v>425</v>
+      </c>
+      <c r="P58" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59">
+        <v>0</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59">
+        <v>0.00103176711883386</v>
+      </c>
+      <c r="D59">
+        <v>0.001098680659197271</v>
+      </c>
+      <c r="E59">
+        <v>0.003482118947431445</v>
+      </c>
+      <c r="F59">
+        <v>0.002133501693606377</v>
+      </c>
+      <c r="G59">
+        <v>0.00223863311111927</v>
+      </c>
+      <c r="H59">
+        <v>0.9999013914799315</v>
+      </c>
+      <c r="I59">
+        <v>0.05379179552409619</v>
+      </c>
+      <c r="J59">
+        <v>0.315520703792572</v>
+      </c>
+      <c r="K59">
+        <v>35.49391174316406</v>
+      </c>
+      <c r="L59">
+        <v>0.1993037760257721</v>
+      </c>
+      <c r="M59">
+        <v>18.05925369262695</v>
+      </c>
+      <c r="N59" t="s">
+        <v>366</v>
+      </c>
+      <c r="O59" t="s">
+        <v>426</v>
+      </c>
+      <c r="P59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60">
+        <v>0</v>
+      </c>
+      <c r="B60" t="s">
+        <v>126</v>
+      </c>
+      <c r="C60">
+        <v>0.001288675522160909</v>
+      </c>
+      <c r="D60">
+        <v>0.00132691184990108</v>
+      </c>
+      <c r="E60">
+        <v>0.005673137959092855</v>
+      </c>
+      <c r="F60">
+        <v>0.00213691359385848</v>
+      </c>
+      <c r="G60">
+        <v>0.002096957992762327</v>
+      </c>
+      <c r="H60">
+        <v>1.000413913571808</v>
+      </c>
+      <c r="I60">
+        <v>0.05955828034937725</v>
+      </c>
+      <c r="J60">
+        <v>0.2338938117027283</v>
+      </c>
+      <c r="K60">
+        <v>76.02297973632812</v>
+      </c>
+      <c r="L60">
+        <v>0.3247097134590149</v>
+      </c>
+      <c r="M60">
+        <v>13.38722801208496</v>
+      </c>
+      <c r="N60" t="s">
+        <v>367</v>
+      </c>
+      <c r="O60" t="s">
+        <v>427</v>
+      </c>
+      <c r="P60" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61">
+        <v>0</v>
+      </c>
+      <c r="B61" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61">
+        <v>0.001467114430199934</v>
+      </c>
+      <c r="D61">
+        <v>0.001571901841089129</v>
+      </c>
+      <c r="E61">
+        <v>0.007893959060311317</v>
+      </c>
+      <c r="F61">
+        <v>0.00220214412547648</v>
+      </c>
+      <c r="G61">
+        <v>0.002358655212447047</v>
+      </c>
+      <c r="H61">
+        <v>1.002019583843329</v>
+      </c>
+      <c r="I61">
+        <v>0.06740300985866601</v>
+      </c>
+      <c r="J61">
+        <v>0.1991271823644638</v>
+      </c>
+      <c r="K61">
+        <v>170.6539764404297</v>
+      </c>
+      <c r="L61">
+        <v>0.4518214166164398</v>
+      </c>
+      <c r="M61">
+        <v>11.39731311798096</v>
+      </c>
+      <c r="N61" t="s">
+        <v>368</v>
+      </c>
+      <c r="O61" t="s">
+        <v>428</v>
+      </c>
+      <c r="P61" t="s">
+        <v>488</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:2">
+      <c r="B1" t="s">
+        <v>489</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/rf_standard/performance.xlsx
+++ b/scripts/rf_standard/performance.xlsx
@@ -9109,12 +9109,6556 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B819"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0008790614665485919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2.441420474497136E-05</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.0006613457226194441</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.000131013774080202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.0006411475478671491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.0005545607418753207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.0004387630906421691</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.000403546349843964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.0008875462808646262</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.0005236683646216989</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.0005103311850689352</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>2.628679794725031E-05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.001224625622853637</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>-0.0002564091118983924</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.0001799154269974679</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.0001368216762784868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>6.125817162683234E-05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.001250406494364142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.0001913269225042313</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.0004163445846643299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.0003055586421396583</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.001384156756103039</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.00139160780236125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.0009853543015196919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.001786721521057189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.0004765824705827981</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>-0.000213240142329596</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>-0.0005395281477831304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>-0.0009103958727791905</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>-0.0002077972458209842</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.0004185778088867664</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.0001921336224768311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>7.228506729006767E-05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.0002432138717267662</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.0007078810012899339</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>-0.0004549456934910268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.0002489580656401813</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>-0.0006090375827625394</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.001904524397104979</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.0006686362903565168</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>-0.0001451362622901797</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.001453868229873478</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>-3.04841287288582E-05</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>-0.0002063521824311465</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.001603584387339652</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.0002009214804274961</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.0001596621295902878</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.0004757878195960075</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.0003489133960101753</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.0002751475549302995</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.0002735260059125721</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>5.196016718400642E-05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>-0.0001765835186233744</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.0004313590761739761</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>0.0001296038972213864</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.0006192376604303718</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.0005430091405287385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>5.514385702554137E-05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>0.0007180552347563207</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.000288643961539492</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.0003472047974355519</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>-0.0001415220613125712</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>62</v>
+      </c>
+      <c r="B64">
+        <v>0.0005111175705678761</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>63</v>
+      </c>
+      <c r="B65">
+        <v>0.002430374035611749</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>64</v>
+      </c>
+      <c r="B66">
+        <v>0.0005131341749802232</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>65</v>
+      </c>
+      <c r="B67">
+        <v>0.0004627893504220992</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>66</v>
+      </c>
+      <c r="B68">
+        <v>0.0002813597675412893</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>67</v>
+      </c>
+      <c r="B69">
+        <v>0.00039367497083731</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>68</v>
+      </c>
+      <c r="B70">
+        <v>0.001391640980727971</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>69</v>
+      </c>
+      <c r="B71">
+        <v>0.000732001441065222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72">
+        <v>70</v>
+      </c>
+      <c r="B72">
+        <v>0.0003389791818335652</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73">
+        <v>71</v>
+      </c>
+      <c r="B73">
+        <v>-0.0008932671044021845</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74">
+        <v>72</v>
+      </c>
+      <c r="B74">
+        <v>0.0006206096149981022</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75">
+        <v>73</v>
+      </c>
+      <c r="B75">
+        <v>0.001096681808121502</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76">
+        <v>74</v>
+      </c>
+      <c r="B76">
+        <v>0.00183706299867481</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77">
+        <v>75</v>
+      </c>
+      <c r="B77">
+        <v>-0.001034632208757102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78">
+        <v>76</v>
+      </c>
+      <c r="B78">
+        <v>0.002948812674731016</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79">
+        <v>77</v>
+      </c>
+      <c r="B79">
+        <v>0.0005431431927718222</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80">
+        <v>78</v>
+      </c>
+      <c r="B80">
+        <v>0.0002642798353917897</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81">
+        <v>79</v>
+      </c>
+      <c r="B81">
+        <v>2.713273715926334E-05</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82">
+        <v>80</v>
+      </c>
+      <c r="B82">
+        <v>-5.421940386440838E-06</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83">
+        <v>81</v>
+      </c>
+      <c r="B83">
+        <v>0.000192781604710035</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84">
+        <v>82</v>
+      </c>
+      <c r="B84">
+        <v>0.0006275709602050483</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85">
+        <v>83</v>
+      </c>
+      <c r="B85">
+        <v>0.0001340273156529292</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86">
+        <v>84</v>
+      </c>
+      <c r="B86">
+        <v>0.0001508488203398883</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87">
+        <v>85</v>
+      </c>
+      <c r="B87">
+        <v>0.0001991942408494651</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88">
+        <v>86</v>
+      </c>
+      <c r="B88">
+        <v>0.0005447124131023884</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89">
+        <v>87</v>
+      </c>
+      <c r="B89">
+        <v>2.995433169417083E-05</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90">
+        <v>88</v>
+      </c>
+      <c r="B90">
+        <v>0.000605338835157454</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91">
+        <v>89</v>
+      </c>
+      <c r="B91">
+        <v>0.0004930426948703825</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92">
+        <v>90</v>
+      </c>
+      <c r="B92">
+        <v>0.0004129578883294016</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93">
+        <v>91</v>
+      </c>
+      <c r="B93">
+        <v>0.001011508633382618</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94">
+        <v>92</v>
+      </c>
+      <c r="B94">
+        <v>0.0007471709395758808</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95">
+        <v>93</v>
+      </c>
+      <c r="B95">
+        <v>0.001551268389448524</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96">
+        <v>94</v>
+      </c>
+      <c r="B96">
+        <v>7.920138887129724E-05</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97">
+        <v>95</v>
+      </c>
+      <c r="B97">
+        <v>0.0004649971087928861</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98">
+        <v>96</v>
+      </c>
+      <c r="B98">
+        <v>0.0003565404331311584</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99">
+        <v>97</v>
+      </c>
+      <c r="B99">
+        <v>0.000476040702778846</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100">
+        <v>98</v>
+      </c>
+      <c r="B100">
+        <v>0.0001975936902454123</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101">
+        <v>99</v>
+      </c>
+      <c r="B101">
+        <v>-0.0002170271909562871</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102">
+        <v>100</v>
+      </c>
+      <c r="B102">
+        <v>0.0002591060765553266</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103">
+        <v>101</v>
+      </c>
+      <c r="B103">
+        <v>-0.0001134469130192883</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104">
+        <v>102</v>
+      </c>
+      <c r="B104">
+        <v>0.0009551336988806725</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105">
+        <v>103</v>
+      </c>
+      <c r="B105">
+        <v>0.0004079369537066668</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106">
+        <v>104</v>
+      </c>
+      <c r="B106">
+        <v>0.0003075158456340432</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107">
+        <v>105</v>
+      </c>
+      <c r="B107">
+        <v>0.00121976004447788</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108">
+        <v>106</v>
+      </c>
+      <c r="B108">
+        <v>0.001383548253215849</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109">
+        <v>107</v>
+      </c>
+      <c r="B109">
+        <v>0.0002950307680293918</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110">
+        <v>108</v>
+      </c>
+      <c r="B110">
+        <v>0.0004150430322624743</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111">
+        <v>109</v>
+      </c>
+      <c r="B111">
+        <v>0.001770527334883809</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112">
+        <v>110</v>
+      </c>
+      <c r="B112">
+        <v>0.0002786803233902901</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113">
+        <v>111</v>
+      </c>
+      <c r="B113">
+        <v>3.295296437499928E-06</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114">
+        <v>112</v>
+      </c>
+      <c r="B114">
+        <v>0.001177276717498899</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115">
+        <v>113</v>
+      </c>
+      <c r="B115">
+        <v>-0.0001163763881777413</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116">
+        <v>114</v>
+      </c>
+      <c r="B116">
+        <v>0.0002956118260044605</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117">
+        <v>115</v>
+      </c>
+      <c r="B117">
+        <v>0.0007304329192265868</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118">
+        <v>116</v>
+      </c>
+      <c r="B118">
+        <v>-0.0002537363907322288</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119">
+        <v>117</v>
+      </c>
+      <c r="B119">
+        <v>0.0003052031679544598</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120">
+        <v>118</v>
+      </c>
+      <c r="B120">
+        <v>0.0002617778955027461</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121">
+        <v>119</v>
+      </c>
+      <c r="B121">
+        <v>-8.053483907133341E-05</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122">
+        <v>120</v>
+      </c>
+      <c r="B122">
+        <v>0.0009873347589746118</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123">
+        <v>121</v>
+      </c>
+      <c r="B123">
+        <v>6.735679198754951E-05</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124">
+        <v>122</v>
+      </c>
+      <c r="B124">
+        <v>0.0004328320210333914</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125">
+        <v>123</v>
+      </c>
+      <c r="B125">
+        <v>0.0003958894812967628</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126">
+        <v>124</v>
+      </c>
+      <c r="B126">
+        <v>0.0002490819024387747</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127">
+        <v>125</v>
+      </c>
+      <c r="B127">
+        <v>0.0009696492343209684</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128">
+        <v>126</v>
+      </c>
+      <c r="B128">
+        <v>0.0008498185779899359</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129">
+        <v>127</v>
+      </c>
+      <c r="B129">
+        <v>0.0007135649211704731</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130">
+        <v>128</v>
+      </c>
+      <c r="B130">
+        <v>0.0002505909651517868</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131">
+        <v>129</v>
+      </c>
+      <c r="B131">
+        <v>0.001578969648107886</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132">
+        <v>130</v>
+      </c>
+      <c r="B132">
+        <v>6.159573240438476E-05</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133">
+        <v>131</v>
+      </c>
+      <c r="B133">
+        <v>-5.594580943579786E-05</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134">
+        <v>132</v>
+      </c>
+      <c r="B134">
+        <v>3.273117181379348E-05</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135">
+        <v>133</v>
+      </c>
+      <c r="B135">
+        <v>0.0004802184412255883</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136">
+        <v>134</v>
+      </c>
+      <c r="B136">
+        <v>0.0004018608015030622</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137">
+        <v>135</v>
+      </c>
+      <c r="B137">
+        <v>0.001260321354493499</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138">
+        <v>136</v>
+      </c>
+      <c r="B138">
+        <v>0.0001961556990863755</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139">
+        <v>137</v>
+      </c>
+      <c r="B139">
+        <v>-8.393403550144285E-05</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140">
+        <v>138</v>
+      </c>
+      <c r="B140">
+        <v>0.0009415298118256032</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141">
+        <v>139</v>
+      </c>
+      <c r="B141">
+        <v>0.0001610208564670756</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142">
+        <v>140</v>
+      </c>
+      <c r="B142">
+        <v>-0.0005246321088634431</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143">
+        <v>141</v>
+      </c>
+      <c r="B143">
+        <v>0.005201346706598997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144">
+        <v>142</v>
+      </c>
+      <c r="B144">
+        <v>0.0006697892094962299</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145">
+        <v>143</v>
+      </c>
+      <c r="B145">
+        <v>0.0008825751137919724</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146">
+        <v>144</v>
+      </c>
+      <c r="B146">
+        <v>0.001098553882911801</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147">
+        <v>145</v>
+      </c>
+      <c r="B147">
+        <v>0.000131076289108023</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148">
+        <v>146</v>
+      </c>
+      <c r="B148">
+        <v>0.001370320562273264</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149">
+        <v>147</v>
+      </c>
+      <c r="B149">
+        <v>0.000895636563654989</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150">
+        <v>148</v>
+      </c>
+      <c r="B150">
+        <v>0.0007861729245632887</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151">
+        <v>149</v>
+      </c>
+      <c r="B151">
+        <v>0.0002814464678522199</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152">
+        <v>150</v>
+      </c>
+      <c r="B152">
+        <v>0.0004051205469295382</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153">
+        <v>151</v>
+      </c>
+      <c r="B153">
+        <v>0.0009630724089220166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154">
+        <v>152</v>
+      </c>
+      <c r="B154">
+        <v>-1.10484725155402E-05</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155">
+        <v>153</v>
+      </c>
+      <c r="B155">
+        <v>-0.0001366753276670352</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156">
+        <v>154</v>
+      </c>
+      <c r="B156">
+        <v>0.003825963474810123</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157">
+        <v>155</v>
+      </c>
+      <c r="B157">
+        <v>0.0008511889609508216</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158">
+        <v>156</v>
+      </c>
+      <c r="B158">
+        <v>0.0002267278323415667</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159">
+        <v>157</v>
+      </c>
+      <c r="B159">
+        <v>0.001315627712756395</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160">
+        <v>158</v>
+      </c>
+      <c r="B160">
+        <v>0.0005874809576198459</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161">
+        <v>159</v>
+      </c>
+      <c r="B161">
+        <v>0.0004831816477235407</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162">
+        <v>160</v>
+      </c>
+      <c r="B162">
+        <v>0.0004220263508614153</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163">
+        <v>161</v>
+      </c>
+      <c r="B163">
+        <v>0.0008751387940719724</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164">
+        <v>162</v>
+      </c>
+      <c r="B164">
+        <v>0.0008764967205934227</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165">
+        <v>163</v>
+      </c>
+      <c r="B165">
+        <v>0.0009103770134970546</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166">
+        <v>164</v>
+      </c>
+      <c r="B166">
+        <v>0.0005642909673042595</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167">
+        <v>165</v>
+      </c>
+      <c r="B167">
+        <v>0.0009106273064389825</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168">
+        <v>166</v>
+      </c>
+      <c r="B168">
+        <v>4.53392458439339E-05</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169">
+        <v>167</v>
+      </c>
+      <c r="B169">
+        <v>0.00251420377753675</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170">
+        <v>168</v>
+      </c>
+      <c r="B170">
+        <v>0.0008843024843372405</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171">
+        <v>169</v>
+      </c>
+      <c r="B171">
+        <v>1.438019717170391E-05</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172">
+        <v>170</v>
+      </c>
+      <c r="B172">
+        <v>0.0002906196459662169</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173">
+        <v>171</v>
+      </c>
+      <c r="B173">
+        <v>0.0005274443537928164</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174">
+        <v>172</v>
+      </c>
+      <c r="B174">
+        <v>0.000195074753719382</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175">
+        <v>173</v>
+      </c>
+      <c r="B175">
+        <v>7.719738641753793E-05</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176">
+        <v>174</v>
+      </c>
+      <c r="B176">
+        <v>0.0003995890729129314</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177">
+        <v>175</v>
+      </c>
+      <c r="B177">
+        <v>0.0007998431683517992</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178">
+        <v>176</v>
+      </c>
+      <c r="B178">
+        <v>0.0005095970700494945</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179">
+        <v>177</v>
+      </c>
+      <c r="B179">
+        <v>0.0004173738707322627</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180">
+        <v>178</v>
+      </c>
+      <c r="B180">
+        <v>0.0006337190861813724</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181">
+        <v>179</v>
+      </c>
+      <c r="B181">
+        <v>0.0006903918110765517</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182">
+        <v>180</v>
+      </c>
+      <c r="B182">
+        <v>-0.00134914624504745</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183">
+        <v>181</v>
+      </c>
+      <c r="B183">
+        <v>-0.0002620057784952223</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184">
+        <v>182</v>
+      </c>
+      <c r="B184">
+        <v>-1.969383447431028E-05</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185">
+        <v>183</v>
+      </c>
+      <c r="B185">
+        <v>0.0005761536885984242</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186">
+        <v>184</v>
+      </c>
+      <c r="B186">
+        <v>0.0005542213912121952</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187">
+        <v>185</v>
+      </c>
+      <c r="B187">
+        <v>0.000284509762423113</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188">
+        <v>186</v>
+      </c>
+      <c r="B188">
+        <v>0.001273997128009796</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>187</v>
+      </c>
+      <c r="B189">
+        <v>0.001093907281756401</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>188</v>
+      </c>
+      <c r="B190">
+        <v>0.0004772529937326908</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>189</v>
+      </c>
+      <c r="B191">
+        <v>0.0001935862383106723</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>190</v>
+      </c>
+      <c r="B192">
+        <v>0.001174019882455468</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>191</v>
+      </c>
+      <c r="B193">
+        <v>0.0001735964033287019</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>192</v>
+      </c>
+      <c r="B194">
+        <v>-0.0007406321237795055</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>193</v>
+      </c>
+      <c r="B195">
+        <v>-0.0007901520002633333</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>194</v>
+      </c>
+      <c r="B196">
+        <v>0.002164196688681841</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>195</v>
+      </c>
+      <c r="B197">
+        <v>0.000136628485051915</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>196</v>
+      </c>
+      <c r="B198">
+        <v>0.0007250094204209745</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>197</v>
+      </c>
+      <c r="B199">
+        <v>0.0004670202906709164</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>198</v>
+      </c>
+      <c r="B200">
+        <v>0.000114058238978032</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>199</v>
+      </c>
+      <c r="B201">
+        <v>0.0006254430627450347</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202">
+        <v>200</v>
+      </c>
+      <c r="B202">
+        <v>0.0001166631918749772</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203">
+        <v>201</v>
+      </c>
+      <c r="B203">
+        <v>0.0001597534428583458</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204">
+        <v>202</v>
+      </c>
+      <c r="B204">
+        <v>0.0007706194883212447</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205">
+        <v>203</v>
+      </c>
+      <c r="B205">
+        <v>0.0004574478371068835</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206">
+        <v>204</v>
+      </c>
+      <c r="B206">
+        <v>5.580415381700732E-05</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207">
+        <v>205</v>
+      </c>
+      <c r="B207">
+        <v>0.0003235842741560191</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208">
+        <v>206</v>
+      </c>
+      <c r="B208">
+        <v>-0.0007942062802612782</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209">
+        <v>207</v>
+      </c>
+      <c r="B209">
+        <v>-0.000173920692759566</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210">
+        <v>208</v>
+      </c>
+      <c r="B210">
+        <v>0.0003461618325673044</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211">
+        <v>209</v>
+      </c>
+      <c r="B211">
+        <v>0.000117828109068796</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212">
+        <v>210</v>
+      </c>
+      <c r="B212">
+        <v>0.0007844942738302052</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213">
+        <v>211</v>
+      </c>
+      <c r="B213">
+        <v>0.0003451186348684132</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214">
+        <v>212</v>
+      </c>
+      <c r="B214">
+        <v>0.0004811672260984778</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215">
+        <v>213</v>
+      </c>
+      <c r="B215">
+        <v>0.0003778742393478751</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216">
+        <v>214</v>
+      </c>
+      <c r="B216">
+        <v>0.0003326826845295727</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217">
+        <v>215</v>
+      </c>
+      <c r="B217">
+        <v>0.0006473585963249207</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218">
+        <v>216</v>
+      </c>
+      <c r="B218">
+        <v>0.0007395833963528275</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219">
+        <v>217</v>
+      </c>
+      <c r="B219">
+        <v>-2.757190316060587E-07</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220">
+        <v>218</v>
+      </c>
+      <c r="B220">
+        <v>0.0005452937330119312</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221">
+        <v>219</v>
+      </c>
+      <c r="B221">
+        <v>-0.003094425890594721</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222">
+        <v>220</v>
+      </c>
+      <c r="B222">
+        <v>0.001038786140270531</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223">
+        <v>221</v>
+      </c>
+      <c r="B223">
+        <v>-0.0002925538865383714</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224">
+        <v>222</v>
+      </c>
+      <c r="B224">
+        <v>0.001227024360559881</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225">
+        <v>223</v>
+      </c>
+      <c r="B225">
+        <v>0.0003276687930338085</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226">
+        <v>224</v>
+      </c>
+      <c r="B226">
+        <v>0.0006139536271803081</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227">
+        <v>225</v>
+      </c>
+      <c r="B227">
+        <v>0.0008055393700487912</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228">
+        <v>226</v>
+      </c>
+      <c r="B228">
+        <v>-2.196037348767277E-05</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229">
+        <v>227</v>
+      </c>
+      <c r="B229">
+        <v>0.0008284291252493858</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230">
+        <v>228</v>
+      </c>
+      <c r="B230">
+        <v>0.0008740535704419017</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231">
+        <v>229</v>
+      </c>
+      <c r="B231">
+        <v>0.0005493093049153686</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232">
+        <v>230</v>
+      </c>
+      <c r="B232">
+        <v>0.0002189969818573445</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233">
+        <v>231</v>
+      </c>
+      <c r="B233">
+        <v>4.55403933301568E-05</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234">
+        <v>232</v>
+      </c>
+      <c r="B234">
+        <v>0.0004863087378907949</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235">
+        <v>233</v>
+      </c>
+      <c r="B235">
+        <v>0.0007054696325212717</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236">
+        <v>234</v>
+      </c>
+      <c r="B236">
+        <v>0.0001124247210100293</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237">
+        <v>235</v>
+      </c>
+      <c r="B237">
+        <v>0.0005767663242295384</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238">
+        <v>236</v>
+      </c>
+      <c r="B238">
+        <v>0.0009011166403070092</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239">
+        <v>237</v>
+      </c>
+      <c r="B239">
+        <v>0.0001338117144769058</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240">
+        <v>238</v>
+      </c>
+      <c r="B240">
+        <v>-0.0002284818328917027</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241">
+        <v>239</v>
+      </c>
+      <c r="B241">
+        <v>0.001742166699841619</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242">
+        <v>240</v>
+      </c>
+      <c r="B242">
+        <v>0.0001316555717494339</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243">
+        <v>241</v>
+      </c>
+      <c r="B243">
+        <v>6.892627425258979E-05</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244">
+        <v>242</v>
+      </c>
+      <c r="B244">
+        <v>0.0004083765670657158</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245">
+        <v>243</v>
+      </c>
+      <c r="B245">
+        <v>0.0001719845167826861</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246">
+        <v>244</v>
+      </c>
+      <c r="B246">
+        <v>0.0004234143998473883</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247">
+        <v>245</v>
+      </c>
+      <c r="B247">
+        <v>0.003327688435092568</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248">
+        <v>246</v>
+      </c>
+      <c r="B248">
+        <v>0.0005120380665175617</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249">
+        <v>247</v>
+      </c>
+      <c r="B249">
+        <v>-1.225407322635874E-05</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250">
+        <v>248</v>
+      </c>
+      <c r="B250">
+        <v>0.0003973078273702413</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251">
+        <v>249</v>
+      </c>
+      <c r="B251">
+        <v>0.0002564852766226977</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252">
+        <v>250</v>
+      </c>
+      <c r="B252">
+        <v>0.0004119948134757578</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253">
+        <v>251</v>
+      </c>
+      <c r="B253">
+        <v>0.0007469646516256034</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254">
+        <v>252</v>
+      </c>
+      <c r="B254">
+        <v>0.0001244643062818795</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255">
+        <v>253</v>
+      </c>
+      <c r="B255">
+        <v>0.0002121753350365907</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256">
+        <v>254</v>
+      </c>
+      <c r="B256">
+        <v>-3.015447691723239E-05</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257">
+        <v>255</v>
+      </c>
+      <c r="B257">
+        <v>5.846432759426534E-05</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258">
+        <v>256</v>
+      </c>
+      <c r="B258">
+        <v>0.0004868459072895348</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259">
+        <v>257</v>
+      </c>
+      <c r="B259">
+        <v>0.000213311956031248</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260">
+        <v>258</v>
+      </c>
+      <c r="B260">
+        <v>0.001796047436073422</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261">
+        <v>259</v>
+      </c>
+      <c r="B261">
+        <v>-0.0002363468229304999</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262">
+        <v>260</v>
+      </c>
+      <c r="B262">
+        <v>0.0006495811976492405</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263">
+        <v>261</v>
+      </c>
+      <c r="B263">
+        <v>0.000237780244788155</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264">
+        <v>262</v>
+      </c>
+      <c r="B264">
+        <v>-4.518426794675179E-05</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265">
+        <v>263</v>
+      </c>
+      <c r="B265">
+        <v>0.000246658775722608</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266">
+        <v>264</v>
+      </c>
+      <c r="B266">
+        <v>0.0007026990642771125</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267">
+        <v>265</v>
+      </c>
+      <c r="B267">
+        <v>0.0004644107830245048</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268">
+        <v>266</v>
+      </c>
+      <c r="B268">
+        <v>0.0005325304809957743</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269">
+        <v>267</v>
+      </c>
+      <c r="B269">
+        <v>0.0009873543167486787</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270">
+        <v>268</v>
+      </c>
+      <c r="B270">
+        <v>0.0002080319536617026</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271">
+        <v>269</v>
+      </c>
+      <c r="B271">
+        <v>0.0004647566238418221</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272">
+        <v>270</v>
+      </c>
+      <c r="B272">
+        <v>-0.000591397110838443</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273">
+        <v>271</v>
+      </c>
+      <c r="B273">
+        <v>0.00131001346744597</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274">
+        <v>272</v>
+      </c>
+      <c r="B274">
+        <v>0.0006880687433294952</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275">
+        <v>273</v>
+      </c>
+      <c r="B275">
+        <v>0.0004198215901851654</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276">
+        <v>274</v>
+      </c>
+      <c r="B276">
+        <v>0.0004873470461461693</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277">
+        <v>275</v>
+      </c>
+      <c r="B277">
+        <v>0.0006844968884252012</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278">
+        <v>276</v>
+      </c>
+      <c r="B278">
+        <v>0.0001692756777629256</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279">
+        <v>277</v>
+      </c>
+      <c r="B279">
+        <v>0.0004821646434720606</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280">
+        <v>278</v>
+      </c>
+      <c r="B280">
+        <v>0.000108462612843141</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281">
+        <v>279</v>
+      </c>
+      <c r="B281">
+        <v>0.0004876565362792462</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282">
+        <v>280</v>
+      </c>
+      <c r="B282">
+        <v>0.0003341819974593818</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283">
+        <v>281</v>
+      </c>
+      <c r="B283">
+        <v>0.0004880147171206772</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284">
+        <v>282</v>
+      </c>
+      <c r="B284">
+        <v>0.000200470196432434</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285">
+        <v>283</v>
+      </c>
+      <c r="B285">
+        <v>-0.0005376584595069289</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286">
+        <v>284</v>
+      </c>
+      <c r="B286">
+        <v>0.001309811370447278</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287">
+        <v>285</v>
+      </c>
+      <c r="B287">
+        <v>0.0005699914763681591</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288">
+        <v>286</v>
+      </c>
+      <c r="B288">
+        <v>0.0008515105000697076</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289">
+        <v>287</v>
+      </c>
+      <c r="B289">
+        <v>0.0002937376848421991</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290">
+        <v>288</v>
+      </c>
+      <c r="B290">
+        <v>0.0001130255404859781</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291">
+        <v>289</v>
+      </c>
+      <c r="B291">
+        <v>7.421723694278626E-06</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292">
+        <v>290</v>
+      </c>
+      <c r="B292">
+        <v>0.001030631014145911</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293">
+        <v>291</v>
+      </c>
+      <c r="B293">
+        <v>0.0002295260055689141</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294">
+        <v>292</v>
+      </c>
+      <c r="B294">
+        <v>5.348710692487657E-05</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295">
+        <v>293</v>
+      </c>
+      <c r="B295">
+        <v>0.0006838269764557481</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296">
+        <v>294</v>
+      </c>
+      <c r="B296">
+        <v>0.0002714634465519339</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297">
+        <v>295</v>
+      </c>
+      <c r="B297">
+        <v>0.0001592870830791071</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298">
+        <v>296</v>
+      </c>
+      <c r="B298">
+        <v>0.0001770291419234127</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299">
+        <v>297</v>
+      </c>
+      <c r="B299">
+        <v>-0.001360433991067111</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300">
+        <v>298</v>
+      </c>
+      <c r="B300">
+        <v>-8.60449654283002E-05</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301">
+        <v>299</v>
+      </c>
+      <c r="B301">
+        <v>0.0006882960442453623</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302">
+        <v>300</v>
+      </c>
+      <c r="B302">
+        <v>0.0001227627799380571</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303">
+        <v>301</v>
+      </c>
+      <c r="B303">
+        <v>0.0002061846753349528</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304">
+        <v>302</v>
+      </c>
+      <c r="B304">
+        <v>0.0004103545506950468</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305">
+        <v>303</v>
+      </c>
+      <c r="B305">
+        <v>0.0006276507047004998</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306">
+        <v>304</v>
+      </c>
+      <c r="B306">
+        <v>0.0002818387001752853</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307">
+        <v>305</v>
+      </c>
+      <c r="B307">
+        <v>0.0002832429308909923</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308">
+        <v>306</v>
+      </c>
+      <c r="B308">
+        <v>-0.0004198413225822151</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309">
+        <v>307</v>
+      </c>
+      <c r="B309">
+        <v>0.000555274251382798</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310">
+        <v>308</v>
+      </c>
+      <c r="B310">
+        <v>0.0002703386708162725</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311">
+        <v>309</v>
+      </c>
+      <c r="B311">
+        <v>-0.0002845692506525666</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312">
+        <v>310</v>
+      </c>
+      <c r="B312">
+        <v>0.0001101285015465692</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313">
+        <v>311</v>
+      </c>
+      <c r="B313">
+        <v>0.0001342028845101595</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314">
+        <v>312</v>
+      </c>
+      <c r="B314">
+        <v>0.001221777871251106</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315">
+        <v>313</v>
+      </c>
+      <c r="B315">
+        <v>0.0005793697782792151</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316">
+        <v>314</v>
+      </c>
+      <c r="B316">
+        <v>0.0004337677964940667</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317">
+        <v>315</v>
+      </c>
+      <c r="B317">
+        <v>0.0003821379505097866</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318">
+        <v>316</v>
+      </c>
+      <c r="B318">
+        <v>0.00128214294090867</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319">
+        <v>317</v>
+      </c>
+      <c r="B319">
+        <v>-0.0003291339962743223</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320">
+        <v>318</v>
+      </c>
+      <c r="B320">
+        <v>0.0003290569293312728</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321">
+        <v>319</v>
+      </c>
+      <c r="B321">
+        <v>0.0009239076753146946</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322">
+        <v>320</v>
+      </c>
+      <c r="B322">
+        <v>0.0002975138486362994</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323">
+        <v>321</v>
+      </c>
+      <c r="B323">
+        <v>-4.391273614601232E-05</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324">
+        <v>322</v>
+      </c>
+      <c r="B324">
+        <v>-0.0005088263424113393</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325">
+        <v>323</v>
+      </c>
+      <c r="B325">
+        <v>-0.001450709998607635</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326">
+        <v>324</v>
+      </c>
+      <c r="B326">
+        <v>-0.0002707838430069387</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327">
+        <v>325</v>
+      </c>
+      <c r="B327">
+        <v>0.0007855986477807164</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328">
+        <v>326</v>
+      </c>
+      <c r="B328">
+        <v>0.0004545445844996721</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329">
+        <v>327</v>
+      </c>
+      <c r="B329">
+        <v>0.0004458039766177535</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330">
+        <v>328</v>
+      </c>
+      <c r="B330">
+        <v>0.0001418634492438287</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331">
+        <v>329</v>
+      </c>
+      <c r="B331">
+        <v>0.0003269285953138024</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332">
+        <v>330</v>
+      </c>
+      <c r="B332">
+        <v>0.001016110996715724</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333">
+        <v>331</v>
+      </c>
+      <c r="B333">
+        <v>0.0009545365464873612</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334">
+        <v>332</v>
+      </c>
+      <c r="B334">
+        <v>0.0007177853840403259</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335">
+        <v>333</v>
+      </c>
+      <c r="B335">
+        <v>0.0006715941126458347</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336">
+        <v>334</v>
+      </c>
+      <c r="B336">
+        <v>0.0004537999338936061</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337">
+        <v>335</v>
+      </c>
+      <c r="B337">
+        <v>0.001734283054247499</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338">
+        <v>336</v>
+      </c>
+      <c r="B338">
+        <v>0.001360425492748618</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339">
+        <v>337</v>
+      </c>
+      <c r="B339">
+        <v>0.0001930837461259216</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340">
+        <v>338</v>
+      </c>
+      <c r="B340">
+        <v>0.001025581732392311</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341">
+        <v>339</v>
+      </c>
+      <c r="B341">
+        <v>-0.0003135410370305181</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342">
+        <v>340</v>
+      </c>
+      <c r="B342">
+        <v>0.0009924381738528609</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343">
+        <v>341</v>
+      </c>
+      <c r="B343">
+        <v>0.0006640130304731429</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344">
+        <v>342</v>
+      </c>
+      <c r="B344">
+        <v>0.0003492944233585149</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345">
+        <v>343</v>
+      </c>
+      <c r="B345">
+        <v>0.001062938245013356</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346">
+        <v>344</v>
+      </c>
+      <c r="B346">
+        <v>0.0001787435612641275</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347">
+        <v>345</v>
+      </c>
+      <c r="B347">
+        <v>0.0003739925159607083</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348">
+        <v>346</v>
+      </c>
+      <c r="B348">
+        <v>0.0003241060767322779</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349">
+        <v>347</v>
+      </c>
+      <c r="B349">
+        <v>0.0003961760958191007</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350">
+        <v>348</v>
+      </c>
+      <c r="B350">
+        <v>0.0008734966395422816</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351">
+        <v>349</v>
+      </c>
+      <c r="B351">
+        <v>0.0005817447090521455</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352">
+        <v>350</v>
+      </c>
+      <c r="B352">
+        <v>0.001120925298891962</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353">
+        <v>351</v>
+      </c>
+      <c r="B353">
+        <v>0.0003206293331459165</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354">
+        <v>352</v>
+      </c>
+      <c r="B354">
+        <v>0.0004156673676334321</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355">
+        <v>353</v>
+      </c>
+      <c r="B355">
+        <v>0.0004486718098632991</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356">
+        <v>354</v>
+      </c>
+      <c r="B356">
+        <v>0.0004170403117313981</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357">
+        <v>355</v>
+      </c>
+      <c r="B357">
+        <v>0.001000292017124593</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358">
+        <v>356</v>
+      </c>
+      <c r="B358">
+        <v>0.0001720607106108218</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359">
+        <v>357</v>
+      </c>
+      <c r="B359">
+        <v>0.0001018308394122869</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360">
+        <v>358</v>
+      </c>
+      <c r="B360">
+        <v>0.0005772833828814328</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361">
+        <v>359</v>
+      </c>
+      <c r="B361">
+        <v>-0.0002134131354978308</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362">
+        <v>360</v>
+      </c>
+      <c r="B362">
+        <v>6.204660894582048E-05</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363">
+        <v>361</v>
+      </c>
+      <c r="B363">
+        <v>0.00249574170447886</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364">
+        <v>362</v>
+      </c>
+      <c r="B364">
+        <v>-2.415277413092554E-05</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365">
+        <v>363</v>
+      </c>
+      <c r="B365">
+        <v>-0.001187219051644206</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366">
+        <v>364</v>
+      </c>
+      <c r="B366">
+        <v>0.0005275597795844078</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367">
+        <v>365</v>
+      </c>
+      <c r="B367">
+        <v>0.0009027677588164806</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368">
+        <v>366</v>
+      </c>
+      <c r="B368">
+        <v>0.000142055272590369</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369">
+        <v>367</v>
+      </c>
+      <c r="B369">
+        <v>0.0009772303747013211</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370">
+        <v>368</v>
+      </c>
+      <c r="B370">
+        <v>-2.636730641825125E-05</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371">
+        <v>369</v>
+      </c>
+      <c r="B371">
+        <v>6.687325367238373E-05</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372">
+        <v>370</v>
+      </c>
+      <c r="B372">
+        <v>0.0006032747915014625</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373">
+        <v>371</v>
+      </c>
+      <c r="B373">
+        <v>0.0004897002363577485</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374">
+        <v>372</v>
+      </c>
+      <c r="B374">
+        <v>0.0005823958781547844</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375">
+        <v>373</v>
+      </c>
+      <c r="B375">
+        <v>0.0001543357211630791</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376">
+        <v>374</v>
+      </c>
+      <c r="B376">
+        <v>0.001238846103660762</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377">
+        <v>375</v>
+      </c>
+      <c r="B377">
+        <v>0.003420892637223005</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378">
+        <v>376</v>
+      </c>
+      <c r="B378">
+        <v>-2.302148641319945E-05</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379">
+        <v>377</v>
+      </c>
+      <c r="B379">
+        <v>3.734253186848946E-05</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380">
+        <v>378</v>
+      </c>
+      <c r="B380">
+        <v>0.000463073403807357</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381">
+        <v>379</v>
+      </c>
+      <c r="B381">
+        <v>0.0003110826946794987</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382">
+        <v>380</v>
+      </c>
+      <c r="B382">
+        <v>0.000830852601211518</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383">
+        <v>381</v>
+      </c>
+      <c r="B383">
+        <v>-9.687048077466898E-06</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384">
+        <v>382</v>
+      </c>
+      <c r="B384">
+        <v>0.0003203636442776769</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385">
+        <v>383</v>
+      </c>
+      <c r="B385">
+        <v>0.0004898751503787935</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386">
+        <v>384</v>
+      </c>
+      <c r="B386">
+        <v>0.0004302284214645624</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387">
+        <v>385</v>
+      </c>
+      <c r="B387">
+        <v>0.001077153137885034</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388">
+        <v>386</v>
+      </c>
+      <c r="B388">
+        <v>0.001105376635678113</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389">
+        <v>387</v>
+      </c>
+      <c r="B389">
+        <v>0.001113577745854855</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390">
+        <v>388</v>
+      </c>
+      <c r="B390">
+        <v>0.0007499218918383121</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391">
+        <v>389</v>
+      </c>
+      <c r="B391">
+        <v>0.001062884228304029</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392">
+        <v>390</v>
+      </c>
+      <c r="B392">
+        <v>0.000253869075095281</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393">
+        <v>391</v>
+      </c>
+      <c r="B393">
+        <v>0.001178232720121741</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394">
+        <v>392</v>
+      </c>
+      <c r="B394">
+        <v>0.0008862880058586597</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395">
+        <v>393</v>
+      </c>
+      <c r="B395">
+        <v>0.000280120613751933</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396">
+        <v>394</v>
+      </c>
+      <c r="B396">
+        <v>0.0004506420518737286</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397">
+        <v>395</v>
+      </c>
+      <c r="B397">
+        <v>0.0001646294549573213</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398">
+        <v>396</v>
+      </c>
+      <c r="B398">
+        <v>0.0001769176451489329</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399">
+        <v>397</v>
+      </c>
+      <c r="B399">
+        <v>0.0001386283693136647</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400">
+        <v>398</v>
+      </c>
+      <c r="B400">
+        <v>2.02038063434884E-05</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401">
+        <v>399</v>
+      </c>
+      <c r="B401">
+        <v>0.0004190793551970273</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402">
+        <v>400</v>
+      </c>
+      <c r="B402">
+        <v>-0.0003069812955800444</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403">
+        <v>401</v>
+      </c>
+      <c r="B403">
+        <v>0.0002632405085023493</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404">
+        <v>402</v>
+      </c>
+      <c r="B404">
+        <v>0.0008458081865683198</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405">
+        <v>403</v>
+      </c>
+      <c r="B405">
+        <v>0.000955380906816572</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406">
+        <v>404</v>
+      </c>
+      <c r="B406">
+        <v>-0.0003424918686505407</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407">
+        <v>405</v>
+      </c>
+      <c r="B407">
+        <v>0.001656411681324244</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408">
+        <v>406</v>
+      </c>
+      <c r="B408">
+        <v>0.001021667383611202</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409">
+        <v>407</v>
+      </c>
+      <c r="B409">
+        <v>-6.026952905813232E-05</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410">
+        <v>408</v>
+      </c>
+      <c r="B410">
+        <v>0.0004581270331982523</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411">
+        <v>409</v>
+      </c>
+      <c r="B411">
+        <v>6.166002276586369E-05</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412">
+        <v>410</v>
+      </c>
+      <c r="B412">
+        <v>0.001682420843280852</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413">
+        <v>411</v>
+      </c>
+      <c r="B413">
+        <v>0.0004318998253438622</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414">
+        <v>412</v>
+      </c>
+      <c r="B414">
+        <v>0.0005039364914409816</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415">
+        <v>413</v>
+      </c>
+      <c r="B415">
+        <v>-0.0003350848564878106</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416">
+        <v>414</v>
+      </c>
+      <c r="B416">
+        <v>0.0004177377850282937</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417">
+        <v>415</v>
+      </c>
+      <c r="B417">
+        <v>0.0004228616016916931</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418">
+        <v>416</v>
+      </c>
+      <c r="B418">
+        <v>0.0006661455845460296</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419">
+        <v>417</v>
+      </c>
+      <c r="B419">
+        <v>0.0007085514371283352</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420">
+        <v>418</v>
+      </c>
+      <c r="B420">
+        <v>0.0004830533289350569</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421">
+        <v>419</v>
+      </c>
+      <c r="B421">
+        <v>0.0002623998443596065</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422">
+        <v>420</v>
+      </c>
+      <c r="B422">
+        <v>0.001078249420970678</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423">
+        <v>421</v>
+      </c>
+      <c r="B423">
+        <v>-8.393578173127025E-05</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424">
+        <v>422</v>
+      </c>
+      <c r="B424">
+        <v>0.0007988261058926582</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425">
+        <v>423</v>
+      </c>
+      <c r="B425">
+        <v>0.000186146775376983</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426">
+        <v>424</v>
+      </c>
+      <c r="B426">
+        <v>0.001293809269554913</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427">
+        <v>425</v>
+      </c>
+      <c r="B427">
+        <v>-0.0004385387874208391</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428">
+        <v>426</v>
+      </c>
+      <c r="B428">
+        <v>0.001572105335071683</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429">
+        <v>427</v>
+      </c>
+      <c r="B429">
+        <v>0.001381911570206285</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430">
+        <v>428</v>
+      </c>
+      <c r="B430">
+        <v>0.0005684368661604822</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431">
+        <v>429</v>
+      </c>
+      <c r="B431">
+        <v>0.0002047349116764963</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432">
+        <v>430</v>
+      </c>
+      <c r="B432">
+        <v>0.0005094754160381854</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433">
+        <v>431</v>
+      </c>
+      <c r="B433">
+        <v>0.0003647751873359084</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434">
+        <v>432</v>
+      </c>
+      <c r="B434">
+        <v>0.0005492219934239984</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435">
+        <v>433</v>
+      </c>
+      <c r="B435">
+        <v>0.0005089092301204801</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436">
+        <v>434</v>
+      </c>
+      <c r="B436">
+        <v>0.0003865622857119888</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437">
+        <v>435</v>
+      </c>
+      <c r="B437">
+        <v>0.0008496902883052826</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438">
+        <v>436</v>
+      </c>
+      <c r="B438">
+        <v>0.001679484732449055</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439">
+        <v>437</v>
+      </c>
+      <c r="B439">
+        <v>-4.982293103239499E-05</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440">
+        <v>438</v>
+      </c>
+      <c r="B440">
+        <v>0.001756691024638712</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441">
+        <v>439</v>
+      </c>
+      <c r="B441">
+        <v>0.003517723176628351</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442">
+        <v>440</v>
+      </c>
+      <c r="B442">
+        <v>0.0005392007878981531</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443">
+        <v>441</v>
+      </c>
+      <c r="B443">
+        <v>0.0007267032633535564</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444">
+        <v>442</v>
+      </c>
+      <c r="B444">
+        <v>0.0004908139817416668</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445">
+        <v>443</v>
+      </c>
+      <c r="B445">
+        <v>0.0005710565019398928</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446">
+        <v>444</v>
+      </c>
+      <c r="B446">
+        <v>0.0001025673627736978</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447">
+        <v>445</v>
+      </c>
+      <c r="B447">
+        <v>0.0003851205401588231</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448">
+        <v>446</v>
+      </c>
+      <c r="B448">
+        <v>0.0003071651444770396</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449">
+        <v>447</v>
+      </c>
+      <c r="B449">
+        <v>0.000316808553179726</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450">
+        <v>448</v>
+      </c>
+      <c r="B450">
+        <v>0.0005678238230757415</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451">
+        <v>449</v>
+      </c>
+      <c r="B451">
+        <v>-0.0004383257764857262</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452">
+        <v>450</v>
+      </c>
+      <c r="B452">
+        <v>-0.0001189509785035625</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453">
+        <v>451</v>
+      </c>
+      <c r="B453">
+        <v>0.0001154566489276476</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454">
+        <v>452</v>
+      </c>
+      <c r="B454">
+        <v>-0.001380293047986925</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455">
+        <v>453</v>
+      </c>
+      <c r="B455">
+        <v>-0.0006060799933038652</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456">
+        <v>454</v>
+      </c>
+      <c r="B456">
+        <v>0.0007830990944057703</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457">
+        <v>455</v>
+      </c>
+      <c r="B457">
+        <v>0.0004956662887707353</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458">
+        <v>456</v>
+      </c>
+      <c r="B458">
+        <v>0.0007278021075762808</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459">
+        <v>457</v>
+      </c>
+      <c r="B459">
+        <v>0.0005810234579257667</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460">
+        <v>458</v>
+      </c>
+      <c r="B460">
+        <v>0.0001435302838217467</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461">
+        <v>459</v>
+      </c>
+      <c r="B461">
+        <v>0.001031572697684169</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462">
+        <v>460</v>
+      </c>
+      <c r="B462">
+        <v>0.000374938128516078</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463">
+        <v>461</v>
+      </c>
+      <c r="B463">
+        <v>0.001655680709518492</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464">
+        <v>462</v>
+      </c>
+      <c r="B464">
+        <v>0.0002212152758147568</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465">
+        <v>463</v>
+      </c>
+      <c r="B465">
+        <v>-0.0002979733981192112</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466">
+        <v>464</v>
+      </c>
+      <c r="B466">
+        <v>0.0006096732686273754</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467">
+        <v>465</v>
+      </c>
+      <c r="B467">
+        <v>0.0005603595054708421</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468">
+        <v>466</v>
+      </c>
+      <c r="B468">
+        <v>0.001158679835498333</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469">
+        <v>467</v>
+      </c>
+      <c r="B469">
+        <v>0.0005805504624731839</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470">
+        <v>468</v>
+      </c>
+      <c r="B470">
+        <v>0.001411676872521639</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471">
+        <v>469</v>
+      </c>
+      <c r="B471">
+        <v>0.0004421829653438181</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2">
+      <c r="A472">
+        <v>470</v>
+      </c>
+      <c r="B472">
+        <v>0.0004184570570942014</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2">
+      <c r="A473">
+        <v>471</v>
+      </c>
+      <c r="B473">
+        <v>8.873947081156075E-05</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2">
+      <c r="A474">
+        <v>472</v>
+      </c>
+      <c r="B474">
+        <v>0.0002105429739458486</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2">
+      <c r="A475">
+        <v>473</v>
+      </c>
+      <c r="B475">
+        <v>0.0002635600685607642</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2">
+      <c r="A476">
+        <v>474</v>
+      </c>
+      <c r="B476">
+        <v>0.0003899000876117498</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2">
+      <c r="A477">
+        <v>475</v>
+      </c>
+      <c r="B477">
+        <v>0.0002960146521218121</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2">
+      <c r="A478">
+        <v>476</v>
+      </c>
+      <c r="B478">
+        <v>0.0009607017273083329</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2">
+      <c r="A479">
+        <v>477</v>
+      </c>
+      <c r="B479">
+        <v>0.001073858002200723</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2">
+      <c r="A480">
+        <v>478</v>
+      </c>
+      <c r="B480">
+        <v>0.006144615821540356</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2">
+      <c r="A481">
+        <v>479</v>
+      </c>
+      <c r="B481">
+        <v>0.0006061073509044945</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2">
+      <c r="A482">
+        <v>480</v>
+      </c>
+      <c r="B482">
+        <v>0.0001091602462111041</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2">
+      <c r="A483">
+        <v>481</v>
+      </c>
+      <c r="B483">
+        <v>0.0006084103370085359</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2">
+      <c r="A484">
+        <v>482</v>
+      </c>
+      <c r="B484">
+        <v>0.0003942572511732578</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2">
+      <c r="A485">
+        <v>483</v>
+      </c>
+      <c r="B485">
+        <v>0.0005569977220147848</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2">
+      <c r="A486">
+        <v>484</v>
+      </c>
+      <c r="B486">
+        <v>-2.317381949978881E-05</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2">
+      <c r="A487">
+        <v>485</v>
+      </c>
+      <c r="B487">
+        <v>0.0003992054844275117</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2">
+      <c r="A488">
+        <v>486</v>
+      </c>
+      <c r="B488">
+        <v>0.0002449634484946728</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2">
+      <c r="A489">
+        <v>487</v>
+      </c>
+      <c r="B489">
+        <v>0.0009343289420939982</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2">
+      <c r="A490">
+        <v>488</v>
+      </c>
+      <c r="B490">
+        <v>0.0002854421618394554</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2">
+      <c r="A491">
+        <v>489</v>
+      </c>
+      <c r="B491">
+        <v>0.0004789935483131558</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2">
+      <c r="A492">
+        <v>490</v>
+      </c>
+      <c r="B492">
+        <v>0.0003631979343481362</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2">
+      <c r="A493">
+        <v>491</v>
+      </c>
+      <c r="B493">
+        <v>0.001365966163575649</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2">
+      <c r="A494">
+        <v>492</v>
+      </c>
+      <c r="B494">
+        <v>0.0007048353436402977</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2">
+      <c r="A495">
+        <v>493</v>
+      </c>
+      <c r="B495">
+        <v>0.0005417497013695538</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2">
+      <c r="A496">
+        <v>494</v>
+      </c>
+      <c r="B496">
+        <v>0.0005628213402815163</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2">
+      <c r="A497">
+        <v>495</v>
+      </c>
+      <c r="B497">
+        <v>0.0006601646891795099</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2">
+      <c r="A498">
+        <v>496</v>
+      </c>
+      <c r="B498">
+        <v>0.0002702059864532202</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2">
+      <c r="A499">
+        <v>497</v>
+      </c>
+      <c r="B499">
+        <v>0.0001453298318665475</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2">
+      <c r="A500">
+        <v>498</v>
+      </c>
+      <c r="B500">
+        <v>0.0004694689123425633</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2">
+      <c r="A501">
+        <v>499</v>
+      </c>
+      <c r="B501">
+        <v>0.0004130384186282754</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2">
+      <c r="A502">
+        <v>500</v>
+      </c>
+      <c r="B502">
+        <v>0.0004054910386912525</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2">
+      <c r="A503">
+        <v>501</v>
+      </c>
+      <c r="B503">
+        <v>0.0006146387895569205</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2">
+      <c r="A504">
+        <v>502</v>
+      </c>
+      <c r="B504">
+        <v>0.001211875583976507</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2">
+      <c r="A505">
+        <v>503</v>
+      </c>
+      <c r="B505">
+        <v>0.001279512536711991</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2">
+      <c r="A506">
+        <v>504</v>
+      </c>
+      <c r="B506">
+        <v>-0.0008127255132421851</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2">
+      <c r="A507">
+        <v>505</v>
+      </c>
+      <c r="B507">
+        <v>0.00158016849309206</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2">
+      <c r="A508">
+        <v>506</v>
+      </c>
+      <c r="B508">
+        <v>0.0007576327188871801</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2">
+      <c r="A509">
+        <v>507</v>
+      </c>
+      <c r="B509">
+        <v>0.000372615730157122</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2">
+      <c r="A510">
+        <v>508</v>
+      </c>
+      <c r="B510">
+        <v>0.0007341656018979847</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2">
+      <c r="A511">
+        <v>509</v>
+      </c>
+      <c r="B511">
+        <v>-6.208770628290949E-06</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2">
+      <c r="A512">
+        <v>510</v>
+      </c>
+      <c r="B512">
+        <v>0.0003890063380822539</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2">
+      <c r="A513">
+        <v>511</v>
+      </c>
+      <c r="B513">
+        <v>0.0004684347077272832</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2">
+      <c r="A514">
+        <v>512</v>
+      </c>
+      <c r="B514">
+        <v>0.000159863440785557</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2">
+      <c r="A515">
+        <v>513</v>
+      </c>
+      <c r="B515">
+        <v>7.733261554676574E-06</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2">
+      <c r="A516">
+        <v>514</v>
+      </c>
+      <c r="B516">
+        <v>-8.331967546837404E-05</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2">
+      <c r="A517">
+        <v>515</v>
+      </c>
+      <c r="B517">
+        <v>6.064253102522343E-05</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2">
+      <c r="A518">
+        <v>516</v>
+      </c>
+      <c r="B518">
+        <v>0.0008797309710644186</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2">
+      <c r="A519">
+        <v>517</v>
+      </c>
+      <c r="B519">
+        <v>0.000383899750886485</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2">
+      <c r="A520">
+        <v>518</v>
+      </c>
+      <c r="B520">
+        <v>0.0006906645139679313</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2">
+      <c r="A521">
+        <v>519</v>
+      </c>
+      <c r="B521">
+        <v>0.0001282244775211439</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2">
+      <c r="A522">
+        <v>520</v>
+      </c>
+      <c r="B522">
+        <v>0.0005696400185115635</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2">
+      <c r="A523">
+        <v>521</v>
+      </c>
+      <c r="B523">
+        <v>0.0004825613868888468</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2">
+      <c r="A524">
+        <v>522</v>
+      </c>
+      <c r="B524">
+        <v>0.0008887556614354253</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2">
+      <c r="A525">
+        <v>523</v>
+      </c>
+      <c r="B525">
+        <v>0.001395054627209902</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2">
+      <c r="A526">
+        <v>524</v>
+      </c>
+      <c r="B526">
+        <v>0.001780818914994597</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2">
+      <c r="A527">
+        <v>525</v>
+      </c>
+      <c r="B527">
+        <v>0.0008256444125436246</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2">
+      <c r="A528">
+        <v>526</v>
+      </c>
+      <c r="B528">
+        <v>8.862232061801478E-05</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2">
+      <c r="A529">
+        <v>527</v>
+      </c>
+      <c r="B529">
+        <v>0.0002097799442708492</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2">
+      <c r="A530">
+        <v>528</v>
+      </c>
+      <c r="B530">
+        <v>0.0004511818988248706</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2">
+      <c r="A531">
+        <v>529</v>
+      </c>
+      <c r="B531">
+        <v>0.0003917430876754224</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2">
+      <c r="A532">
+        <v>530</v>
+      </c>
+      <c r="B532">
+        <v>0.0005587713676504791</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2">
+      <c r="A533">
+        <v>531</v>
+      </c>
+      <c r="B533">
+        <v>0.0002992749505210668</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2">
+      <c r="A534">
+        <v>532</v>
+      </c>
+      <c r="B534">
+        <v>0.000672602909617126</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2">
+      <c r="A535">
+        <v>533</v>
+      </c>
+      <c r="B535">
+        <v>0.000587761343922466</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2">
+      <c r="A536">
+        <v>534</v>
+      </c>
+      <c r="B536">
+        <v>0.0001526773703517392</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2">
+      <c r="A537">
+        <v>535</v>
+      </c>
+      <c r="B537">
+        <v>0.001082968316040933</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2">
+      <c r="A538">
+        <v>536</v>
+      </c>
+      <c r="B538">
+        <v>0.0009103751508519053</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2">
+      <c r="A539">
+        <v>537</v>
+      </c>
+      <c r="B539">
+        <v>0.003460605163127184</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2">
+      <c r="A540">
+        <v>538</v>
+      </c>
+      <c r="B540">
+        <v>0.0001437636674381793</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2">
+      <c r="A541">
+        <v>539</v>
+      </c>
+      <c r="B541">
+        <v>0.0003760520194191486</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2">
+      <c r="A542">
+        <v>540</v>
+      </c>
+      <c r="B542">
+        <v>0.0005890316097065806</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2">
+      <c r="A543">
+        <v>541</v>
+      </c>
+      <c r="B543">
+        <v>0.0001949436846189201</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2">
+      <c r="A544">
+        <v>542</v>
+      </c>
+      <c r="B544">
+        <v>0.0007379192975349724</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2">
+      <c r="A545">
+        <v>543</v>
+      </c>
+      <c r="B545">
+        <v>0.0001352516119368374</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2">
+      <c r="A546">
+        <v>544</v>
+      </c>
+      <c r="B546">
+        <v>0.0008253789856098592</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2">
+      <c r="A547">
+        <v>545</v>
+      </c>
+      <c r="B547">
+        <v>0.0005204864428378642</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2">
+      <c r="A548">
+        <v>546</v>
+      </c>
+      <c r="B548">
+        <v>0.00081212492659688</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2">
+      <c r="A549">
+        <v>547</v>
+      </c>
+      <c r="B549">
+        <v>0.0004308097413741052</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2">
+      <c r="A550">
+        <v>548</v>
+      </c>
+      <c r="B550">
+        <v>0.0005574178649112582</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2">
+      <c r="A551">
+        <v>549</v>
+      </c>
+      <c r="B551">
+        <v>0.0005315514863468707</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2">
+      <c r="A552">
+        <v>550</v>
+      </c>
+      <c r="B552">
+        <v>0.001417360850609839</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2">
+      <c r="A553">
+        <v>551</v>
+      </c>
+      <c r="B553">
+        <v>0.001224586158059537</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2">
+      <c r="A554">
+        <v>552</v>
+      </c>
+      <c r="B554">
+        <v>0.0003496086865197867</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2">
+      <c r="A555">
+        <v>553</v>
+      </c>
+      <c r="B555">
+        <v>0.0007043166551738977</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2">
+      <c r="A556">
+        <v>554</v>
+      </c>
+      <c r="B556">
+        <v>0.0006451270310208201</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2">
+      <c r="A557">
+        <v>555</v>
+      </c>
+      <c r="B557">
+        <v>0.0004292753001209348</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2">
+      <c r="A558">
+        <v>556</v>
+      </c>
+      <c r="B558">
+        <v>0.0009713473846204579</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2">
+      <c r="A559">
+        <v>557</v>
+      </c>
+      <c r="B559">
+        <v>0.0008008714066818357</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2">
+      <c r="A560">
+        <v>558</v>
+      </c>
+      <c r="B560">
+        <v>0.001008715364150703</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2">
+      <c r="A561">
+        <v>559</v>
+      </c>
+      <c r="B561">
+        <v>0.0002707664971239865</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2">
+      <c r="A562">
+        <v>560</v>
+      </c>
+      <c r="B562">
+        <v>4.191693369648419E-05</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2">
+      <c r="A563">
+        <v>561</v>
+      </c>
+      <c r="B563">
+        <v>0.0002006692666327581</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2">
+      <c r="A564">
+        <v>562</v>
+      </c>
+      <c r="B564">
+        <v>0.0001423075591446832</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2">
+      <c r="A565">
+        <v>563</v>
+      </c>
+      <c r="B565">
+        <v>0.00344367977231741</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2">
+      <c r="A566">
+        <v>564</v>
+      </c>
+      <c r="B566">
+        <v>0.0005164097528904676</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2">
+      <c r="A567">
+        <v>565</v>
+      </c>
+      <c r="B567">
+        <v>-0.0003254147013649344</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2">
+      <c r="A568">
+        <v>566</v>
+      </c>
+      <c r="B568">
+        <v>0.0002917399106081575</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2">
+      <c r="A569">
+        <v>567</v>
+      </c>
+      <c r="B569">
+        <v>0.0003627875121310353</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2">
+      <c r="A570">
+        <v>568</v>
+      </c>
+      <c r="B570">
+        <v>0.0002805153490044177</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2">
+      <c r="A571">
+        <v>569</v>
+      </c>
+      <c r="B571">
+        <v>0.0004698863485828042</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2">
+      <c r="A572">
+        <v>570</v>
+      </c>
+      <c r="B572">
+        <v>0.0004302834277041256</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2">
+      <c r="A573">
+        <v>571</v>
+      </c>
+      <c r="B573">
+        <v>0.000638444151263684</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2">
+      <c r="A574">
+        <v>572</v>
+      </c>
+      <c r="B574">
+        <v>0.0007461675559170544</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2">
+      <c r="A575">
+        <v>573</v>
+      </c>
+      <c r="B575">
+        <v>0.0005048636812716722</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2">
+      <c r="A576">
+        <v>574</v>
+      </c>
+      <c r="B576">
+        <v>0.000424734374973923</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2">
+      <c r="A577">
+        <v>575</v>
+      </c>
+      <c r="B577">
+        <v>0.001157479826360941</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2">
+      <c r="A578">
+        <v>576</v>
+      </c>
+      <c r="B578">
+        <v>0.002237500622868538</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2">
+      <c r="A579">
+        <v>577</v>
+      </c>
+      <c r="B579">
+        <v>0.0007746962364763021</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2">
+      <c r="A580">
+        <v>578</v>
+      </c>
+      <c r="B580">
+        <v>0.0004144613922107965</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2">
+      <c r="A581">
+        <v>579</v>
+      </c>
+      <c r="B581">
+        <v>0.001112944562919438</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2">
+      <c r="A582">
+        <v>580</v>
+      </c>
+      <c r="B582">
+        <v>0.001289751613512635</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2">
+      <c r="A583">
+        <v>581</v>
+      </c>
+      <c r="B583">
+        <v>0.0003734074416570365</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2">
+      <c r="A584">
+        <v>582</v>
+      </c>
+      <c r="B584">
+        <v>0.0002493719512131065</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2">
+      <c r="A585">
+        <v>583</v>
+      </c>
+      <c r="B585">
+        <v>0.0003636730252765119</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2">
+      <c r="A586">
+        <v>584</v>
+      </c>
+      <c r="B586">
+        <v>0.0003413756203372031</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2">
+      <c r="A587">
+        <v>585</v>
+      </c>
+      <c r="B587">
+        <v>0.0001902409421745688</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2">
+      <c r="A588">
+        <v>586</v>
+      </c>
+      <c r="B588">
+        <v>-0.0002808969584293664</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2">
+      <c r="A589">
+        <v>587</v>
+      </c>
+      <c r="B589">
+        <v>0.0002988033520523459</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2">
+      <c r="A590">
+        <v>588</v>
+      </c>
+      <c r="B590">
+        <v>0.000330488954205066</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2">
+      <c r="A591">
+        <v>589</v>
+      </c>
+      <c r="B591">
+        <v>0.002318172948434949</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2">
+      <c r="A592">
+        <v>590</v>
+      </c>
+      <c r="B592">
+        <v>0.0002508089528419077</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2">
+      <c r="A593">
+        <v>591</v>
+      </c>
+      <c r="B593">
+        <v>0.0004914677119813859</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2">
+      <c r="A594">
+        <v>592</v>
+      </c>
+      <c r="B594">
+        <v>0.0003984855429735035</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2">
+      <c r="A595">
+        <v>593</v>
+      </c>
+      <c r="B595">
+        <v>0.0005377188208512962</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2">
+      <c r="A596">
+        <v>594</v>
+      </c>
+      <c r="B596">
+        <v>0.0004895872552879155</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2">
+      <c r="A597">
+        <v>595</v>
+      </c>
+      <c r="B597">
+        <v>0.0005113246734254062</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2">
+      <c r="A598">
+        <v>596</v>
+      </c>
+      <c r="B598">
+        <v>0.0004453253641258925</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2">
+      <c r="A599">
+        <v>597</v>
+      </c>
+      <c r="B599">
+        <v>-9.98863106360659E-05</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2">
+      <c r="A600">
+        <v>598</v>
+      </c>
+      <c r="B600">
+        <v>0.0004033264121972024</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2">
+      <c r="A601">
+        <v>599</v>
+      </c>
+      <c r="B601">
+        <v>0.001188316382467747</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2">
+      <c r="A602">
+        <v>600</v>
+      </c>
+      <c r="B602">
+        <v>0.0009152176789939404</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2">
+      <c r="A603">
+        <v>601</v>
+      </c>
+      <c r="B603">
+        <v>0.001838358351960778</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2">
+      <c r="A604">
+        <v>602</v>
+      </c>
+      <c r="B604">
+        <v>0.008192100562155247</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2">
+      <c r="A605">
+        <v>603</v>
+      </c>
+      <c r="B605">
+        <v>0.0008478037198074162</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2">
+      <c r="A606">
+        <v>604</v>
+      </c>
+      <c r="B606">
+        <v>-0.0001990448654396459</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2">
+      <c r="A607">
+        <v>605</v>
+      </c>
+      <c r="B607">
+        <v>0.001051392056979239</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2">
+      <c r="A608">
+        <v>606</v>
+      </c>
+      <c r="B608">
+        <v>0.001344096264801919</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2">
+      <c r="A609">
+        <v>607</v>
+      </c>
+      <c r="B609">
+        <v>0.0002935595402959734</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2">
+      <c r="A610">
+        <v>608</v>
+      </c>
+      <c r="B610">
+        <v>0.0002116105606546625</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2">
+      <c r="A611">
+        <v>609</v>
+      </c>
+      <c r="B611">
+        <v>0.0003323637065477669</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2">
+      <c r="A612">
+        <v>610</v>
+      </c>
+      <c r="B612">
+        <v>0.0001317501009907573</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2">
+      <c r="A613">
+        <v>611</v>
+      </c>
+      <c r="B613">
+        <v>0.0005826291162520647</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2">
+      <c r="A614">
+        <v>612</v>
+      </c>
+      <c r="B614">
+        <v>0.0001334220287390053</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2">
+      <c r="A615">
+        <v>613</v>
+      </c>
+      <c r="B615">
+        <v>0.0007279086858034134</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2">
+      <c r="A616">
+        <v>614</v>
+      </c>
+      <c r="B616">
+        <v>0.0008639540174044669</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2">
+      <c r="A617">
+        <v>615</v>
+      </c>
+      <c r="B617">
+        <v>-0.001141938613727689</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2">
+      <c r="A618">
+        <v>616</v>
+      </c>
+      <c r="B618">
+        <v>0.0008936902158893645</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2">
+      <c r="A619">
+        <v>617</v>
+      </c>
+      <c r="B619">
+        <v>-0.0001502275408711284</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2">
+      <c r="A620">
+        <v>618</v>
+      </c>
+      <c r="B620">
+        <v>0.0003366016608197242</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2">
+      <c r="A621">
+        <v>619</v>
+      </c>
+      <c r="B621">
+        <v>0.001300632255151868</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2">
+      <c r="A622">
+        <v>620</v>
+      </c>
+      <c r="B622">
+        <v>-0.001073390361852944</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2">
+      <c r="A623">
+        <v>621</v>
+      </c>
+      <c r="B623">
+        <v>0.0007869085529819131</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2">
+      <c r="A624">
+        <v>622</v>
+      </c>
+      <c r="B624">
+        <v>0.0006807189784012735</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2">
+      <c r="A625">
+        <v>623</v>
+      </c>
+      <c r="B625">
+        <v>0.0008865120471455157</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2">
+      <c r="A626">
+        <v>624</v>
+      </c>
+      <c r="B626">
+        <v>0.0004532179445959628</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2">
+      <c r="A627">
+        <v>625</v>
+      </c>
+      <c r="B627">
+        <v>0.0003981415356975049</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2">
+      <c r="A628">
+        <v>626</v>
+      </c>
+      <c r="B628">
+        <v>0.0003992159035988152</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2">
+      <c r="A629">
+        <v>627</v>
+      </c>
+      <c r="B629">
+        <v>0.0004127750871703029</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2">
+      <c r="A630">
+        <v>628</v>
+      </c>
+      <c r="B630">
+        <v>-0.004373001400381327</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2">
+      <c r="A631">
+        <v>629</v>
+      </c>
+      <c r="B631">
+        <v>0.0004452642751857638</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2">
+      <c r="A632">
+        <v>630</v>
+      </c>
+      <c r="B632">
+        <v>0.001022982993163168</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2">
+      <c r="A633">
+        <v>631</v>
+      </c>
+      <c r="B633">
+        <v>0.000313274678774178</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2">
+      <c r="A634">
+        <v>632</v>
+      </c>
+      <c r="B634">
+        <v>0.001007692539133132</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2">
+      <c r="A635">
+        <v>633</v>
+      </c>
+      <c r="B635">
+        <v>0.000368149921996519</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2">
+      <c r="A636">
+        <v>634</v>
+      </c>
+      <c r="B636">
+        <v>0.0004534019972197711</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2">
+      <c r="A637">
+        <v>635</v>
+      </c>
+      <c r="B637">
+        <v>0.0004677193064708263</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2">
+      <c r="A638">
+        <v>636</v>
+      </c>
+      <c r="B638">
+        <v>0.0004892319557256997</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2">
+      <c r="A639">
+        <v>637</v>
+      </c>
+      <c r="B639">
+        <v>0.0002545894531067461</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2">
+      <c r="A640">
+        <v>638</v>
+      </c>
+      <c r="B640">
+        <v>0.0009320197277702391</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2">
+      <c r="A641">
+        <v>639</v>
+      </c>
+      <c r="B641">
+        <v>0.000887781847268343</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2">
+      <c r="A642">
+        <v>640</v>
+      </c>
+      <c r="B642">
+        <v>0.0005348217091523111</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2">
+      <c r="A643">
+        <v>641</v>
+      </c>
+      <c r="B643">
+        <v>-0.002986985025927424</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2">
+      <c r="A644">
+        <v>642</v>
+      </c>
+      <c r="B644">
+        <v>0.0002238446759292856</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2">
+      <c r="A645">
+        <v>643</v>
+      </c>
+      <c r="B645">
+        <v>0.001852046581916511</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2">
+      <c r="A646">
+        <v>644</v>
+      </c>
+      <c r="B646">
+        <v>0.0007477917824871838</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2">
+      <c r="A647">
+        <v>645</v>
+      </c>
+      <c r="B647">
+        <v>0.0001727770577417687</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2">
+      <c r="A648">
+        <v>646</v>
+      </c>
+      <c r="B648">
+        <v>-0.001550132175907493</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2">
+      <c r="A649">
+        <v>647</v>
+      </c>
+      <c r="B649">
+        <v>-0.0003569084510672837</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2">
+      <c r="A650">
+        <v>648</v>
+      </c>
+      <c r="B650">
+        <v>0.000694054295308888</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2">
+      <c r="A651">
+        <v>649</v>
+      </c>
+      <c r="B651">
+        <v>3.532278424245305E-05</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2">
+      <c r="A652">
+        <v>650</v>
+      </c>
+      <c r="B652">
+        <v>0.0001883090008050203</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2">
+      <c r="A653">
+        <v>651</v>
+      </c>
+      <c r="B653">
+        <v>0.000343223538948223</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2">
+      <c r="A654">
+        <v>652</v>
+      </c>
+      <c r="B654">
+        <v>-0.002358068944886327</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2">
+      <c r="A655">
+        <v>653</v>
+      </c>
+      <c r="B655">
+        <v>0.0009778556413948536</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2">
+      <c r="A656">
+        <v>654</v>
+      </c>
+      <c r="B656">
+        <v>-0.001251150504685938</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2">
+      <c r="A657">
+        <v>655</v>
+      </c>
+      <c r="B657">
+        <v>0.0004171016917098314</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2">
+      <c r="A658">
+        <v>656</v>
+      </c>
+      <c r="B658">
+        <v>0.0002273967256769538</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2">
+      <c r="A659">
+        <v>657</v>
+      </c>
+      <c r="B659">
+        <v>0.0004814480198547244</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2">
+      <c r="A660">
+        <v>658</v>
+      </c>
+      <c r="B660">
+        <v>-0.0003946209326386452</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2">
+      <c r="A661">
+        <v>659</v>
+      </c>
+      <c r="B661">
+        <v>0.003559286007657647</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2">
+      <c r="A662">
+        <v>660</v>
+      </c>
+      <c r="B662">
+        <v>0.0008813582244329154</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2">
+      <c r="A663">
+        <v>661</v>
+      </c>
+      <c r="B663">
+        <v>-0.000189087848411873</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2">
+      <c r="A664">
+        <v>662</v>
+      </c>
+      <c r="B664">
+        <v>0.000408508931286633</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2">
+      <c r="A665">
+        <v>663</v>
+      </c>
+      <c r="B665">
+        <v>0.0007062007789500058</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2">
+      <c r="A666">
+        <v>664</v>
+      </c>
+      <c r="B666">
+        <v>0.000495483516715467</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2">
+      <c r="A667">
+        <v>665</v>
+      </c>
+      <c r="B667">
+        <v>0.0006437699194066226</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2">
+      <c r="A668">
+        <v>666</v>
+      </c>
+      <c r="B668">
+        <v>0.00194555229973048</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2">
+      <c r="A669">
+        <v>667</v>
+      </c>
+      <c r="B669">
+        <v>-0.005243572872132063</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2">
+      <c r="A670">
+        <v>668</v>
+      </c>
+      <c r="B670">
+        <v>0.0006269272998906672</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2">
+      <c r="A671">
+        <v>669</v>
+      </c>
+      <c r="B671">
+        <v>0.000215065068914555</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2">
+      <c r="A672">
+        <v>670</v>
+      </c>
+      <c r="B672">
+        <v>0.0003094223502557725</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2">
+      <c r="A673">
+        <v>671</v>
+      </c>
+      <c r="B673">
+        <v>7.558441575383767E-05</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2">
+      <c r="A674">
+        <v>672</v>
+      </c>
+      <c r="B674">
+        <v>0.0003375422093085945</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2">
+      <c r="A675">
+        <v>673</v>
+      </c>
+      <c r="B675">
+        <v>0.0004767337813973427</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2">
+      <c r="A676">
+        <v>674</v>
+      </c>
+      <c r="B676">
+        <v>-4.466177415451966E-06</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2">
+      <c r="A677">
+        <v>675</v>
+      </c>
+      <c r="B677">
+        <v>0.0006698566139675677</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2">
+      <c r="A678">
+        <v>676</v>
+      </c>
+      <c r="B678">
+        <v>2.006197064474691E-05</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2">
+      <c r="A679">
+        <v>677</v>
+      </c>
+      <c r="B679">
+        <v>0.0003075506829190999</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2">
+      <c r="A680">
+        <v>678</v>
+      </c>
+      <c r="B680">
+        <v>9.57070296863094E-05</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2">
+      <c r="A681">
+        <v>679</v>
+      </c>
+      <c r="B681">
+        <v>0.0003627165860962123</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2">
+      <c r="A682">
+        <v>680</v>
+      </c>
+      <c r="B682">
+        <v>0.006714133080095053</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2">
+      <c r="A683">
+        <v>681</v>
+      </c>
+      <c r="B683">
+        <v>0.001139949425123632</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2">
+      <c r="A684">
+        <v>682</v>
+      </c>
+      <c r="B684">
+        <v>-0.0005121839931234717</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2">
+      <c r="A685">
+        <v>683</v>
+      </c>
+      <c r="B685">
+        <v>0.0002031061012530699</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2">
+      <c r="A686">
+        <v>684</v>
+      </c>
+      <c r="B686">
+        <v>0.0004523618845269084</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2">
+      <c r="A687">
+        <v>685</v>
+      </c>
+      <c r="B687">
+        <v>0.0005147476913407445</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2">
+      <c r="A688">
+        <v>686</v>
+      </c>
+      <c r="B688">
+        <v>0.0003383728035259992</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2">
+      <c r="A689">
+        <v>687</v>
+      </c>
+      <c r="B689">
+        <v>0.0002138918644050136</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2">
+      <c r="A690">
+        <v>688</v>
+      </c>
+      <c r="B690">
+        <v>0.0003302846744190902</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2">
+      <c r="A691">
+        <v>689</v>
+      </c>
+      <c r="B691">
+        <v>0.0009352061897516251</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2">
+      <c r="A692">
+        <v>690</v>
+      </c>
+      <c r="B692">
+        <v>0.0003208032576367259</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2">
+      <c r="A693">
+        <v>691</v>
+      </c>
+      <c r="B693">
+        <v>-0.0003139437176287174</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2">
+      <c r="A694">
+        <v>692</v>
+      </c>
+      <c r="B694">
+        <v>0.001066181110218167</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2">
+      <c r="A695">
+        <v>693</v>
+      </c>
+      <c r="B695">
+        <v>0.001287718303501606</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2">
+      <c r="A696">
+        <v>694</v>
+      </c>
+      <c r="B696">
+        <v>-0.000110270208097063</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2">
+      <c r="A697">
+        <v>695</v>
+      </c>
+      <c r="B697">
+        <v>1.940334868777427E-06</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2">
+      <c r="A698">
+        <v>696</v>
+      </c>
+      <c r="B698">
+        <v>0.000346647429978475</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2">
+      <c r="A699">
+        <v>697</v>
+      </c>
+      <c r="B699">
+        <v>0.0007668453035876155</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2">
+      <c r="A700">
+        <v>698</v>
+      </c>
+      <c r="B700">
+        <v>0.0005873558111488819</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2">
+      <c r="A701">
+        <v>699</v>
+      </c>
+      <c r="B701">
+        <v>-5.584938480751589E-05</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2">
+      <c r="A702">
+        <v>700</v>
+      </c>
+      <c r="B702">
+        <v>0.000102791607787367</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2">
+      <c r="A703">
+        <v>701</v>
+      </c>
+      <c r="B703">
+        <v>0.0002981770085170865</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2">
+      <c r="A704">
+        <v>702</v>
+      </c>
+      <c r="B704">
+        <v>0.0004008320684079081</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2">
+      <c r="A705">
+        <v>703</v>
+      </c>
+      <c r="B705">
+        <v>0.0004227979225106537</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2">
+      <c r="A706">
+        <v>704</v>
+      </c>
+      <c r="B706">
+        <v>0.000180505303433165</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2">
+      <c r="A707">
+        <v>705</v>
+      </c>
+      <c r="B707">
+        <v>-8.574838284403086E-05</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2">
+      <c r="A708">
+        <v>706</v>
+      </c>
+      <c r="B708">
+        <v>-0.007446011528372765</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2">
+      <c r="A709">
+        <v>707</v>
+      </c>
+      <c r="B709">
+        <v>0.0001403711648890749</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2">
+      <c r="A710">
+        <v>708</v>
+      </c>
+      <c r="B710">
+        <v>0.0009224688983522356</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2">
+      <c r="A711">
+        <v>709</v>
+      </c>
+      <c r="B711">
+        <v>0.0002448534942232072</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2">
+      <c r="A712">
+        <v>710</v>
+      </c>
+      <c r="B712">
+        <v>8.420572703471407E-05</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2">
+      <c r="A713">
+        <v>711</v>
+      </c>
+      <c r="B713">
+        <v>0.0002726283564697951</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2">
+      <c r="A714">
+        <v>712</v>
+      </c>
+      <c r="B714">
+        <v>0.0003723778645507991</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2">
+      <c r="A715">
+        <v>713</v>
+      </c>
+      <c r="B715">
+        <v>-4.941743827657774E-05</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2">
+      <c r="A716">
+        <v>714</v>
+      </c>
+      <c r="B716">
+        <v>0.0002736204769462347</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2">
+      <c r="A717">
+        <v>715</v>
+      </c>
+      <c r="B717">
+        <v>-0.0001067808188963681</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2">
+      <c r="A718">
+        <v>716</v>
+      </c>
+      <c r="B718">
+        <v>0.0003602943324949592</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2">
+      <c r="A719">
+        <v>717</v>
+      </c>
+      <c r="B719">
+        <v>1.952644561242778E-05</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2">
+      <c r="A720">
+        <v>718</v>
+      </c>
+      <c r="B720">
+        <v>0.0009410256170667708</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2">
+      <c r="A721">
+        <v>719</v>
+      </c>
+      <c r="B721">
+        <v>0.006224711891263723</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2">
+      <c r="A722">
+        <v>720</v>
+      </c>
+      <c r="B722">
+        <v>-2.01646671484923E-05</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2">
+      <c r="A723">
+        <v>721</v>
+      </c>
+      <c r="B723">
+        <v>0.0001908426202135161</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2">
+      <c r="A724">
+        <v>722</v>
+      </c>
+      <c r="B724">
+        <v>5.294451329973526E-05</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2">
+      <c r="A725">
+        <v>723</v>
+      </c>
+      <c r="B725">
+        <v>1.566492642268713E-06</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2">
+      <c r="A726">
+        <v>724</v>
+      </c>
+      <c r="B726">
+        <v>0.000313484895741567</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2">
+      <c r="A727">
+        <v>725</v>
+      </c>
+      <c r="B727">
+        <v>0.0004086481058038771</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2">
+      <c r="A728">
+        <v>726</v>
+      </c>
+      <c r="B728">
+        <v>0.0003516723518259823</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2">
+      <c r="A729">
+        <v>727</v>
+      </c>
+      <c r="B729">
+        <v>0.0003723143599927425</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2">
+      <c r="A730">
+        <v>728</v>
+      </c>
+      <c r="B730">
+        <v>0.0001824745268095285</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2">
+      <c r="A731">
+        <v>729</v>
+      </c>
+      <c r="B731">
+        <v>-5.831331145600416E-05</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2">
+      <c r="A732">
+        <v>730</v>
+      </c>
+      <c r="B732">
+        <v>0.0002271929406560957</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2">
+      <c r="A733">
+        <v>731</v>
+      </c>
+      <c r="B733">
+        <v>0.00127740518655628</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2">
+      <c r="A734">
+        <v>732</v>
+      </c>
+      <c r="B734">
+        <v>0.004861115943640471</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2">
+      <c r="A735">
+        <v>733</v>
+      </c>
+      <c r="B735">
+        <v>0.0004211059713270515</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2">
+      <c r="A736">
+        <v>734</v>
+      </c>
+      <c r="B736">
+        <v>0.000331036135321483</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2">
+      <c r="A737">
+        <v>735</v>
+      </c>
+      <c r="B737">
+        <v>0.0001692296791588888</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2">
+      <c r="A738">
+        <v>736</v>
+      </c>
+      <c r="B738">
+        <v>0.0002483463322278112</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2">
+      <c r="A739">
+        <v>737</v>
+      </c>
+      <c r="B739">
+        <v>0.0002612891548778862</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2">
+      <c r="A740">
+        <v>738</v>
+      </c>
+      <c r="B740">
+        <v>-0.0001167361770058051</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2">
+      <c r="A741">
+        <v>739</v>
+      </c>
+      <c r="B741">
+        <v>2.433130975987297E-05</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2">
+      <c r="A742">
+        <v>740</v>
+      </c>
+      <c r="B742">
+        <v>9.306798892794177E-05</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2">
+      <c r="A743">
+        <v>741</v>
+      </c>
+      <c r="B743">
+        <v>0.0003647962003014982</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2">
+      <c r="A744">
+        <v>742</v>
+      </c>
+      <c r="B744">
+        <v>3.822786311502568E-05</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2">
+      <c r="A745">
+        <v>743</v>
+      </c>
+      <c r="B745">
+        <v>0.0007998343789950013</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2">
+      <c r="A746">
+        <v>744</v>
+      </c>
+      <c r="B746">
+        <v>0.000153206245158799</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2">
+      <c r="A747">
+        <v>745</v>
+      </c>
+      <c r="B747">
+        <v>0.005060326308012009</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2">
+      <c r="A748">
+        <v>746</v>
+      </c>
+      <c r="B748">
+        <v>0.002020628890022635</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2">
+      <c r="A749">
+        <v>747</v>
+      </c>
+      <c r="B749">
+        <v>0.001007413491606712</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2">
+      <c r="A750">
+        <v>748</v>
+      </c>
+      <c r="B750">
+        <v>0.0005113029037602246</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2">
+      <c r="A751">
+        <v>749</v>
+      </c>
+      <c r="B751">
+        <v>9.051406959770247E-05</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2">
+      <c r="A752">
+        <v>750</v>
+      </c>
+      <c r="B752">
+        <v>0.0002285246300743893</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2">
+      <c r="A753">
+        <v>751</v>
+      </c>
+      <c r="B753">
+        <v>0.0001633331412449479</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2">
+      <c r="A754">
+        <v>752</v>
+      </c>
+      <c r="B754">
+        <v>0.000398858159314841</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2">
+      <c r="A755">
+        <v>753</v>
+      </c>
+      <c r="B755">
+        <v>0.0001577303773956373</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2">
+      <c r="A756">
+        <v>754</v>
+      </c>
+      <c r="B756">
+        <v>0.0004873359866905957</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2">
+      <c r="A757">
+        <v>755</v>
+      </c>
+      <c r="B757">
+        <v>0.0003687755379360169</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2">
+      <c r="A758">
+        <v>756</v>
+      </c>
+      <c r="B758">
+        <v>0.0002269784745294601</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2">
+      <c r="A759">
+        <v>757</v>
+      </c>
+      <c r="B759">
+        <v>0.0003737278748303652</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2">
+      <c r="A760">
+        <v>758</v>
+      </c>
+      <c r="B760">
+        <v>-0.003234394360333681</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2">
+      <c r="A761">
+        <v>759</v>
+      </c>
+      <c r="B761">
+        <v>0.0002872280310839415</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2">
+      <c r="A762">
+        <v>760</v>
+      </c>
+      <c r="B762">
+        <v>3.275764538557269E-05</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2">
+      <c r="A763">
+        <v>761</v>
+      </c>
+      <c r="B763">
+        <v>-1.450608760933392E-05</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2">
+      <c r="A764">
+        <v>762</v>
+      </c>
+      <c r="B764">
+        <v>0.0002713289286475629</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2">
+      <c r="A765">
+        <v>763</v>
+      </c>
+      <c r="B765">
+        <v>0.0001510485744802281</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2">
+      <c r="A766">
+        <v>764</v>
+      </c>
+      <c r="B766">
+        <v>0.0002500856062397361</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2">
+      <c r="A767">
+        <v>765</v>
+      </c>
+      <c r="B767">
+        <v>0.0005389320431277156</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2">
+      <c r="A768">
+        <v>766</v>
+      </c>
+      <c r="B768">
+        <v>0.0002740804629866034</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2">
+      <c r="A769">
+        <v>767</v>
+      </c>
+      <c r="B769">
+        <v>0.0002035508077824488</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2">
+      <c r="A770">
+        <v>768</v>
+      </c>
+      <c r="B770">
+        <v>0.0002680259058251977</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2">
+      <c r="A771">
+        <v>769</v>
+      </c>
+      <c r="B771">
+        <v>0.0004187568265479058</v>
+      </c>
+    </row>
+    <row r="772" spans="1:2">
+      <c r="A772">
+        <v>770</v>
+      </c>
+      <c r="B772">
+        <v>0.0001345776399830356</v>
+      </c>
+    </row>
+    <row r="773" spans="1:2">
+      <c r="A773">
+        <v>771</v>
+      </c>
+      <c r="B773">
+        <v>0.000468057143734768</v>
+      </c>
+    </row>
+    <row r="774" spans="1:2">
+      <c r="A774">
+        <v>772</v>
+      </c>
+      <c r="B774">
+        <v>0.0006200966890901327</v>
+      </c>
+    </row>
+    <row r="775" spans="1:2">
+      <c r="A775">
+        <v>773</v>
+      </c>
+      <c r="B775">
+        <v>0.001100893598049879</v>
+      </c>
+    </row>
+    <row r="776" spans="1:2">
+      <c r="A776">
+        <v>774</v>
+      </c>
+      <c r="B776">
+        <v>0.0004455716116353869</v>
+      </c>
+    </row>
+    <row r="777" spans="1:2">
+      <c r="A777">
+        <v>775</v>
+      </c>
+      <c r="B777">
+        <v>-9.061724995262921E-05</v>
+      </c>
+    </row>
+    <row r="778" spans="1:2">
+      <c r="A778">
+        <v>776</v>
+      </c>
+      <c r="B778">
+        <v>0.000210846759728156</v>
+      </c>
+    </row>
+    <row r="779" spans="1:2">
+      <c r="A779">
+        <v>777</v>
+      </c>
+      <c r="B779">
+        <v>5.30192228325177E-05</v>
+      </c>
+    </row>
+    <row r="780" spans="1:2">
+      <c r="A780">
+        <v>778</v>
+      </c>
+      <c r="B780">
+        <v>0.002106717089191079</v>
+      </c>
+    </row>
+    <row r="781" spans="1:2">
+      <c r="A781">
+        <v>779</v>
+      </c>
+      <c r="B781">
+        <v>0.0003121124755125493</v>
+      </c>
+    </row>
+    <row r="782" spans="1:2">
+      <c r="A782">
+        <v>780</v>
+      </c>
+      <c r="B782">
+        <v>0.0004530212318059057</v>
+      </c>
+    </row>
+    <row r="783" spans="1:2">
+      <c r="A783">
+        <v>781</v>
+      </c>
+      <c r="B783">
+        <v>0.0005174806574359536</v>
+      </c>
+    </row>
+    <row r="784" spans="1:2">
+      <c r="A784">
+        <v>782</v>
+      </c>
+      <c r="B784">
+        <v>0.0001622078416403383</v>
+      </c>
+    </row>
+    <row r="785" spans="1:2">
+      <c r="A785">
+        <v>783</v>
+      </c>
+      <c r="B785">
+        <v>0.0001628013851586729</v>
+      </c>
+    </row>
+    <row r="786" spans="1:2">
+      <c r="A786">
+        <v>784</v>
+      </c>
+      <c r="B786">
+        <v>0.0003061519237235188</v>
+      </c>
+    </row>
+    <row r="787" spans="1:2">
+      <c r="A787">
+        <v>785</v>
+      </c>
+      <c r="B787">
+        <v>0.0001329346268903464</v>
+      </c>
+    </row>
+    <row r="788" spans="1:2">
+      <c r="A788">
+        <v>786</v>
+      </c>
+      <c r="B788">
+        <v>0.0003252220631111413</v>
+      </c>
+    </row>
+    <row r="789" spans="1:2">
+      <c r="A789">
+        <v>787</v>
+      </c>
+      <c r="B789">
+        <v>8.539699774701148E-05</v>
+      </c>
+    </row>
+    <row r="790" spans="1:2">
+      <c r="A790">
+        <v>788</v>
+      </c>
+      <c r="B790">
+        <v>0.0002238935703644529</v>
+      </c>
+    </row>
+    <row r="791" spans="1:2">
+      <c r="A791">
+        <v>789</v>
+      </c>
+      <c r="B791">
+        <v>0.0005520277773030102</v>
+      </c>
+    </row>
+    <row r="792" spans="1:2">
+      <c r="A792">
+        <v>790</v>
+      </c>
+      <c r="B792">
+        <v>0.0002293930010637268</v>
+      </c>
+    </row>
+    <row r="793" spans="1:2">
+      <c r="A793">
+        <v>791</v>
+      </c>
+      <c r="B793">
+        <v>0.004215256310999393</v>
+      </c>
+    </row>
+    <row r="794" spans="1:2">
+      <c r="A794">
+        <v>792</v>
+      </c>
+      <c r="B794">
+        <v>-0.0001174914432340302</v>
+      </c>
+    </row>
+    <row r="795" spans="1:2">
+      <c r="A795">
+        <v>793</v>
+      </c>
+      <c r="B795">
+        <v>0.0002716117596719414</v>
+      </c>
+    </row>
+    <row r="796" spans="1:2">
+      <c r="A796">
+        <v>794</v>
+      </c>
+      <c r="B796">
+        <v>4.028998591820709E-05</v>
+      </c>
+    </row>
+    <row r="797" spans="1:2">
+      <c r="A797">
+        <v>795</v>
+      </c>
+      <c r="B797">
+        <v>7.716948312008753E-05</v>
+      </c>
+    </row>
+    <row r="798" spans="1:2">
+      <c r="A798">
+        <v>796</v>
+      </c>
+      <c r="B798">
+        <v>0.0001163351116701961</v>
+      </c>
+    </row>
+    <row r="799" spans="1:2">
+      <c r="A799">
+        <v>797</v>
+      </c>
+      <c r="B799">
+        <v>0.0001789336238289252</v>
+      </c>
+    </row>
+    <row r="800" spans="1:2">
+      <c r="A800">
+        <v>798</v>
+      </c>
+      <c r="B800">
+        <v>0.000387607840821147</v>
+      </c>
+    </row>
+    <row r="801" spans="1:2">
+      <c r="A801">
+        <v>799</v>
+      </c>
+      <c r="B801">
+        <v>0.0005292827845551074</v>
+      </c>
+    </row>
+    <row r="802" spans="1:2">
+      <c r="A802">
+        <v>800</v>
+      </c>
+      <c r="B802">
+        <v>0.0001161175023298711</v>
+      </c>
+    </row>
+    <row r="803" spans="1:2">
+      <c r="A803">
+        <v>801</v>
+      </c>
+      <c r="B803">
+        <v>-3.758189632208087E-05</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2">
+      <c r="A804">
+        <v>802</v>
+      </c>
+      <c r="B804">
+        <v>0.0001030436251312494</v>
+      </c>
+    </row>
+    <row r="805" spans="1:2">
+      <c r="A805">
+        <v>803</v>
+      </c>
+      <c r="B805">
+        <v>0.0004592205223161727</v>
+      </c>
+    </row>
+    <row r="806" spans="1:2">
+      <c r="A806">
+        <v>804</v>
+      </c>
+      <c r="B806">
+        <v>4.200543116894551E-05</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2">
+      <c r="A807">
+        <v>805</v>
+      </c>
+      <c r="B807">
+        <v>-9.438845154363662E-06</v>
+      </c>
+    </row>
+    <row r="808" spans="1:2">
+      <c r="A808">
+        <v>806</v>
+      </c>
+      <c r="B808">
+        <v>0.0001901625219034031</v>
+      </c>
+    </row>
+    <row r="809" spans="1:2">
+      <c r="A809">
+        <v>807</v>
+      </c>
+      <c r="B809">
+        <v>0.0007273419760167599</v>
+      </c>
+    </row>
+    <row r="810" spans="1:2">
+      <c r="A810">
+        <v>808</v>
+      </c>
+      <c r="B810">
+        <v>0.0002254580031149089</v>
+      </c>
+    </row>
+    <row r="811" spans="1:2">
+      <c r="A811">
+        <v>809</v>
+      </c>
+      <c r="B811">
+        <v>0.0004606463480740786</v>
+      </c>
+    </row>
+    <row r="812" spans="1:2">
+      <c r="A812">
+        <v>810</v>
+      </c>
+      <c r="B812">
+        <v>0.0005810240982100368</v>
+      </c>
+    </row>
+    <row r="813" spans="1:2">
+      <c r="A813">
+        <v>811</v>
+      </c>
+      <c r="B813">
+        <v>0.0004936343757435679</v>
+      </c>
+    </row>
+    <row r="814" spans="1:2">
+      <c r="A814">
+        <v>812</v>
+      </c>
+      <c r="B814">
+        <v>0.0001261603465536609</v>
+      </c>
+    </row>
+    <row r="815" spans="1:2">
+      <c r="A815">
+        <v>813</v>
+      </c>
+      <c r="B815">
+        <v>0.0005602819728665054</v>
+      </c>
+    </row>
+    <row r="816" spans="1:2">
+      <c r="A816">
+        <v>814</v>
+      </c>
+      <c r="B816">
+        <v>0.000336681812768802</v>
+      </c>
+    </row>
+    <row r="817" spans="1:2">
+      <c r="A817">
+        <v>815</v>
+      </c>
+      <c r="B817">
+        <v>0.0004459137853700668</v>
+      </c>
+    </row>
+    <row r="818" spans="1:2">
+      <c r="A818">
+        <v>816</v>
+      </c>
+      <c r="B818">
+        <v>-0.0002916798985097557</v>
+      </c>
+    </row>
+    <row r="819" spans="1:2">
+      <c r="A819">
+        <v>817</v>
+      </c>
+      <c r="B819">
+        <v>0.0003543112543411553</v>
       </c>
     </row>
   </sheetData>
@@ -9124,12 +15668,508 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.006927728652954102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.008339047431945801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.000849604606628418</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.005140304565429688</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.006284594535827637</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.008747220039367676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.00368201732635498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.006192445755004883</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.007530450820922852</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.007002949714660645</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.008764743804931641</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.01139700412750244</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <v>0.0106658935546875</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>0.002946257591247559</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>0.00643002986907959</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>0.002986907958984375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <v>0.002658247947692871</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <v>0.006385564804077148</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <v>0.008308172225952148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <v>0.00443267822265625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <v>0.00586998462677002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <v>0.005215644836425781</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24">
+        <v>0.002424955368041992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25">
+        <v>0.002989649772644043</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>0.002846598625183105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27">
+        <v>0.009294629096984863</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>0.007655501365661621</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29">
+        <v>0.004592061042785645</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30">
+        <v>0.00908958911895752</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31">
+        <v>0.008010506629943848</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32">
+        <v>0.004780292510986328</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33">
+        <v>0.006893277168273926</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34">
+        <v>0.008508443832397461</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>33</v>
+      </c>
+      <c r="B35">
+        <v>0.01159977912902832</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>34</v>
+      </c>
+      <c r="B36">
+        <v>0.001094698905944824</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>35</v>
+      </c>
+      <c r="B37">
+        <v>0.007869482040405273</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>36</v>
+      </c>
+      <c r="B38">
+        <v>0.01247107982635498</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>37</v>
+      </c>
+      <c r="B39">
+        <v>0.006876349449157715</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>38</v>
+      </c>
+      <c r="B40">
+        <v>0.007581710815429688</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>39</v>
+      </c>
+      <c r="B41">
+        <v>0.004193425178527832</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>0.008647441864013672</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>0.009756326675415039</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>0.009927988052368164</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>43</v>
+      </c>
+      <c r="B45">
+        <v>0.006780385971069336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>44</v>
+      </c>
+      <c r="B46">
+        <v>0.01003468036651611</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>0.005895614624023438</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>0.01664948463439941</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>47</v>
+      </c>
+      <c r="B49">
+        <v>0.004834532737731934</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>48</v>
+      </c>
+      <c r="B50">
+        <v>0.001848340034484863</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>49</v>
+      </c>
+      <c r="B51">
+        <v>0.001433014869689941</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>50</v>
+      </c>
+      <c r="B52">
+        <v>0.003285765647888184</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>51</v>
+      </c>
+      <c r="B53">
+        <v>0.001237630844116211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>52</v>
+      </c>
+      <c r="B54">
+        <v>0.0102086067199707</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>53</v>
+      </c>
+      <c r="B55">
+        <v>0.005244612693786621</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>54</v>
+      </c>
+      <c r="B56">
+        <v>-0.004286050796508789</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>55</v>
+      </c>
+      <c r="B57">
+        <v>0.009131312370300293</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>56</v>
+      </c>
+      <c r="B58">
+        <v>0.007940053939819336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>57</v>
+      </c>
+      <c r="B59">
+        <v>0.011039137840271</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>58</v>
+      </c>
+      <c r="B60">
+        <v>7.62939453125E-06</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>0.006267905235290527</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>60</v>
+      </c>
+      <c r="B62">
+        <v>0.007265090942382812</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>61</v>
+      </c>
+      <c r="B63">
+        <v>0.00227653980255127</v>
       </c>
     </row>
   </sheetData>
@@ -9139,12 +16179,108 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="1:2">
       <c r="B1" t="s">
         <v>489</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.02783036231994629</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.03359091281890869</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>0.04083073139190674</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>0.02500617504119873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>0.01949226856231689</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>0.03923773765563965</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0.03327977657318115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>0.03958642482757568</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>0.04596531391143799</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>0.03096210956573486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>0.01573264598846436</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>0.03482556343078613</v>
       </c>
     </row>
   </sheetData>
